--- a/Data/Data-ETFPESOV.xlsx
+++ b/Data/Data-ETFPESOV.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Desktop\Dashboards\ETFPESOV\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CFCCACA-0B55-4983-B6D4-7346C665877D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D95F7EC-2D64-4E34-BDCB-1A95E4CBD679}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{F6F75CCC-009E-413C-B55D-A670828334F1}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="31">
   <si>
     <t>Fecha</t>
   </si>
@@ -515,7 +515,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E89EACC1-FF2B-4ECD-9B28-49A6BC374F12}">
-  <dimension ref="A1:AD364"/>
+  <dimension ref="A1:AD365"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="24" max="27" width="11.5546875" style="3"/>
@@ -31153,8 +31153,8 @@
       <c r="C363">
         <v>150171104.33000001</v>
       </c>
-      <c r="D363" t="s">
-        <v>23</v>
+      <c r="D363">
+        <v>547</v>
       </c>
       <c r="E363">
         <v>3384</v>
@@ -31169,7 +31169,7 @@
         <v>5.9100017074000002</v>
       </c>
       <c r="I363">
-        <v>182.88</v>
+        <v>182.40043803320751</v>
       </c>
       <c r="J363">
         <v>6.41</v>
@@ -31181,7 +31181,7 @@
         <v>11.03223980000001</v>
       </c>
       <c r="M363">
-        <v>11.78825918832529</v>
+        <v>11.495119438540403</v>
       </c>
       <c r="N363">
         <v>6.5799791199999991</v>
@@ -31190,19 +31190,19 @@
         <v>6.5699999999999994</v>
       </c>
       <c r="P363">
-        <v>4.7028467483318785E-2</v>
+        <v>4.2890509546017093E-3</v>
       </c>
       <c r="Q363">
-        <v>3.3933928961874957E-2</v>
+        <v>3.9631041697139081E-3</v>
       </c>
       <c r="R363">
-        <v>0.11060754078161893</v>
+        <v>0.10888647456276021</v>
       </c>
       <c r="S363">
-        <v>0.30054235834682252</v>
+        <v>4.2171598801277188E-2</v>
       </c>
       <c r="T363">
-        <v>0.32755468437867252</v>
+        <v>6.8177775518007966E-2</v>
       </c>
       <c r="U363">
         <v>112.8</v>
@@ -31248,6 +31248,9 @@
       <c r="D364" t="s">
         <v>23</v>
       </c>
+      <c r="E364">
+        <v>7861.7</v>
+      </c>
       <c r="F364">
         <v>1</v>
       </c>
@@ -31279,13 +31282,13 @@
         <v>6.5699999999999994</v>
       </c>
       <c r="P364">
-        <v>6.6992483992895729E-2</v>
+        <v>4.3944875414737459E-3</v>
       </c>
       <c r="Q364">
-        <v>4.783553059903891E-2</v>
+        <v>4.0035873721614695E-3</v>
       </c>
       <c r="R364">
-        <v>0.11226532309381644</v>
+        <v>0.10887865624986232</v>
       </c>
       <c r="S364">
         <v>5.0394769067740874E-2</v>
@@ -31294,7 +31297,7 @@
         <v>7.710227115416135E-2</v>
       </c>
       <c r="U364">
-        <v>112.8</v>
+        <v>112.31</v>
       </c>
       <c r="V364">
         <v>-2.0670901147217924</v>
@@ -31303,24 +31306,116 @@
         <v>-3.9109511967821864</v>
       </c>
       <c r="X364" s="3">
-        <v>1.5379915289035484E-2</v>
+        <v>1.0969133742124049E-2</v>
       </c>
       <c r="Y364" s="3">
-        <v>5.6449252352799295E-3</v>
+        <v>5.5026419595731093E-3</v>
       </c>
       <c r="Z364" s="3">
-        <v>4.1842846656368502E-3</v>
+        <v>4.1107716398549928E-3</v>
       </c>
       <c r="AA364" s="3">
-        <v>4.553490847039301E-3</v>
+        <v>4.5289865051120152E-3</v>
       </c>
       <c r="AB364">
-        <v>9994.01</v>
+        <v>9703.1049999999996</v>
       </c>
       <c r="AC364">
+        <v>10576.775000000001</v>
+      </c>
+      <c r="AD364">
+        <v>14321.875</v>
+      </c>
+    </row>
+    <row r="365" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="A365" s="1">
+        <v>46283</v>
+      </c>
+      <c r="B365">
+        <v>110.67340795</v>
+      </c>
+      <c r="C365">
+        <v>149685784.25999999</v>
+      </c>
+      <c r="D365" t="s">
+        <v>23</v>
+      </c>
+      <c r="E365" t="s">
+        <v>23</v>
+      </c>
+      <c r="F365">
+        <v>4</v>
+      </c>
+      <c r="G365">
+        <v>6.3579762243269</v>
+      </c>
+      <c r="H365">
+        <v>6.0463281355343126</v>
+      </c>
+      <c r="I365">
+        <v>181.83</v>
+      </c>
+      <c r="J365">
+        <v>6.4</v>
+      </c>
+      <c r="K365">
+        <v>6.08</v>
+      </c>
+      <c r="L365">
+        <v>10.673407950000001</v>
+      </c>
+      <c r="M365">
+        <v>11.146430272381846</v>
+      </c>
+      <c r="N365">
+        <v>6.5791947586887867</v>
+      </c>
+      <c r="O365">
+        <v>6.5699999999999994</v>
+      </c>
+      <c r="P365">
+        <v>4.372674693305989E-3</v>
+      </c>
+      <c r="Q365">
+        <v>3.9727637591424241E-3</v>
+      </c>
+      <c r="R365">
+        <v>0.10887495167388754</v>
+      </c>
+      <c r="S365">
+        <v>5.0405785332741093E-2</v>
+      </c>
+      <c r="T365">
+        <v>8.3632683139500674E-2</v>
+      </c>
+      <c r="U365">
+        <v>112.31</v>
+      </c>
+      <c r="V365">
+        <v>-2.4355925637628006</v>
+      </c>
+      <c r="W365">
+        <v>-3.9109511967821864</v>
+      </c>
+      <c r="X365" s="3">
+        <v>1.4787581590867571E-2</v>
+      </c>
+      <c r="Y365" s="3">
+        <v>5.6499551773537644E-3</v>
+      </c>
+      <c r="Z365" s="3">
+        <v>4.302365294292408E-3</v>
+      </c>
+      <c r="AA365" s="3">
+        <v>4.5876232620566271E-3</v>
+      </c>
+      <c r="AB365">
+        <v>9412.2000000000007</v>
+      </c>
+      <c r="AC365">
         <v>10628.95</v>
       </c>
-      <c r="AD364">
+      <c r="AD365">
         <v>14490.15</v>
       </c>
     </row>

--- a/Data/Data-ETFPESOV.xlsx
+++ b/Data/Data-ETFPESOV.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Desktop\Dashboards\ETFPESOV\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D95F7EC-2D64-4E34-BDCB-1A95E4CBD679}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3151095-F89A-4E9B-9E3C-3D9CD9BC88D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{F6F75CCC-009E-413C-B55D-A670828334F1}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="31">
   <si>
     <t>Fecha</t>
   </si>
@@ -515,7 +515,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E89EACC1-FF2B-4ECD-9B28-49A6BC374F12}">
-  <dimension ref="A1:AD365"/>
+  <dimension ref="A1:AD366"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="24" max="27" width="11.5546875" style="3"/>
@@ -31245,8 +31245,8 @@
       <c r="C364">
         <v>150251150.05000001</v>
       </c>
-      <c r="D364" t="s">
-        <v>23</v>
+      <c r="D364">
+        <v>547</v>
       </c>
       <c r="E364">
         <v>7861.7</v>
@@ -31337,11 +31337,11 @@
       <c r="C365">
         <v>149685784.25999999</v>
       </c>
-      <c r="D365" t="s">
-        <v>23</v>
-      </c>
-      <c r="E365" t="s">
-        <v>23</v>
+      <c r="D365">
+        <v>547</v>
+      </c>
+      <c r="E365">
+        <v>36206.1</v>
       </c>
       <c r="F365">
         <v>4</v>
@@ -31389,7 +31389,7 @@
         <v>8.3632683139500674E-2</v>
       </c>
       <c r="U365">
-        <v>112.31</v>
+        <v>112.44</v>
       </c>
       <c r="V365">
         <v>-2.4355925637628006</v>
@@ -31398,24 +31398,116 @@
         <v>-3.9109511967821864</v>
       </c>
       <c r="X365" s="3">
-        <v>1.4787581590867571E-2</v>
+        <v>1.5962208833382174E-2</v>
       </c>
       <c r="Y365" s="3">
-        <v>5.6499551773537644E-3</v>
+        <v>5.6878463787252038E-3</v>
       </c>
       <c r="Z365" s="3">
-        <v>4.302365294292408E-3</v>
+        <v>4.3219424150009846E-3</v>
       </c>
       <c r="AA365" s="3">
-        <v>4.5876232620566271E-3</v>
+        <v>4.5941489689594866E-3</v>
       </c>
       <c r="AB365">
-        <v>9412.2000000000007</v>
+        <v>9703.1049999999996</v>
       </c>
       <c r="AC365">
-        <v>10628.95</v>
+        <v>10634.04</v>
       </c>
       <c r="AD365">
+        <v>14523.3</v>
+      </c>
+    </row>
+    <row r="366" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="A366" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B366">
+        <v>110.81867879520665</v>
+      </c>
+      <c r="C366">
+        <v>149882263.070517</v>
+      </c>
+      <c r="D366" t="s">
+        <v>23</v>
+      </c>
+      <c r="E366" t="s">
+        <v>23</v>
+      </c>
+      <c r="F366">
+        <v>1</v>
+      </c>
+      <c r="G366">
+        <v>6.3557316163667386</v>
+      </c>
+      <c r="H366">
+        <v>6.0441481168528863</v>
+      </c>
+      <c r="I366">
+        <v>182.08</v>
+      </c>
+      <c r="J366">
+        <v>6.4</v>
+      </c>
+      <c r="K366">
+        <v>6.0699999999999994</v>
+      </c>
+      <c r="L366">
+        <v>10.81867879520666</v>
+      </c>
+      <c r="M366">
+        <v>11.299246680939801</v>
+      </c>
+      <c r="N366">
+        <v>6.5793489930680016</v>
+      </c>
+      <c r="O366">
+        <v>6.5699999999999994</v>
+      </c>
+      <c r="P366">
+        <v>4.4355898494029579E-3</v>
+      </c>
+      <c r="Q366">
+        <v>4.0198950463059104E-3</v>
+      </c>
+      <c r="R366">
+        <v>0.10887551116599235</v>
+      </c>
+      <c r="S366">
+        <v>4.9291594819744766E-2</v>
+      </c>
+      <c r="T366">
+        <v>8.7653872026094426E-2</v>
+      </c>
+      <c r="U366">
+        <v>112.44</v>
+      </c>
+      <c r="V366">
+        <v>-2.3075287027786717</v>
+      </c>
+      <c r="W366">
+        <v>-3.9109511967821864</v>
+      </c>
+      <c r="X366" s="3">
+        <v>1.4630396449587302E-2</v>
+      </c>
+      <c r="Y366" s="3">
+        <v>5.827183966778289E-3</v>
+      </c>
+      <c r="Z366" s="3">
+        <v>4.4744891749780857E-3</v>
+      </c>
+      <c r="AA366" s="3">
+        <v>4.6558024365681815E-3</v>
+      </c>
+      <c r="AB366">
+        <v>9994.01</v>
+      </c>
+      <c r="AC366">
+        <v>10639.13</v>
+      </c>
+      <c r="AD366">
         <v>14490.15</v>
       </c>
     </row>

--- a/Data/Data-ETFPESOV.xlsx
+++ b/Data/Data-ETFPESOV.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Desktop\Dashboards\ETFPESOV\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3151095-F89A-4E9B-9E3C-3D9CD9BC88D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3E530AB-2A3A-447A-8C59-FD3AA774A2C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{F6F75CCC-009E-413C-B55D-A670828334F1}"/>
   </bookViews>
@@ -515,7 +515,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E89EACC1-FF2B-4ECD-9B28-49A6BC374F12}">
-  <dimension ref="A1:AD366"/>
+  <dimension ref="A1:AD367"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="24" max="27" width="11.5546875" style="3"/>
@@ -31429,11 +31429,11 @@
       <c r="C366">
         <v>149882263.070517</v>
       </c>
-      <c r="D366" t="s">
-        <v>23</v>
-      </c>
-      <c r="E366" t="s">
-        <v>23</v>
+      <c r="D366">
+        <v>547</v>
+      </c>
+      <c r="E366">
+        <v>11151.15</v>
       </c>
       <c r="F366">
         <v>1</v>
@@ -31481,7 +31481,7 @@
         <v>8.7653872026094426E-2</v>
       </c>
       <c r="U366">
-        <v>112.44</v>
+        <v>112.64</v>
       </c>
       <c r="V366">
         <v>-2.3075287027786717</v>
@@ -31490,25 +31490,117 @@
         <v>-3.9109511967821864</v>
       </c>
       <c r="X366" s="3">
-        <v>1.4630396449587302E-2</v>
+        <v>1.6435146354335739E-2</v>
       </c>
       <c r="Y366" s="3">
-        <v>5.827183966778289E-3</v>
+        <v>5.885401705641142E-3</v>
       </c>
       <c r="Z366" s="3">
-        <v>4.4744891749780857E-3</v>
+        <v>4.5045683400572268E-3</v>
       </c>
       <c r="AA366" s="3">
-        <v>4.6558024365681815E-3</v>
+        <v>4.6658288249278946E-3</v>
       </c>
       <c r="AB366">
-        <v>9994.01</v>
+        <v>10047.755000000001</v>
       </c>
       <c r="AC366">
-        <v>10639.13</v>
+        <v>10696.294999999998</v>
       </c>
       <c r="AD366">
-        <v>14490.15</v>
+        <v>14321.875</v>
+      </c>
+    </row>
+    <row r="367" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="A367" s="1">
+        <v>46287</v>
+      </c>
+      <c r="B367">
+        <v>110.78181239025936</v>
+      </c>
+      <c r="C367">
+        <v>149832401.25782579</v>
+      </c>
+      <c r="D367" t="s">
+        <v>23</v>
+      </c>
+      <c r="E367" t="s">
+        <v>23</v>
+      </c>
+      <c r="F367">
+        <v>2</v>
+      </c>
+      <c r="G367">
+        <v>6.3555408481594524</v>
+      </c>
+      <c r="H367">
+        <v>6.0612159766497733</v>
+      </c>
+      <c r="I367">
+        <v>182.03</v>
+      </c>
+      <c r="J367">
+        <v>6.4</v>
+      </c>
+      <c r="K367">
+        <v>6.09</v>
+      </c>
+      <c r="L367">
+        <v>10.781812390259372</v>
+      </c>
+      <c r="M367">
+        <v>11.26868339922822</v>
+      </c>
+      <c r="N367">
+        <v>6.57934675882227</v>
+      </c>
+      <c r="O367">
+        <v>6.5699999999999994</v>
+      </c>
+      <c r="P367">
+        <v>4.3772927667476641E-3</v>
+      </c>
+      <c r="Q367">
+        <v>4.056640700670985E-3</v>
+      </c>
+      <c r="R367">
+        <v>0.10887478134796312</v>
+      </c>
+      <c r="S367">
+        <v>5.2597659179975942E-2</v>
+      </c>
+      <c r="T367">
+        <v>9.0874488519987473E-2</v>
+      </c>
+      <c r="U367">
+        <v>112.64</v>
+      </c>
+      <c r="V367">
+        <v>-2.3400283702201263</v>
+      </c>
+      <c r="W367">
+        <v>-3.9109511967821864</v>
+      </c>
+      <c r="X367" s="3">
+        <v>1.6773399619015583E-2</v>
+      </c>
+      <c r="Y367" s="3">
+        <v>6.2941648043504965E-3</v>
+      </c>
+      <c r="Z367" s="3">
+        <v>4.7738208465831012E-3</v>
+      </c>
+      <c r="AA367" s="3">
+        <v>4.7392286830733087E-3</v>
+      </c>
+      <c r="AB367">
+        <v>10101.5</v>
+      </c>
+      <c r="AC367">
+        <v>10753.46</v>
+      </c>
+      <c r="AD367">
+        <v>14153.6</v>
       </c>
     </row>
   </sheetData>

--- a/Data/Data-ETFPESOV.xlsx
+++ b/Data/Data-ETFPESOV.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Desktop\Dashboards\ETFPESOV\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D638D73-6A6E-47B4-863A-212E144E12FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B9CE4C2-8AFF-4B35-95B7-1892C6BCBAD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{F6F75CCC-009E-413C-B55D-A670828334F1}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="35">
   <si>
     <t>Fecha</t>
   </si>
@@ -141,6 +141,9 @@
   </si>
   <si>
     <t>Slippage 360 días</t>
+  </si>
+  <si>
+    <t>Dislocation 360 días</t>
   </si>
 </sst>
 </file>
@@ -524,13 +527,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E89EACC1-FF2B-4ECD-9B28-49A6BC374F12}">
-  <dimension ref="A1:AG367"/>
+  <dimension ref="A1:AH367"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="27" max="30" width="11.5546875" style="3"/>
+    <col min="27" max="31" width="11.5546875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -621,17 +624,20 @@
       <c r="AD1" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AE1" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="AF1" t="s">
         <v>28</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AG1" t="s">
         <v>29</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AH1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>45748</v>
       </c>
@@ -684,7 +690,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>45749</v>
       </c>
@@ -743,7 +749,7 @@
         <v>1.2143671677051771E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>45750</v>
       </c>
@@ -802,7 +808,7 @@
         <v>9.1175034119250764E-3</v>
       </c>
     </row>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>45751</v>
       </c>
@@ -861,7 +867,7 @@
         <v>1.1159691476292588E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>45754</v>
       </c>
@@ -920,7 +926,7 @@
         <v>1.3318351860941879E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>45755</v>
       </c>
@@ -979,7 +985,7 @@
         <v>1.4496105894190592E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>45756</v>
       </c>
@@ -1038,7 +1044,7 @@
         <v>1.059531283173043E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>45757</v>
       </c>
@@ -1097,7 +1103,7 @@
         <v>9.5170229436190024E-3</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>45758</v>
       </c>
@@ -1156,7 +1162,7 @@
         <v>1.2588309241094331E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>45761</v>
       </c>
@@ -1215,7 +1221,7 @@
         <v>3.6875895667234371E-3</v>
       </c>
     </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>45762</v>
       </c>
@@ -1274,7 +1280,7 @@
         <v>4.4103347852244568E-3</v>
       </c>
     </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>45763</v>
       </c>
@@ -1333,7 +1339,7 @@
         <v>1.069542784982902E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>45768</v>
       </c>
@@ -1392,7 +1398,7 @@
         <v>3.2775521211678704E-3</v>
       </c>
     </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>45769</v>
       </c>
@@ -1451,7 +1457,7 @@
         <v>8.2411514863298674E-3</v>
       </c>
     </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>45770</v>
       </c>
@@ -1510,7 +1516,7 @@
         <v>9.8259889689884528E-3</v>
       </c>
     </row>
-    <row r="17" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>45771</v>
       </c>
@@ -1569,7 +1575,7 @@
         <v>6.1477814565573663E-3</v>
       </c>
     </row>
-    <row r="18" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>45772</v>
       </c>
@@ -1628,7 +1634,7 @@
         <v>7.6715295615414902E-3</v>
       </c>
     </row>
-    <row r="19" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>45775</v>
       </c>
@@ -1687,7 +1693,7 @@
         <v>6.3277755685609005E-4</v>
       </c>
     </row>
-    <row r="20" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>45776</v>
       </c>
@@ -1746,7 +1752,7 @@
         <v>2.1853312366791888E-3</v>
       </c>
     </row>
-    <row r="21" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>45777</v>
       </c>
@@ -1805,7 +1811,7 @@
         <v>5.0849546986864169E-5</v>
       </c>
     </row>
-    <row r="22" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>45779</v>
       </c>
@@ -1864,7 +1870,7 @@
         <v>5.3071721745676648E-3</v>
       </c>
     </row>
-    <row r="23" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>45782</v>
       </c>
@@ -1923,7 +1929,7 @@
         <v>1.5255835720811017E-3</v>
       </c>
     </row>
-    <row r="24" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>45783</v>
       </c>
@@ -1982,7 +1988,7 @@
         <v>7.5744419926038198E-4</v>
       </c>
     </row>
-    <row r="25" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>45784</v>
       </c>
@@ -2041,7 +2047,7 @@
         <v>3.3848643678949797E-3</v>
       </c>
     </row>
-    <row r="26" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>45785</v>
       </c>
@@ -2100,7 +2106,7 @@
         <v>2.6257951324997197E-3</v>
       </c>
     </row>
-    <row r="27" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>45786</v>
       </c>
@@ -2159,7 +2165,7 @@
         <v>5.2926816086399375E-3</v>
       </c>
     </row>
-    <row r="28" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>45789</v>
       </c>
@@ -2218,7 +2224,7 @@
         <v>3.0927042456607712E-3</v>
       </c>
     </row>
-    <row r="29" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>45790</v>
       </c>
@@ -2277,7 +2283,7 @@
         <v>6.1827320898003579E-3</v>
       </c>
     </row>
-    <row r="30" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>45791</v>
       </c>
@@ -2339,7 +2345,7 @@
         <v>5.6980368512211665E-3</v>
       </c>
     </row>
-    <row r="31" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>45792</v>
       </c>
@@ -2403,11 +2409,11 @@
       <c r="AA31" s="3">
         <v>4.8608982705755643E-4</v>
       </c>
-      <c r="AE31">
+      <c r="AF31">
         <v>9647.375</v>
       </c>
     </row>
-    <row r="32" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>45793</v>
       </c>
@@ -2474,11 +2480,11 @@
       <c r="AB32" s="3">
         <v>6.2665012949956562E-3</v>
       </c>
-      <c r="AE32">
+      <c r="AF32">
         <v>10502.5</v>
       </c>
     </row>
-    <row r="33" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <v>45796</v>
       </c>
@@ -2545,11 +2551,11 @@
       <c r="AB33" s="3">
         <v>6.1630421294285092E-3</v>
       </c>
-      <c r="AE33">
+      <c r="AF33">
         <v>9670</v>
       </c>
     </row>
-    <row r="34" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <v>45797</v>
       </c>
@@ -2616,11 +2622,11 @@
       <c r="AB34" s="3">
         <v>5.9266907183791497E-3</v>
       </c>
-      <c r="AE34">
+      <c r="AF34">
         <v>9670</v>
       </c>
     </row>
-    <row r="35" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <v>45798</v>
       </c>
@@ -2687,11 +2693,11 @@
       <c r="AB35" s="3">
         <v>5.6861777173842437E-3</v>
       </c>
-      <c r="AE35">
+      <c r="AF35">
         <v>9670</v>
       </c>
     </row>
-    <row r="36" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <v>45799</v>
       </c>
@@ -2758,11 +2764,11 @@
       <c r="AB36" s="3">
         <v>5.5889371273719155E-3</v>
       </c>
-      <c r="AE36">
+      <c r="AF36">
         <v>9151.625</v>
       </c>
     </row>
-    <row r="37" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <v>45800</v>
       </c>
@@ -2829,11 +2835,11 @@
       <c r="AB37" s="3">
         <v>5.259256676984559E-3</v>
       </c>
-      <c r="AE37">
+      <c r="AF37">
         <v>8644.5</v>
       </c>
     </row>
-    <row r="38" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
         <v>45803</v>
       </c>
@@ -2900,11 +2906,11 @@
       <c r="AB38" s="3">
         <v>4.8532578926983039E-3</v>
       </c>
-      <c r="AE38">
+      <c r="AF38">
         <v>7933</v>
       </c>
     </row>
-    <row r="39" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
         <v>45804</v>
       </c>
@@ -2971,11 +2977,11 @@
       <c r="AB39" s="3">
         <v>4.6787848643285324E-3</v>
       </c>
-      <c r="AE39">
+      <c r="AF39">
         <v>7933</v>
       </c>
     </row>
-    <row r="40" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
         <v>45805</v>
       </c>
@@ -3042,11 +3048,11 @@
       <c r="AB40" s="3">
         <v>4.3807507694360072E-3</v>
       </c>
-      <c r="AE40">
+      <c r="AF40">
         <v>7645.5</v>
       </c>
     </row>
-    <row r="41" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
         <v>45806</v>
       </c>
@@ -3113,11 +3119,11 @@
       <c r="AB41" s="3">
         <v>4.3637680370545552E-3</v>
       </c>
-      <c r="AE41">
+      <c r="AF41">
         <v>7645.5</v>
       </c>
     </row>
-    <row r="42" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A42" s="1">
         <v>45807</v>
       </c>
@@ -3184,11 +3190,11 @@
       <c r="AB42" s="3">
         <v>4.393838404902802E-3</v>
       </c>
-      <c r="AE42">
+      <c r="AF42">
         <v>7645.5</v>
       </c>
     </row>
-    <row r="43" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
         <v>45810</v>
       </c>
@@ -3255,11 +3261,11 @@
       <c r="AB43" s="3">
         <v>4.4301950701605862E-3</v>
       </c>
-      <c r="AE43">
+      <c r="AF43">
         <v>7498.4</v>
       </c>
     </row>
-    <row r="44" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A44" s="1">
         <v>45811</v>
       </c>
@@ -3326,11 +3332,11 @@
       <c r="AB44" s="3">
         <v>4.137834048655825E-3</v>
       </c>
-      <c r="AE44">
+      <c r="AF44">
         <v>7498.4</v>
       </c>
     </row>
-    <row r="45" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A45" s="1">
         <v>45812</v>
       </c>
@@ -3397,11 +3403,11 @@
       <c r="AB45" s="3">
         <v>4.4570803702725318E-3</v>
       </c>
-      <c r="AE45">
+      <c r="AF45">
         <v>7645.5</v>
       </c>
     </row>
-    <row r="46" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A46" s="1">
         <v>45813</v>
       </c>
@@ -3468,11 +3474,11 @@
       <c r="AB46" s="3">
         <v>4.6162492353916474E-3</v>
       </c>
-      <c r="AE46">
+      <c r="AF46">
         <v>7498.4</v>
       </c>
     </row>
-    <row r="47" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A47" s="1">
         <v>45814</v>
       </c>
@@ -3539,11 +3545,11 @@
       <c r="AB47" s="3">
         <v>4.3222752519325421E-3</v>
       </c>
-      <c r="AE47">
+      <c r="AF47">
         <v>7498.4</v>
       </c>
     </row>
-    <row r="48" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A48" s="1">
         <v>45817</v>
       </c>
@@ -3610,11 +3616,11 @@
       <c r="AB48" s="3">
         <v>4.6849065629606364E-3</v>
       </c>
-      <c r="AE48">
+      <c r="AF48">
         <v>7293.4</v>
       </c>
     </row>
-    <row r="49" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A49" s="1">
         <v>45818</v>
       </c>
@@ -3681,11 +3687,11 @@
       <c r="AB49" s="3">
         <v>4.6384705220430689E-3</v>
       </c>
-      <c r="AE49">
+      <c r="AF49">
         <v>7134.1</v>
       </c>
     </row>
-    <row r="50" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A50" s="1">
         <v>45819</v>
       </c>
@@ -3752,11 +3758,11 @@
       <c r="AB50" s="3">
         <v>4.6664129334426383E-3</v>
       </c>
-      <c r="AE50">
+      <c r="AF50">
         <v>7293.4</v>
       </c>
     </row>
-    <row r="51" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A51" s="1">
         <v>45820</v>
       </c>
@@ -3823,11 +3829,11 @@
       <c r="AB51" s="3">
         <v>5.2675602972583249E-3</v>
       </c>
-      <c r="AE51">
+      <c r="AF51">
         <v>7134.1</v>
       </c>
     </row>
-    <row r="52" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A52" s="1">
         <v>45821</v>
       </c>
@@ -3894,11 +3900,11 @@
       <c r="AB52" s="3">
         <v>5.5293339508853921E-3</v>
       </c>
-      <c r="AE52">
+      <c r="AF52">
         <v>7134.1</v>
       </c>
     </row>
-    <row r="53" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A53" s="1">
         <v>45824</v>
       </c>
@@ -3965,11 +3971,11 @@
       <c r="AB53" s="3">
         <v>5.5137481465377617E-3</v>
       </c>
-      <c r="AE53">
+      <c r="AF53">
         <v>7134.1</v>
       </c>
     </row>
-    <row r="54" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A54" s="1">
         <v>45825</v>
       </c>
@@ -4036,11 +4042,11 @@
       <c r="AB54" s="3">
         <v>6.0266003457495549E-3</v>
       </c>
-      <c r="AE54">
+      <c r="AF54">
         <v>7293.4</v>
       </c>
     </row>
-    <row r="55" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A55" s="1">
         <v>45826</v>
       </c>
@@ -4107,11 +4113,11 @@
       <c r="AB55" s="3">
         <v>6.1513707289073292E-3</v>
       </c>
-      <c r="AE55">
+      <c r="AF55">
         <v>7293.4</v>
       </c>
     </row>
-    <row r="56" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A56" s="1">
         <v>45827</v>
       </c>
@@ -4178,11 +4184,11 @@
       <c r="AB56" s="3">
         <v>6.5730272152609882E-3</v>
       </c>
-      <c r="AE56">
+      <c r="AF56">
         <v>7293.4</v>
       </c>
     </row>
-    <row r="57" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A57" s="1">
         <v>45828</v>
       </c>
@@ -4249,11 +4255,11 @@
       <c r="AB57" s="3">
         <v>6.5461243176998174E-3</v>
       </c>
-      <c r="AE57">
+      <c r="AF57">
         <v>7454.7749999999996</v>
       </c>
     </row>
-    <row r="58" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A58" s="1">
         <v>45831</v>
       </c>
@@ -4320,11 +4326,11 @@
       <c r="AB58" s="3">
         <v>6.8964796237906325E-3</v>
       </c>
-      <c r="AE58">
+      <c r="AF58">
         <v>7293.4</v>
       </c>
     </row>
-    <row r="59" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A59" s="1">
         <v>45832</v>
       </c>
@@ -4391,11 +4397,11 @@
       <c r="AB59" s="3">
         <v>6.8322889123812293E-3</v>
       </c>
-      <c r="AE59">
+      <c r="AF59">
         <v>7310.0249999999996</v>
       </c>
     </row>
-    <row r="60" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A60" s="1">
         <v>45833</v>
       </c>
@@ -4465,11 +4471,11 @@
       <c r="AB60" s="3">
         <v>7.3114624557207063E-3</v>
       </c>
-      <c r="AE60">
+      <c r="AF60">
         <v>7310.0249999999996</v>
       </c>
     </row>
-    <row r="61" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A61" s="1">
         <v>45834</v>
       </c>
@@ -4542,14 +4548,14 @@
       <c r="AB61" s="3">
         <v>7.3831807931911773E-3</v>
       </c>
-      <c r="AE61">
+      <c r="AF61">
         <v>7310.0249999999996</v>
       </c>
-      <c r="AF61">
+      <c r="AG61">
         <v>7645.5</v>
       </c>
     </row>
-    <row r="62" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A62" s="1">
         <v>45835</v>
       </c>
@@ -4625,14 +4631,14 @@
       <c r="AC62" s="3">
         <v>6.9015563871449468E-3</v>
       </c>
-      <c r="AE62">
+      <c r="AF62">
         <v>7191.625</v>
       </c>
-      <c r="AF62">
+      <c r="AG62">
         <v>7645.5</v>
       </c>
     </row>
-    <row r="63" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A63" s="1">
         <v>45838</v>
       </c>
@@ -4708,14 +4714,14 @@
       <c r="AC63" s="3">
         <v>6.7114990341783972E-3</v>
       </c>
-      <c r="AE63">
+      <c r="AF63">
         <v>6920.8600000000006</v>
       </c>
-      <c r="AF63">
+      <c r="AG63">
         <v>7541.375</v>
       </c>
     </row>
-    <row r="64" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A64" s="1">
         <v>45839</v>
       </c>
@@ -4791,14 +4797,14 @@
       <c r="AC64" s="3">
         <v>6.5613316585293475E-3</v>
       </c>
-      <c r="AE64">
+      <c r="AF64">
         <v>6920.8600000000006</v>
       </c>
-      <c r="AF64">
+      <c r="AG64">
         <v>7541.375</v>
       </c>
     </row>
-    <row r="65" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A65" s="1">
         <v>45840</v>
       </c>
@@ -4874,14 +4880,14 @@
       <c r="AC65" s="3">
         <v>6.3989718212730858E-3</v>
       </c>
-      <c r="AE65">
+      <c r="AF65">
         <v>6652.2350000000006</v>
       </c>
-      <c r="AF65">
+      <c r="AG65">
         <v>7454.7749999999996</v>
       </c>
     </row>
-    <row r="66" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A66" s="1">
         <v>45841</v>
       </c>
@@ -4957,14 +4963,14 @@
       <c r="AC66" s="3">
         <v>6.3636343699625432E-3</v>
       </c>
-      <c r="AE66">
+      <c r="AF66">
         <v>6652.2350000000006</v>
       </c>
-      <c r="AF66">
+      <c r="AG66">
         <v>7310.0249999999996</v>
       </c>
     </row>
-    <row r="67" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A67" s="1">
         <v>45842</v>
       </c>
@@ -5040,14 +5046,14 @@
       <c r="AC67" s="3">
         <v>6.1348798210633495E-3</v>
       </c>
-      <c r="AE67">
+      <c r="AF67">
         <v>6652.2350000000006</v>
       </c>
-      <c r="AF67">
+      <c r="AG67">
         <v>7310.0249999999996</v>
       </c>
     </row>
-    <row r="68" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A68" s="1">
         <v>45845</v>
       </c>
@@ -5123,14 +5129,14 @@
       <c r="AC68" s="3">
         <v>6.2122102969713912E-3</v>
       </c>
-      <c r="AE68">
+      <c r="AF68">
         <v>6652.2350000000006</v>
       </c>
-      <c r="AF68">
+      <c r="AG68">
         <v>7191.625</v>
       </c>
     </row>
-    <row r="69" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A69" s="1">
         <v>45846</v>
       </c>
@@ -5206,14 +5212,14 @@
       <c r="AC69" s="3">
         <v>6.0701656911555119E-3</v>
       </c>
-      <c r="AE69">
+      <c r="AF69">
         <v>6652.2350000000006</v>
       </c>
-      <c r="AF69">
+      <c r="AG69">
         <v>7134.1</v>
       </c>
     </row>
-    <row r="70" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A70" s="1">
         <v>45847</v>
       </c>
@@ -5289,14 +5295,14 @@
       <c r="AC70" s="3">
         <v>6.1561868942258549E-3</v>
       </c>
-      <c r="AE70">
+      <c r="AF70">
         <v>6652.2350000000006</v>
       </c>
-      <c r="AF70">
+      <c r="AG70">
         <v>7040.1</v>
       </c>
     </row>
-    <row r="71" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A71" s="1">
         <v>45848</v>
       </c>
@@ -5372,14 +5378,14 @@
       <c r="AC71" s="3">
         <v>6.1095515100836346E-3</v>
       </c>
-      <c r="AE71">
+      <c r="AF71">
         <v>6625.6100000000006</v>
       </c>
-      <c r="AF71">
+      <c r="AG71">
         <v>7040.1</v>
       </c>
     </row>
-    <row r="72" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A72" s="1">
         <v>45849</v>
       </c>
@@ -5455,14 +5461,14 @@
       <c r="AC72" s="3">
         <v>6.2630541465242846E-3</v>
       </c>
-      <c r="AE72">
+      <c r="AF72">
         <v>6625.6100000000006</v>
       </c>
-      <c r="AF72">
+      <c r="AG72">
         <v>7040.1</v>
       </c>
     </row>
-    <row r="73" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A73" s="1">
         <v>45852</v>
       </c>
@@ -5538,14 +5544,14 @@
       <c r="AC73" s="3">
         <v>6.296081099942898E-3</v>
       </c>
-      <c r="AE73">
+      <c r="AF73">
         <v>6584</v>
       </c>
-      <c r="AF73">
+      <c r="AG73">
         <v>6942</v>
       </c>
     </row>
-    <row r="74" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A74" s="1">
         <v>45853</v>
       </c>
@@ -5621,14 +5627,14 @@
       <c r="AC74" s="3">
         <v>6.2766721906584184E-3</v>
       </c>
-      <c r="AE74">
+      <c r="AF74">
         <v>6584</v>
       </c>
-      <c r="AF74">
+      <c r="AG74">
         <v>6942</v>
       </c>
     </row>
-    <row r="75" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A75" s="1">
         <v>45854</v>
       </c>
@@ -5704,14 +5710,14 @@
       <c r="AC75" s="3">
         <v>6.2261547849749412E-3</v>
       </c>
-      <c r="AE75">
+      <c r="AF75">
         <v>6584</v>
       </c>
-      <c r="AF75">
+      <c r="AG75">
         <v>7040.1</v>
       </c>
     </row>
-    <row r="76" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A76" s="1">
         <v>45855</v>
       </c>
@@ -5787,14 +5793,14 @@
       <c r="AC76" s="3">
         <v>6.1567737609288997E-3</v>
       </c>
-      <c r="AE76">
+      <c r="AF76">
         <v>6488.5</v>
       </c>
-      <c r="AF76">
+      <c r="AG76">
         <v>6942</v>
       </c>
     </row>
-    <row r="77" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A77" s="1">
         <v>45856</v>
       </c>
@@ -5870,14 +5876,14 @@
       <c r="AC77" s="3">
         <v>6.1820930048682148E-3</v>
       </c>
-      <c r="AE77">
+      <c r="AF77">
         <v>6488.5</v>
       </c>
-      <c r="AF77">
+      <c r="AG77">
         <v>6942</v>
       </c>
     </row>
-    <row r="78" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A78" s="1">
         <v>45859</v>
       </c>
@@ -5953,14 +5959,14 @@
       <c r="AC78" s="3">
         <v>6.1518086269915671E-3</v>
       </c>
-      <c r="AE78">
+      <c r="AF78">
         <v>6584</v>
       </c>
-      <c r="AF78">
+      <c r="AG78">
         <v>6852.875</v>
       </c>
     </row>
-    <row r="79" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A79" s="1">
         <v>45860</v>
       </c>
@@ -6036,14 +6042,14 @@
       <c r="AC79" s="3">
         <v>6.3018379566585252E-3</v>
       </c>
-      <c r="AE79">
+      <c r="AF79">
         <v>6584</v>
       </c>
-      <c r="AF79">
+      <c r="AG79">
         <v>6737.7350000000006</v>
       </c>
     </row>
-    <row r="80" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A80" s="1">
         <v>45862</v>
       </c>
@@ -6119,14 +6125,14 @@
       <c r="AC80" s="3">
         <v>6.4089382659734519E-3</v>
       </c>
-      <c r="AE80">
+      <c r="AF80">
         <v>6495.5</v>
       </c>
-      <c r="AF80">
+      <c r="AG80">
         <v>6737.7350000000006</v>
       </c>
     </row>
-    <row r="81" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A81" s="1">
         <v>45863</v>
       </c>
@@ -6202,14 +6208,14 @@
       <c r="AC81" s="3">
         <v>6.65637470883305E-3</v>
       </c>
-      <c r="AE81">
+      <c r="AF81">
         <v>6584</v>
       </c>
-      <c r="AF81">
+      <c r="AG81">
         <v>6737.7350000000006</v>
       </c>
     </row>
-    <row r="82" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A82" s="1">
         <v>45868</v>
       </c>
@@ -6285,14 +6291,14 @@
       <c r="AC82" s="3">
         <v>6.8492599598846092E-3</v>
       </c>
-      <c r="AE82">
+      <c r="AF82">
         <v>6584</v>
       </c>
-      <c r="AF82">
+      <c r="AG82">
         <v>6737.7350000000006</v>
       </c>
     </row>
-    <row r="83" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A83" s="1">
         <v>45869</v>
       </c>
@@ -6368,14 +6374,14 @@
       <c r="AC83" s="3">
         <v>7.0961278255910476E-3</v>
       </c>
-      <c r="AE83">
+      <c r="AF83">
         <v>6584</v>
       </c>
-      <c r="AF83">
+      <c r="AG83">
         <v>6737.7350000000006</v>
       </c>
     </row>
-    <row r="84" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A84" s="1">
         <v>45870</v>
       </c>
@@ -6451,14 +6457,14 @@
       <c r="AC84" s="3">
         <v>7.1629179134118613E-3</v>
       </c>
-      <c r="AE84">
+      <c r="AF84">
         <v>6584</v>
       </c>
-      <c r="AF84">
+      <c r="AG84">
         <v>6852.875</v>
       </c>
     </row>
-    <row r="85" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A85" s="1">
         <v>45873</v>
       </c>
@@ -6534,14 +6540,14 @@
       <c r="AC85" s="3">
         <v>7.4370585941120502E-3</v>
       </c>
-      <c r="AE85">
+      <c r="AF85">
         <v>6495.5</v>
       </c>
-      <c r="AF85">
+      <c r="AG85">
         <v>6737.7350000000006</v>
       </c>
     </row>
-    <row r="86" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A86" s="1">
         <v>45874</v>
       </c>
@@ -6617,14 +6623,14 @@
       <c r="AC86" s="3">
         <v>7.5128588293622992E-3</v>
       </c>
-      <c r="AE86">
+      <c r="AF86">
         <v>6495.5</v>
       </c>
-      <c r="AF86">
+      <c r="AG86">
         <v>6737.7350000000006</v>
       </c>
     </row>
-    <row r="87" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A87" s="1">
         <v>45876</v>
       </c>
@@ -6700,14 +6706,14 @@
       <c r="AC87" s="3">
         <v>7.6768085933003717E-3</v>
       </c>
-      <c r="AE87">
+      <c r="AF87">
         <v>6495.5</v>
       </c>
-      <c r="AF87">
+      <c r="AG87">
         <v>6808.45</v>
       </c>
     </row>
-    <row r="88" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A88" s="1">
         <v>45877</v>
       </c>
@@ -6783,14 +6789,14 @@
       <c r="AC88" s="3">
         <v>7.650062788466124E-3</v>
       </c>
-      <c r="AE88">
+      <c r="AF88">
         <v>6695.8249999999998</v>
       </c>
-      <c r="AF88">
+      <c r="AG88">
         <v>6808.45</v>
       </c>
     </row>
-    <row r="89" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A89" s="1">
         <v>45880</v>
       </c>
@@ -6866,14 +6872,14 @@
       <c r="AC89" s="3">
         <v>7.6395748759014188E-3</v>
       </c>
-      <c r="AE89">
+      <c r="AF89">
         <v>6695.8249999999998</v>
       </c>
-      <c r="AF89">
+      <c r="AG89">
         <v>6852.875</v>
       </c>
     </row>
-    <row r="90" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A90" s="1">
         <v>45881</v>
       </c>
@@ -6949,14 +6955,14 @@
       <c r="AC90" s="3">
         <v>7.6210483462443059E-3</v>
       </c>
-      <c r="AE90">
+      <c r="AF90">
         <v>6808.45</v>
       </c>
-      <c r="AF90">
+      <c r="AG90">
         <v>6942</v>
       </c>
     </row>
-    <row r="91" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A91" s="1">
         <v>45882</v>
       </c>
@@ -7032,14 +7038,14 @@
       <c r="AC91" s="3">
         <v>7.6563327619468121E-3</v>
       </c>
-      <c r="AE91">
+      <c r="AF91">
         <v>6695.8249999999998</v>
       </c>
-      <c r="AF91">
+      <c r="AG91">
         <v>6852.875</v>
       </c>
     </row>
-    <row r="92" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A92" s="1">
         <v>45883</v>
       </c>
@@ -7115,14 +7121,14 @@
       <c r="AC92" s="3">
         <v>7.6178839856940314E-3</v>
       </c>
-      <c r="AE92">
+      <c r="AF92">
         <v>6695.8249999999998</v>
       </c>
-      <c r="AF92">
+      <c r="AG92">
         <v>6808.45</v>
       </c>
     </row>
-    <row r="93" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A93" s="1">
         <v>45884</v>
       </c>
@@ -7198,14 +7204,14 @@
       <c r="AC93" s="3">
         <v>7.5902649535302515E-3</v>
       </c>
-      <c r="AE93">
-        <v>6808.45</v>
-      </c>
       <c r="AF93">
         <v>6808.45</v>
       </c>
-    </row>
-    <row r="94" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="AG93">
+        <v>6808.45</v>
+      </c>
+    </row>
+    <row r="94" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A94" s="1">
         <v>45887</v>
       </c>
@@ -7281,14 +7287,14 @@
       <c r="AC94" s="3">
         <v>7.5847829576447369E-3</v>
       </c>
-      <c r="AE94">
+      <c r="AF94">
         <v>6695.8249999999998</v>
       </c>
-      <c r="AF94">
+      <c r="AG94">
         <v>6737.4349999999995</v>
       </c>
     </row>
-    <row r="95" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A95" s="1">
         <v>45888</v>
       </c>
@@ -7364,14 +7370,14 @@
       <c r="AC95" s="3">
         <v>7.6158543155400438E-3</v>
       </c>
-      <c r="AE95">
+      <c r="AF95">
         <v>6695.8249999999998</v>
       </c>
-      <c r="AF95">
+      <c r="AG95">
         <v>6652.2350000000006</v>
       </c>
     </row>
-    <row r="96" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A96" s="1">
         <v>45889</v>
       </c>
@@ -7447,14 +7453,14 @@
       <c r="AC96" s="3">
         <v>7.5705418629686072E-3</v>
       </c>
-      <c r="AE96">
+      <c r="AF96">
         <v>6695.8249999999998</v>
       </c>
-      <c r="AF96">
+      <c r="AG96">
         <v>6652.2350000000006</v>
       </c>
     </row>
-    <row r="97" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A97" s="1">
         <v>45890</v>
       </c>
@@ -7530,14 +7536,14 @@
       <c r="AC97" s="3">
         <v>7.5607864490240019E-3</v>
       </c>
-      <c r="AE97">
+      <c r="AF97">
         <v>6695.8249999999998</v>
       </c>
-      <c r="AF97">
+      <c r="AG97">
         <v>6652.2350000000006</v>
       </c>
     </row>
-    <row r="98" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A98" s="1">
         <v>45891</v>
       </c>
@@ -7613,14 +7619,14 @@
       <c r="AC98" s="3">
         <v>7.8211208564440884E-3</v>
       </c>
-      <c r="AE98">
+      <c r="AF98">
         <v>6643.1749999999993</v>
       </c>
-      <c r="AF98">
+      <c r="AG98">
         <v>6652.2350000000006</v>
       </c>
     </row>
-    <row r="99" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A99" s="1">
         <v>45894</v>
       </c>
@@ -7696,14 +7702,14 @@
       <c r="AC99" s="3">
         <v>7.8373507051832693E-3</v>
       </c>
-      <c r="AE99">
+      <c r="AF99">
         <v>6643.1749999999993</v>
       </c>
-      <c r="AF99">
+      <c r="AG99">
         <v>6652.2350000000006</v>
       </c>
     </row>
-    <row r="100" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A100" s="1">
         <v>45895</v>
       </c>
@@ -7779,14 +7785,14 @@
       <c r="AC100" s="3">
         <v>7.8595008480541722E-3</v>
       </c>
-      <c r="AE100">
+      <c r="AF100">
         <v>6478.2</v>
       </c>
-      <c r="AF100">
+      <c r="AG100">
         <v>6611.125</v>
       </c>
     </row>
-    <row r="101" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A101" s="1">
         <v>45896</v>
       </c>
@@ -7862,14 +7868,14 @@
       <c r="AC101" s="3">
         <v>7.6855037848890476E-3</v>
       </c>
-      <c r="AE101">
+      <c r="AF101">
         <v>6643.1749999999993</v>
       </c>
-      <c r="AF101">
+      <c r="AG101">
         <v>6625.6100000000006</v>
       </c>
     </row>
-    <row r="102" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A102" s="1">
         <v>45897</v>
       </c>
@@ -7945,14 +7951,14 @@
       <c r="AC102" s="3">
         <v>7.6304611781258767E-3</v>
       </c>
-      <c r="AE102">
+      <c r="AF102">
         <v>6808.45</v>
       </c>
-      <c r="AF102">
+      <c r="AG102">
         <v>6737.4349999999995</v>
       </c>
     </row>
-    <row r="103" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A103" s="1">
         <v>45898</v>
       </c>
@@ -8028,14 +8034,14 @@
       <c r="AC103" s="3">
         <v>7.6544659281167346E-3</v>
       </c>
-      <c r="AE103">
+      <c r="AF103">
         <v>6902.375</v>
       </c>
-      <c r="AF103">
+      <c r="AG103">
         <v>6737.4349999999995</v>
       </c>
     </row>
-    <row r="104" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A104" s="1">
         <v>45901</v>
       </c>
@@ -8111,14 +8117,14 @@
       <c r="AC104" s="3">
         <v>7.906752994373812E-3</v>
       </c>
-      <c r="AE104">
+      <c r="AF104">
         <v>6902.375</v>
       </c>
-      <c r="AF104">
+      <c r="AG104">
         <v>6737.4349999999995</v>
       </c>
     </row>
-    <row r="105" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A105" s="1">
         <v>45902</v>
       </c>
@@ -8194,14 +8200,14 @@
       <c r="AC105" s="3">
         <v>7.7477576021668434E-3</v>
       </c>
-      <c r="AE105">
+      <c r="AF105">
         <v>6902.375</v>
       </c>
-      <c r="AF105">
+      <c r="AG105">
         <v>6737.4349999999995</v>
       </c>
     </row>
-    <row r="106" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A106" s="1">
         <v>45903</v>
       </c>
@@ -8277,14 +8283,14 @@
       <c r="AC106" s="3">
         <v>7.6626613838614004E-3</v>
       </c>
-      <c r="AE106">
+      <c r="AF106">
         <v>7008.5</v>
       </c>
-      <c r="AF106">
+      <c r="AG106">
         <v>6808.45</v>
       </c>
     </row>
-    <row r="107" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A107" s="1">
         <v>45904</v>
       </c>
@@ -8360,14 +8366,14 @@
       <c r="AC107" s="3">
         <v>7.8691741373417296E-3</v>
       </c>
-      <c r="AE107">
+      <c r="AF107">
         <v>7008.5</v>
       </c>
-      <c r="AF107">
+      <c r="AG107">
         <v>6808.45</v>
       </c>
     </row>
-    <row r="108" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A108" s="1">
         <v>45905</v>
       </c>
@@ -8443,14 +8449,14 @@
       <c r="AC108" s="3">
         <v>7.6774175557350281E-3</v>
       </c>
-      <c r="AE108">
+      <c r="AF108">
         <v>7066.25</v>
       </c>
-      <c r="AF108">
+      <c r="AG108">
         <v>6852.875</v>
       </c>
     </row>
-    <row r="109" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A109" s="1">
         <v>45908</v>
       </c>
@@ -8526,14 +8532,14 @@
       <c r="AC109" s="3">
         <v>7.6181575062390849E-3</v>
       </c>
-      <c r="AE109">
+      <c r="AF109">
         <v>7317.875</v>
       </c>
-      <c r="AF109">
+      <c r="AG109">
         <v>6942</v>
       </c>
     </row>
-    <row r="110" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A110" s="1">
         <v>45909</v>
       </c>
@@ -8609,14 +8615,14 @@
       <c r="AC110" s="3">
         <v>7.6251956493885685E-3</v>
       </c>
-      <c r="AE110">
+      <c r="AF110">
         <v>7625.625</v>
       </c>
-      <c r="AF110">
+      <c r="AG110">
         <v>6942</v>
       </c>
     </row>
-    <row r="111" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A111" s="1">
         <v>45910</v>
       </c>
@@ -8692,14 +8698,14 @@
       <c r="AC111" s="3">
         <v>7.3290807714569061E-3</v>
       </c>
-      <c r="AE111">
+      <c r="AF111">
         <v>7625.625</v>
       </c>
-      <c r="AF111">
+      <c r="AG111">
         <v>6991.5</v>
       </c>
     </row>
-    <row r="112" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A112" s="1">
         <v>45911</v>
       </c>
@@ -8775,14 +8781,14 @@
       <c r="AC112" s="3">
         <v>7.3665415883067114E-3</v>
       </c>
-      <c r="AE112">
+      <c r="AF112">
         <v>7876</v>
       </c>
-      <c r="AF112">
+      <c r="AG112">
         <v>7008.5</v>
       </c>
     </row>
-    <row r="113" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A113" s="1">
         <v>45912</v>
       </c>
@@ -8858,14 +8864,14 @@
       <c r="AC113" s="3">
         <v>7.305880642223395E-3</v>
       </c>
-      <c r="AE113">
+      <c r="AF113">
         <v>8153.3</v>
       </c>
-      <c r="AF113">
+      <c r="AG113">
         <v>7008.5</v>
       </c>
     </row>
-    <row r="114" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A114" s="1">
         <v>45915</v>
       </c>
@@ -8941,14 +8947,14 @@
       <c r="AC114" s="3">
         <v>7.1861703480900502E-3</v>
       </c>
-      <c r="AE114">
+      <c r="AF114">
         <v>8360.1</v>
       </c>
-      <c r="AF114">
+      <c r="AG114">
         <v>7008.5</v>
       </c>
     </row>
-    <row r="115" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A115" s="1">
         <v>45916</v>
       </c>
@@ -9024,14 +9030,14 @@
       <c r="AC115" s="3">
         <v>7.2765412039985152E-3</v>
       </c>
-      <c r="AE115">
+      <c r="AF115">
         <v>8451.2000000000007</v>
       </c>
-      <c r="AF115">
+      <c r="AG115">
         <v>7066.25</v>
       </c>
     </row>
-    <row r="116" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A116" s="1">
         <v>45917</v>
       </c>
@@ -9107,14 +9113,14 @@
       <c r="AC116" s="3">
         <v>7.0359316059136834E-3</v>
       </c>
-      <c r="AE116">
+      <c r="AF116">
         <v>8451.2000000000007</v>
       </c>
-      <c r="AF116">
+      <c r="AG116">
         <v>7008.5</v>
       </c>
     </row>
-    <row r="117" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A117" s="1">
         <v>45918</v>
       </c>
@@ -9190,14 +9196,14 @@
       <c r="AC117" s="3">
         <v>7.0246497446100733E-3</v>
       </c>
-      <c r="AE117">
+      <c r="AF117">
         <v>8451.2000000000007</v>
       </c>
-      <c r="AF117">
+      <c r="AG117">
         <v>7008.5</v>
       </c>
     </row>
-    <row r="118" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A118" s="1">
         <v>45919</v>
       </c>
@@ -9273,14 +9279,14 @@
       <c r="AC118" s="3">
         <v>6.8122508229457755E-3</v>
       </c>
-      <c r="AE118">
+      <c r="AF118">
         <v>8451.2000000000007</v>
       </c>
-      <c r="AF118">
+      <c r="AG118">
         <v>7066.25</v>
       </c>
     </row>
-    <row r="119" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A119" s="1">
         <v>45922</v>
       </c>
@@ -9356,14 +9362,14 @@
       <c r="AC119" s="3">
         <v>6.8681220427587357E-3</v>
       </c>
-      <c r="AE119">
+      <c r="AF119">
         <v>8360.1</v>
       </c>
-      <c r="AF119">
+      <c r="AG119">
         <v>7008.5</v>
       </c>
     </row>
-    <row r="120" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A120" s="1">
         <v>45923</v>
       </c>
@@ -9439,14 +9445,14 @@
       <c r="AC120" s="3">
         <v>6.5329129905547069E-3</v>
       </c>
-      <c r="AE120">
+      <c r="AF120">
         <v>8360.1</v>
       </c>
-      <c r="AF120">
+      <c r="AG120">
         <v>7066.25</v>
       </c>
     </row>
-    <row r="121" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A121" s="1">
         <v>45924</v>
       </c>
@@ -9522,14 +9528,14 @@
       <c r="AC121" s="3">
         <v>6.4413467172099248E-3</v>
       </c>
-      <c r="AE121">
+      <c r="AF121">
         <v>8360.1</v>
       </c>
-      <c r="AF121">
+      <c r="AG121">
         <v>7008.5</v>
       </c>
     </row>
-    <row r="122" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A122" s="1">
         <v>45925</v>
       </c>
@@ -9605,14 +9611,14 @@
       <c r="AC122" s="3">
         <v>6.4648808280828472E-3</v>
       </c>
-      <c r="AE122">
+      <c r="AF122">
         <v>8451.2000000000007</v>
       </c>
-      <c r="AF122">
+      <c r="AG122">
         <v>7066.25</v>
       </c>
     </row>
-    <row r="123" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A123" s="1">
         <v>45926</v>
       </c>
@@ -9688,14 +9694,14 @@
       <c r="AC123" s="3">
         <v>6.5250494429455333E-3</v>
       </c>
-      <c r="AE123">
+      <c r="AF123">
         <v>8451.2000000000007</v>
       </c>
-      <c r="AF123">
+      <c r="AG123">
         <v>7210.75</v>
       </c>
     </row>
-    <row r="124" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A124" s="1">
         <v>45929</v>
       </c>
@@ -9771,14 +9777,14 @@
       <c r="AC124" s="3">
         <v>6.6263282636312443E-3</v>
       </c>
-      <c r="AE124">
+      <c r="AF124">
         <v>8451.2000000000007</v>
       </c>
-      <c r="AF124">
+      <c r="AG124">
         <v>7066.25</v>
       </c>
     </row>
-    <row r="125" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A125" s="1">
         <v>45930</v>
       </c>
@@ -9854,14 +9860,14 @@
       <c r="AC125" s="3">
         <v>6.6331936424698333E-3</v>
       </c>
-      <c r="AE125">
+      <c r="AF125">
         <v>8522.9</v>
       </c>
-      <c r="AF125">
+      <c r="AG125">
         <v>7210.75</v>
       </c>
     </row>
-    <row r="126" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A126" s="1">
         <v>45931</v>
       </c>
@@ -9937,14 +9943,14 @@
       <c r="AC126" s="3">
         <v>6.4850387316871634E-3</v>
       </c>
-      <c r="AE126">
+      <c r="AF126">
         <v>8652.85</v>
       </c>
-      <c r="AF126">
+      <c r="AG126">
         <v>7417.125</v>
       </c>
     </row>
-    <row r="127" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A127" s="1">
         <v>45932</v>
       </c>
@@ -10020,14 +10026,14 @@
       <c r="AC127" s="3">
         <v>6.485880362181908E-3</v>
       </c>
-      <c r="AE127">
+      <c r="AF127">
         <v>8522.9</v>
       </c>
-      <c r="AF127">
+      <c r="AG127">
         <v>7210.75</v>
       </c>
     </row>
-    <row r="128" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A128" s="1">
         <v>45933</v>
       </c>
@@ -10103,14 +10109,14 @@
       <c r="AC128" s="3">
         <v>6.2968881602275262E-3</v>
       </c>
-      <c r="AE128">
+      <c r="AF128">
         <v>8652.85</v>
       </c>
-      <c r="AF128">
+      <c r="AG128">
         <v>7417.125</v>
       </c>
     </row>
-    <row r="129" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A129" s="1">
         <v>45936</v>
       </c>
@@ -10186,14 +10192,14 @@
       <c r="AC129" s="3">
         <v>6.3064164487823572E-3</v>
       </c>
-      <c r="AE129">
+      <c r="AF129">
         <v>8652.85</v>
       </c>
-      <c r="AF129">
+      <c r="AG129">
         <v>7525.25</v>
       </c>
     </row>
-    <row r="130" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A130" s="1">
         <v>45937</v>
       </c>
@@ -10269,14 +10275,14 @@
       <c r="AC130" s="3">
         <v>6.0460838528188735E-3</v>
       </c>
-      <c r="AE130">
+      <c r="AF130">
         <v>8652.85</v>
       </c>
-      <c r="AF130">
+      <c r="AG130">
         <v>7525.25</v>
       </c>
     </row>
-    <row r="131" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A131" s="1">
         <v>45939</v>
       </c>
@@ -10352,14 +10358,14 @@
       <c r="AC131" s="3">
         <v>6.0568006152864505E-3</v>
       </c>
-      <c r="AE131">
+      <c r="AF131">
         <v>8522.9</v>
       </c>
-      <c r="AF131">
+      <c r="AG131">
         <v>7525.25</v>
       </c>
     </row>
-    <row r="132" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A132" s="1">
         <v>45940</v>
       </c>
@@ -10435,14 +10441,14 @@
       <c r="AC132" s="3">
         <v>5.907494519511251E-3</v>
       </c>
-      <c r="AE132">
+      <c r="AF132">
         <v>8522.9</v>
       </c>
-      <c r="AF132">
+      <c r="AG132">
         <v>7525.25</v>
       </c>
     </row>
-    <row r="133" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A133" s="1">
         <v>45943</v>
       </c>
@@ -10518,14 +10524,14 @@
       <c r="AC133" s="3">
         <v>5.71389081200749E-3</v>
       </c>
-      <c r="AE133">
+      <c r="AF133">
         <v>8451.2000000000007</v>
       </c>
-      <c r="AF133">
+      <c r="AG133">
         <v>7525.25</v>
       </c>
     </row>
-    <row r="134" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A134" s="1">
         <v>45944</v>
       </c>
@@ -10601,14 +10607,14 @@
       <c r="AC134" s="3">
         <v>5.6807464262441064E-3</v>
       </c>
-      <c r="AE134">
+      <c r="AF134">
         <v>8522.9</v>
       </c>
-      <c r="AF134">
+      <c r="AG134">
         <v>7619.625</v>
       </c>
     </row>
-    <row r="135" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A135" s="1">
         <v>45945</v>
       </c>
@@ -10684,14 +10690,14 @@
       <c r="AC135" s="3">
         <v>5.7072872717359906E-3</v>
       </c>
-      <c r="AE135">
+      <c r="AF135">
         <v>8522.9</v>
       </c>
-      <c r="AF135">
+      <c r="AG135">
         <v>7618.625</v>
       </c>
     </row>
-    <row r="136" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A136" s="1">
         <v>45946</v>
       </c>
@@ -10767,14 +10773,14 @@
       <c r="AC136" s="3">
         <v>5.6856319139418467E-3</v>
       </c>
-      <c r="AE136">
+      <c r="AF136">
         <v>8451.2000000000007</v>
       </c>
-      <c r="AF136">
+      <c r="AG136">
         <v>7720</v>
       </c>
     </row>
-    <row r="137" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A137" s="1">
         <v>45947</v>
       </c>
@@ -10850,14 +10856,14 @@
       <c r="AC137" s="3">
         <v>5.6815755224319479E-3</v>
       </c>
-      <c r="AE137">
+      <c r="AF137">
         <v>8397.2999999999993</v>
       </c>
-      <c r="AF137">
+      <c r="AG137">
         <v>7720</v>
       </c>
     </row>
-    <row r="138" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A138" s="1">
         <v>45950</v>
       </c>
@@ -10933,14 +10939,14 @@
       <c r="AC138" s="3">
         <v>5.602851734553967E-3</v>
       </c>
-      <c r="AE138">
+      <c r="AF138">
         <v>8250.4</v>
       </c>
-      <c r="AF138">
+      <c r="AG138">
         <v>7720</v>
       </c>
     </row>
-    <row r="139" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A139" s="1">
         <v>45951</v>
       </c>
@@ -11016,14 +11022,14 @@
       <c r="AC139" s="3">
         <v>5.4549239859485177E-3</v>
       </c>
-      <c r="AE139">
+      <c r="AF139">
         <v>8131</v>
       </c>
-      <c r="AF139">
+      <c r="AG139">
         <v>7720</v>
       </c>
     </row>
-    <row r="140" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A140" s="1">
         <v>45952</v>
       </c>
@@ -11099,14 +11105,14 @@
       <c r="AC140" s="3">
         <v>5.3296575431893813E-3</v>
       </c>
-      <c r="AE140">
+      <c r="AF140">
         <v>7915.1</v>
       </c>
-      <c r="AF140">
+      <c r="AG140">
         <v>7720</v>
       </c>
     </row>
-    <row r="141" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A141" s="1">
         <v>45953</v>
       </c>
@@ -11182,14 +11188,14 @@
       <c r="AC141" s="3">
         <v>5.1538047758677335E-3</v>
       </c>
-      <c r="AE141">
+      <c r="AF141">
         <v>7915.1</v>
       </c>
-      <c r="AF141">
+      <c r="AG141">
         <v>7720</v>
       </c>
     </row>
-    <row r="142" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A142" s="1">
         <v>45954</v>
       </c>
@@ -11265,14 +11271,14 @@
       <c r="AC142" s="3">
         <v>4.8817614733585851E-3</v>
       </c>
-      <c r="AE142">
+      <c r="AF142">
         <v>7915.1</v>
       </c>
-      <c r="AF142">
+      <c r="AG142">
         <v>7876</v>
       </c>
     </row>
-    <row r="143" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A143" s="1">
         <v>45957</v>
       </c>
@@ -11348,14 +11354,14 @@
       <c r="AC143" s="3">
         <v>4.7666167604414724E-3</v>
       </c>
-      <c r="AE143">
+      <c r="AF143">
         <v>7744.5</v>
       </c>
-      <c r="AF143">
+      <c r="AG143">
         <v>7900.5</v>
       </c>
     </row>
-    <row r="144" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A144" s="1">
         <v>45958</v>
       </c>
@@ -11431,14 +11437,14 @@
       <c r="AC144" s="3">
         <v>4.8304182322860085E-3</v>
       </c>
-      <c r="AE144">
+      <c r="AF144">
         <v>7598</v>
       </c>
-      <c r="AF144">
+      <c r="AG144">
         <v>7900.5</v>
       </c>
     </row>
-    <row r="145" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A145" s="1">
         <v>45959</v>
       </c>
@@ -11514,14 +11520,14 @@
       <c r="AC145" s="3">
         <v>4.5532108676766348E-3</v>
       </c>
-      <c r="AE145">
+      <c r="AF145">
         <v>7598</v>
       </c>
-      <c r="AF145">
+      <c r="AG145">
         <v>8071.1</v>
       </c>
     </row>
-    <row r="146" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A146" s="1">
         <v>45960</v>
       </c>
@@ -11597,14 +11603,14 @@
       <c r="AC146" s="3">
         <v>4.5960276958907382E-3</v>
       </c>
-      <c r="AE146">
+      <c r="AF146">
         <v>7598</v>
       </c>
-      <c r="AF146">
+      <c r="AG146">
         <v>8071.1</v>
       </c>
     </row>
-    <row r="147" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A147" s="1">
         <v>45961</v>
       </c>
@@ -11680,14 +11686,14 @@
       <c r="AC147" s="3">
         <v>4.4357336484116289E-3</v>
       </c>
-      <c r="AE147">
+      <c r="AF147">
         <v>7598</v>
       </c>
-      <c r="AF147">
+      <c r="AG147">
         <v>8071.1</v>
       </c>
     </row>
-    <row r="148" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A148" s="1">
         <v>45964</v>
       </c>
@@ -11763,14 +11769,14 @@
       <c r="AC148" s="3">
         <v>4.4956658033175334E-3</v>
       </c>
-      <c r="AE148">
+      <c r="AF148">
         <v>7598</v>
       </c>
-      <c r="AF148">
+      <c r="AG148">
         <v>8131</v>
       </c>
     </row>
-    <row r="149" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A149" s="1">
         <v>45965</v>
       </c>
@@ -11846,14 +11852,14 @@
       <c r="AC149" s="3">
         <v>4.5015573065474842E-3</v>
       </c>
-      <c r="AE149">
+      <c r="AF149">
         <v>7744.5</v>
       </c>
-      <c r="AF149">
+      <c r="AG149">
         <v>8131</v>
       </c>
     </row>
-    <row r="150" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A150" s="1">
         <v>45966</v>
       </c>
@@ -11929,14 +11935,14 @@
       <c r="AC150" s="3">
         <v>4.4300138464987539E-3</v>
       </c>
-      <c r="AE150">
+      <c r="AF150">
         <v>7744.5</v>
       </c>
-      <c r="AF150">
+      <c r="AG150">
         <v>8131</v>
       </c>
     </row>
-    <row r="151" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A151" s="1">
         <v>45967</v>
       </c>
@@ -12012,14 +12018,14 @@
       <c r="AC151" s="3">
         <v>4.421629038976682E-3</v>
       </c>
-      <c r="AE151">
+      <c r="AF151">
         <v>7744.5</v>
       </c>
-      <c r="AF151">
+      <c r="AG151">
         <v>8131</v>
       </c>
     </row>
-    <row r="152" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A152" s="1">
         <v>45968</v>
       </c>
@@ -12095,14 +12101,14 @@
       <c r="AC152" s="3">
         <v>4.5283004355598346E-3</v>
       </c>
-      <c r="AE152">
+      <c r="AF152">
         <v>7744.5</v>
       </c>
-      <c r="AF152">
+      <c r="AG152">
         <v>8213.2000000000007</v>
       </c>
     </row>
-    <row r="153" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A153" s="1">
         <v>45971</v>
       </c>
@@ -12178,14 +12184,14 @@
       <c r="AC153" s="3">
         <v>4.5565909138471899E-3</v>
       </c>
-      <c r="AE153">
+      <c r="AF153">
         <v>7629.5</v>
       </c>
-      <c r="AF153">
+      <c r="AG153">
         <v>8213.2000000000007</v>
       </c>
     </row>
-    <row r="154" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A154" s="1">
         <v>45972</v>
       </c>
@@ -12261,14 +12267,14 @@
       <c r="AC154" s="3">
         <v>4.5748452387624743E-3</v>
       </c>
-      <c r="AE154">
+      <c r="AF154">
         <v>7946.6</v>
       </c>
-      <c r="AF154">
+      <c r="AG154">
         <v>8318.7999999999993</v>
       </c>
     </row>
-    <row r="155" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A155" s="1">
         <v>45973</v>
       </c>
@@ -12344,14 +12350,14 @@
       <c r="AC155" s="3">
         <v>4.5379896079971987E-3</v>
       </c>
-      <c r="AE155">
+      <c r="AF155">
         <v>7946.6</v>
       </c>
-      <c r="AF155">
+      <c r="AG155">
         <v>8397.2999999999993</v>
       </c>
     </row>
-    <row r="156" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A156" s="1">
         <v>45974</v>
       </c>
@@ -12427,14 +12433,14 @@
       <c r="AC156" s="3">
         <v>4.5400915790872985E-3</v>
       </c>
-      <c r="AE156">
+      <c r="AF156">
         <v>7629.5</v>
       </c>
-      <c r="AF156">
+      <c r="AG156">
         <v>8397.2999999999993</v>
       </c>
     </row>
-    <row r="157" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A157" s="1">
         <v>45975</v>
       </c>
@@ -12510,14 +12516,14 @@
       <c r="AC157" s="3">
         <v>4.5653903867253131E-3</v>
       </c>
-      <c r="AE157">
+      <c r="AF157">
         <v>7946.6</v>
       </c>
-      <c r="AF157">
+      <c r="AG157">
         <v>8397.2999999999993</v>
       </c>
     </row>
-    <row r="158" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A158" s="1">
         <v>45978</v>
       </c>
@@ -12593,14 +12599,14 @@
       <c r="AC158" s="3">
         <v>4.3407969238762742E-3</v>
       </c>
-      <c r="AE158">
+      <c r="AF158">
         <v>7946.6</v>
       </c>
-      <c r="AF158">
+      <c r="AG158">
         <v>8451.2000000000007</v>
       </c>
     </row>
-    <row r="159" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A159" s="1">
         <v>45979</v>
       </c>
@@ -12676,14 +12682,14 @@
       <c r="AC159" s="3">
         <v>4.3001818628709519E-3</v>
       </c>
-      <c r="AE159">
+      <c r="AF159">
         <v>7946.6</v>
       </c>
-      <c r="AF159">
+      <c r="AG159">
         <v>8451.2000000000007</v>
       </c>
     </row>
-    <row r="160" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A160" s="1">
         <v>45980</v>
       </c>
@@ -12759,14 +12765,14 @@
       <c r="AC160" s="3">
         <v>4.2966788763034612E-3</v>
       </c>
-      <c r="AE160">
+      <c r="AF160">
         <v>8236.6</v>
       </c>
-      <c r="AF160">
+      <c r="AG160">
         <v>8522.9</v>
       </c>
     </row>
-    <row r="161" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A161" s="1">
         <v>45981</v>
       </c>
@@ -12842,14 +12848,14 @@
       <c r="AC161" s="3">
         <v>4.3542587530315032E-3</v>
       </c>
-      <c r="AE161">
+      <c r="AF161">
         <v>8429</v>
       </c>
-      <c r="AF161">
+      <c r="AG161">
         <v>8482.9</v>
       </c>
     </row>
-    <row r="162" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A162" s="1">
         <v>45982</v>
       </c>
@@ -12925,14 +12931,14 @@
       <c r="AC162" s="3">
         <v>4.3763390345263531E-3</v>
       </c>
-      <c r="AE162">
+      <c r="AF162">
         <v>8429</v>
       </c>
-      <c r="AF162">
+      <c r="AG162">
         <v>8482.9</v>
       </c>
     </row>
-    <row r="163" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A163" s="1">
         <v>45985</v>
       </c>
@@ -13008,14 +13014,14 @@
       <c r="AC163" s="3">
         <v>4.3427772796820144E-3</v>
       </c>
-      <c r="AE163">
+      <c r="AF163">
         <v>8690</v>
       </c>
-      <c r="AF163">
+      <c r="AG163">
         <v>8482.9</v>
       </c>
     </row>
-    <row r="164" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A164" s="1">
         <v>45986</v>
       </c>
@@ -13091,14 +13097,14 @@
       <c r="AC164" s="3">
         <v>4.1249634122205352E-3</v>
       </c>
-      <c r="AE164">
+      <c r="AF164">
         <v>8690</v>
       </c>
-      <c r="AF164">
+      <c r="AG164">
         <v>8542</v>
       </c>
     </row>
-    <row r="165" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A165" s="1">
         <v>45987</v>
       </c>
@@ -13174,14 +13180,14 @@
       <c r="AC165" s="3">
         <v>4.1636261628320813E-3</v>
       </c>
-      <c r="AE165">
+      <c r="AF165">
         <v>8690</v>
       </c>
-      <c r="AF165">
+      <c r="AG165">
         <v>8542</v>
       </c>
     </row>
-    <row r="166" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A166" s="1">
         <v>45988</v>
       </c>
@@ -13257,14 +13263,14 @@
       <c r="AC166" s="3">
         <v>4.0666730297134945E-3</v>
       </c>
-      <c r="AE166">
+      <c r="AF166">
         <v>9725.5</v>
       </c>
-      <c r="AF166">
+      <c r="AG166">
         <v>8542</v>
       </c>
     </row>
-    <row r="167" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A167" s="1">
         <v>45989</v>
       </c>
@@ -13340,14 +13346,14 @@
       <c r="AC167" s="3">
         <v>3.8763956069660563E-3</v>
       </c>
-      <c r="AE167">
+      <c r="AF167">
         <v>10866.15</v>
       </c>
-      <c r="AF167">
+      <c r="AG167">
         <v>8542</v>
       </c>
     </row>
-    <row r="168" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A168" s="1">
         <v>45992</v>
       </c>
@@ -13423,14 +13429,14 @@
       <c r="AC168" s="3">
         <v>3.7804822853696927E-3</v>
       </c>
-      <c r="AE168">
+      <c r="AF168">
         <v>11249.65</v>
       </c>
-      <c r="AF168">
+      <c r="AG168">
         <v>8652.85</v>
       </c>
     </row>
-    <row r="169" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A169" s="1">
         <v>45993</v>
       </c>
@@ -13506,14 +13512,14 @@
       <c r="AC169" s="3">
         <v>3.7479075176312269E-3</v>
       </c>
-      <c r="AE169">
+      <c r="AF169">
         <v>11249.65</v>
       </c>
-      <c r="AF169">
+      <c r="AG169">
         <v>8652.85</v>
       </c>
     </row>
-    <row r="170" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A170" s="1">
         <v>45994</v>
       </c>
@@ -13589,14 +13595,14 @@
       <c r="AC170" s="3">
         <v>3.730920995648505E-3</v>
       </c>
-      <c r="AE170">
+      <c r="AF170">
         <v>11347.4</v>
       </c>
-      <c r="AF170">
+      <c r="AG170">
         <v>8652.85</v>
       </c>
     </row>
-    <row r="171" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A171" s="1">
         <v>45995</v>
       </c>
@@ -13672,14 +13678,14 @@
       <c r="AC171" s="3">
         <v>3.7242186307130756E-3</v>
       </c>
-      <c r="AE171">
+      <c r="AF171">
         <v>12178.75</v>
       </c>
-      <c r="AF171">
+      <c r="AG171">
         <v>8730</v>
       </c>
     </row>
-    <row r="172" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A172" s="1">
         <v>45996</v>
       </c>
@@ -13755,14 +13761,14 @@
       <c r="AC172" s="3">
         <v>3.5995697674783131E-3</v>
       </c>
-      <c r="AE172">
+      <c r="AF172">
         <v>12539.9</v>
       </c>
-      <c r="AF172">
+      <c r="AG172">
         <v>8730</v>
       </c>
     </row>
-    <row r="173" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A173" s="1">
         <v>46001</v>
       </c>
@@ -13838,14 +13844,14 @@
       <c r="AC173" s="3">
         <v>3.6693636658061764E-3</v>
       </c>
-      <c r="AE173">
+      <c r="AF173">
         <v>14971.65</v>
       </c>
-      <c r="AF173">
+      <c r="AG173">
         <v>8730</v>
       </c>
     </row>
-    <row r="174" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A174" s="1">
         <v>46002</v>
       </c>
@@ -13921,14 +13927,14 @@
       <c r="AC174" s="3">
         <v>3.7841093757449225E-3</v>
       </c>
-      <c r="AE174">
+      <c r="AF174">
         <v>14971.65</v>
       </c>
-      <c r="AF174">
+      <c r="AG174">
         <v>8730</v>
       </c>
     </row>
-    <row r="175" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A175" s="1">
         <v>46003</v>
       </c>
@@ -14004,14 +14010,14 @@
       <c r="AC175" s="3">
         <v>3.7209129002054196E-3</v>
       </c>
-      <c r="AE175">
+      <c r="AF175">
         <v>12539.9</v>
       </c>
-      <c r="AF175">
+      <c r="AG175">
         <v>8542</v>
       </c>
     </row>
-    <row r="176" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A176" s="1">
         <v>46006</v>
       </c>
@@ -14087,14 +14093,14 @@
       <c r="AC176" s="3">
         <v>3.7413958832044755E-3</v>
       </c>
-      <c r="AE176">
+      <c r="AF176">
         <v>16880.400000000001</v>
       </c>
-      <c r="AF176">
+      <c r="AG176">
         <v>8730</v>
       </c>
     </row>
-    <row r="177" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A177" s="1">
         <v>46007</v>
       </c>
@@ -14170,14 +14176,14 @@
       <c r="AC177" s="3">
         <v>3.7384982021080129E-3</v>
       </c>
-      <c r="AE177">
+      <c r="AF177">
         <v>16880.400000000001</v>
       </c>
-      <c r="AF177">
+      <c r="AG177">
         <v>8885.9</v>
       </c>
     </row>
-    <row r="178" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A178" s="1">
         <v>46008</v>
       </c>
@@ -14253,14 +14259,14 @@
       <c r="AC178" s="3">
         <v>3.6975351505111036E-3</v>
       </c>
-      <c r="AE178">
+      <c r="AF178">
         <v>16880.400000000001</v>
       </c>
-      <c r="AF178">
+      <c r="AG178">
         <v>9733.4</v>
       </c>
     </row>
-    <row r="179" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A179" s="1">
         <v>46009</v>
       </c>
@@ -14336,14 +14342,14 @@
       <c r="AC179" s="3">
         <v>3.6442491903668811E-3</v>
       </c>
-      <c r="AE179">
+      <c r="AF179">
         <v>13701.3</v>
       </c>
-      <c r="AF179">
+      <c r="AG179">
         <v>10623.9</v>
       </c>
     </row>
-    <row r="180" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A180" s="1">
         <v>46010</v>
       </c>
@@ -14422,14 +14428,14 @@
       <c r="AC180" s="3">
         <v>3.6381774294722371E-3</v>
       </c>
-      <c r="AE180">
+      <c r="AF180">
         <v>16036.1</v>
       </c>
-      <c r="AF180">
+      <c r="AG180">
         <v>10623.9</v>
       </c>
     </row>
-    <row r="181" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A181" s="1">
         <v>46013</v>
       </c>
@@ -14511,17 +14517,17 @@
       <c r="AC181" s="3">
         <v>3.6393274147369296E-3</v>
       </c>
-      <c r="AE181">
+      <c r="AF181">
         <v>16036.1</v>
       </c>
-      <c r="AF181">
+      <c r="AG181">
         <v>10623.9</v>
       </c>
-      <c r="AG181">
+      <c r="AH181">
         <v>8081.85</v>
       </c>
     </row>
-    <row r="182" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A182" s="1">
         <v>46014</v>
       </c>
@@ -14606,17 +14612,17 @@
       <c r="AD182" s="3">
         <v>5.7102448237267706E-3</v>
       </c>
-      <c r="AE182">
+      <c r="AF182">
         <v>19191.5</v>
       </c>
-      <c r="AF182">
+      <c r="AG182">
         <v>10623.9</v>
       </c>
-      <c r="AG182">
+      <c r="AH182">
         <v>8131</v>
       </c>
     </row>
-    <row r="183" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A183" s="1">
         <v>46015</v>
       </c>
@@ -14701,17 +14707,17 @@
       <c r="AD183" s="3">
         <v>5.6626750392903468E-3</v>
       </c>
-      <c r="AE183">
+      <c r="AF183">
         <v>19191.5</v>
       </c>
-      <c r="AF183">
+      <c r="AG183">
         <v>10623.9</v>
       </c>
-      <c r="AG183">
+      <c r="AH183">
         <v>8131</v>
       </c>
     </row>
-    <row r="184" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A184" s="1">
         <v>46017</v>
       </c>
@@ -14796,17 +14802,17 @@
       <c r="AD184" s="3">
         <v>5.6373497141166042E-3</v>
       </c>
-      <c r="AE184">
+      <c r="AF184">
         <v>19191.5</v>
       </c>
-      <c r="AF184">
+      <c r="AG184">
         <v>10917.05</v>
       </c>
-      <c r="AG184">
+      <c r="AH184">
         <v>8131</v>
       </c>
     </row>
-    <row r="185" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A185" s="1">
         <v>46020</v>
       </c>
@@ -14891,17 +14897,17 @@
       <c r="AD185" s="3">
         <v>5.5988679022529637E-3</v>
       </c>
-      <c r="AE185">
+      <c r="AF185">
         <v>19191.5</v>
       </c>
-      <c r="AF185">
+      <c r="AG185">
         <v>11249.65</v>
       </c>
-      <c r="AG185">
+      <c r="AH185">
         <v>8131</v>
       </c>
     </row>
-    <row r="186" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A186" s="1">
         <v>46021</v>
       </c>
@@ -14986,17 +14992,17 @@
       <c r="AD186" s="3">
         <v>5.5445035712478547E-3</v>
       </c>
-      <c r="AE186">
+      <c r="AF186">
         <v>19191.5</v>
       </c>
-      <c r="AF186">
+      <c r="AG186">
         <v>11021.7</v>
       </c>
-      <c r="AG186">
+      <c r="AH186">
         <v>8131</v>
       </c>
     </row>
-    <row r="187" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A187" s="1">
         <v>46022</v>
       </c>
@@ -15081,17 +15087,17 @@
       <c r="AD187" s="3">
         <v>5.4837553449070238E-3</v>
       </c>
-      <c r="AE187">
+      <c r="AF187">
         <v>19191.5</v>
       </c>
-      <c r="AF187">
+      <c r="AG187">
         <v>11249.65</v>
       </c>
-      <c r="AG187">
+      <c r="AH187">
         <v>8131</v>
       </c>
     </row>
-    <row r="188" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A188" s="1">
         <v>46024</v>
       </c>
@@ -15176,17 +15182,17 @@
       <c r="AD188" s="3">
         <v>5.4454632742878799E-3</v>
       </c>
-      <c r="AE188">
+      <c r="AF188">
         <v>19191.5</v>
       </c>
-      <c r="AF188">
+      <c r="AG188">
         <v>11249.65</v>
       </c>
-      <c r="AG188">
+      <c r="AH188">
         <v>8131</v>
       </c>
     </row>
-    <row r="189" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A189" s="1">
         <v>46027</v>
       </c>
@@ -15271,17 +15277,17 @@
       <c r="AD189" s="3">
         <v>5.4255124912297569E-3</v>
       </c>
-      <c r="AE189">
+      <c r="AF189">
         <v>19191.5</v>
       </c>
-      <c r="AF189">
+      <c r="AG189">
         <v>11249.65</v>
       </c>
-      <c r="AG189">
+      <c r="AH189">
         <v>8131</v>
       </c>
     </row>
-    <row r="190" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A190" s="1">
         <v>46028</v>
       </c>
@@ -15366,17 +15372,17 @@
       <c r="AD190" s="3">
         <v>5.3943384404344149E-3</v>
       </c>
-      <c r="AE190">
+      <c r="AF190">
         <v>19191.5</v>
       </c>
-      <c r="AF190">
+      <c r="AG190">
         <v>11347.4</v>
       </c>
-      <c r="AG190">
+      <c r="AH190">
         <v>8131</v>
       </c>
     </row>
-    <row r="191" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A191" s="1">
         <v>46029</v>
       </c>
@@ -15461,17 +15467,17 @@
       <c r="AD191" s="3">
         <v>5.4136868392037378E-3</v>
       </c>
-      <c r="AE191">
+      <c r="AF191">
         <v>19191.5</v>
       </c>
-      <c r="AF191">
+      <c r="AG191">
         <v>11522.05</v>
       </c>
-      <c r="AG191">
+      <c r="AH191">
         <v>8152.4</v>
       </c>
     </row>
-    <row r="192" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A192" s="1">
         <v>46030</v>
       </c>
@@ -15556,17 +15562,17 @@
       <c r="AD192" s="3">
         <v>5.441331006855653E-3</v>
       </c>
-      <c r="AE192">
+      <c r="AF192">
         <v>20234.699999999997</v>
       </c>
-      <c r="AF192">
+      <c r="AG192">
         <v>12346</v>
       </c>
-      <c r="AG192">
+      <c r="AH192">
         <v>8188.4250000000002</v>
       </c>
     </row>
-    <row r="193" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A193" s="1">
         <v>46031</v>
       </c>
@@ -15651,17 +15657,17 @@
       <c r="AD193" s="3">
         <v>5.4176358987933909E-3</v>
       </c>
-      <c r="AE193">
+      <c r="AF193">
         <v>20698.900000000001</v>
       </c>
-      <c r="AF193">
+      <c r="AG193">
         <v>13340.150000000001</v>
       </c>
-      <c r="AG193">
+      <c r="AH193">
         <v>8188.4250000000002</v>
       </c>
     </row>
-    <row r="194" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A194" s="1">
         <v>46034</v>
       </c>
@@ -15746,17 +15752,17 @@
       <c r="AD194" s="3">
         <v>5.4629295964237811E-3</v>
       </c>
-      <c r="AE194">
+      <c r="AF194">
         <v>21211.72</v>
       </c>
-      <c r="AF194">
+      <c r="AG194">
         <v>13340.150000000001</v>
       </c>
-      <c r="AG194">
+      <c r="AH194">
         <v>8249.2250000000004</v>
       </c>
     </row>
-    <row r="195" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A195" s="1">
         <v>46035</v>
       </c>
@@ -15841,17 +15847,17 @@
       <c r="AD195" s="3">
         <v>5.4822331000854273E-3</v>
       </c>
-      <c r="AE195">
+      <c r="AF195">
         <v>21996.120000000003</v>
       </c>
-      <c r="AF195">
+      <c r="AG195">
         <v>13701.3</v>
       </c>
-      <c r="AG195">
+      <c r="AH195">
         <v>8318.7999999999993</v>
       </c>
     </row>
-    <row r="196" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A196" s="1">
         <v>46036</v>
       </c>
@@ -15936,17 +15942,17 @@
       <c r="AD196" s="3">
         <v>5.4692780723639579E-3</v>
       </c>
-      <c r="AE196">
+      <c r="AF196">
         <v>21996.120000000003</v>
       </c>
-      <c r="AF196">
+      <c r="AG196">
         <v>13939.3</v>
       </c>
-      <c r="AG196">
+      <c r="AH196">
         <v>8318.7999999999993</v>
       </c>
     </row>
-    <row r="197" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A197" s="1">
         <v>46037</v>
       </c>
@@ -16031,17 +16037,17 @@
       <c r="AD197" s="3">
         <v>5.4801489748018978E-3</v>
       </c>
-      <c r="AE197">
+      <c r="AF197">
         <v>24845.1</v>
       </c>
-      <c r="AF197">
+      <c r="AG197">
         <v>15185.95</v>
       </c>
-      <c r="AG197">
+      <c r="AH197">
         <v>8318.7999999999993</v>
       </c>
     </row>
-    <row r="198" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A198" s="1">
         <v>46038</v>
       </c>
@@ -16126,17 +16132,17 @@
       <c r="AD198" s="3">
         <v>5.4888741418327586E-3</v>
       </c>
-      <c r="AE198">
+      <c r="AF198">
         <v>24845.1</v>
       </c>
-      <c r="AF198">
+      <c r="AG198">
         <v>17282.75</v>
       </c>
-      <c r="AG198">
+      <c r="AH198">
         <v>8318.7999999999993</v>
       </c>
     </row>
-    <row r="199" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A199" s="1">
         <v>46041</v>
       </c>
@@ -16221,17 +16227,17 @@
       <c r="AD199" s="3">
         <v>5.5114678242524926E-3</v>
       </c>
-      <c r="AE199">
+      <c r="AF199">
         <v>28786.97</v>
       </c>
-      <c r="AF199">
+      <c r="AG199">
         <v>19191.5</v>
       </c>
-      <c r="AG199">
+      <c r="AH199">
         <v>8318.7999999999993</v>
       </c>
     </row>
-    <row r="200" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A200" s="1">
         <v>46042</v>
       </c>
@@ -16316,17 +16322,17 @@
       <c r="AD200" s="3">
         <v>5.5295314244653603E-3</v>
       </c>
-      <c r="AE200">
+      <c r="AF200">
         <v>31332.370000000003</v>
       </c>
-      <c r="AF200">
+      <c r="AG200">
         <v>20234.699999999997</v>
       </c>
-      <c r="AG200">
+      <c r="AH200">
         <v>8367.4249999999993</v>
       </c>
     </row>
-    <row r="201" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A201" s="1">
         <v>46043</v>
       </c>
@@ -16411,17 +16417,17 @@
       <c r="AD201" s="3">
         <v>5.5620078027309137E-3</v>
       </c>
-      <c r="AE201">
+      <c r="AF201">
         <v>31332.370000000003</v>
       </c>
-      <c r="AF201">
+      <c r="AG201">
         <v>20698.900000000001</v>
       </c>
-      <c r="AG201">
+      <c r="AH201">
         <v>8408.7250000000004</v>
       </c>
     </row>
-    <row r="202" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A202" s="1">
         <v>46044</v>
       </c>
@@ -16506,17 +16512,17 @@
       <c r="AD202" s="3">
         <v>5.5511170310316446E-3</v>
       </c>
-      <c r="AE202">
+      <c r="AF202">
         <v>28786.97</v>
       </c>
-      <c r="AF202">
+      <c r="AG202">
         <v>20698.900000000001</v>
       </c>
-      <c r="AG202">
+      <c r="AH202">
         <v>8451.2000000000007</v>
       </c>
     </row>
-    <row r="203" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A203" s="1">
         <v>46045</v>
       </c>
@@ -16601,17 +16607,17 @@
       <c r="AD203" s="3">
         <v>5.5438080791846041E-3</v>
       </c>
-      <c r="AE203">
+      <c r="AF203">
         <v>24845.1</v>
       </c>
-      <c r="AF203">
+      <c r="AG203">
         <v>20698.900000000001</v>
       </c>
-      <c r="AG203">
+      <c r="AH203">
         <v>8451.2000000000007</v>
       </c>
     </row>
-    <row r="204" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A204" s="1">
         <v>46048</v>
       </c>
@@ -16696,17 +16702,17 @@
       <c r="AD204" s="3">
         <v>5.5440042568878712E-3</v>
       </c>
-      <c r="AE204">
+      <c r="AF204">
         <v>24845.1</v>
       </c>
-      <c r="AF204">
+      <c r="AG204">
         <v>20698.900000000001</v>
       </c>
-      <c r="AG204">
+      <c r="AH204">
         <v>8482.9</v>
       </c>
     </row>
-    <row r="205" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A205" s="1">
         <v>46049</v>
       </c>
@@ -16791,17 +16797,17 @@
       <c r="AD205" s="3">
         <v>5.5548965053158744E-3</v>
       </c>
-      <c r="AE205">
+      <c r="AF205">
         <v>24845.1</v>
       </c>
-      <c r="AF205">
+      <c r="AG205">
         <v>20698.900000000001</v>
       </c>
-      <c r="AG205">
+      <c r="AH205">
         <v>8516.6</v>
       </c>
     </row>
-    <row r="206" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A206" s="1">
         <v>46050</v>
       </c>
@@ -16886,17 +16892,17 @@
       <c r="AD206" s="3">
         <v>5.581124550173496E-3</v>
       </c>
-      <c r="AE206">
+      <c r="AF206">
         <v>21748.6</v>
       </c>
-      <c r="AF206">
+      <c r="AG206">
         <v>20698.900000000001</v>
       </c>
-      <c r="AG206">
+      <c r="AH206">
         <v>8482.9</v>
       </c>
     </row>
-    <row r="207" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A207" s="1">
         <v>46051</v>
       </c>
@@ -16981,17 +16987,17 @@
       <c r="AD207" s="3">
         <v>5.593937686967222E-3</v>
       </c>
-      <c r="AE207">
+      <c r="AF207">
         <v>21748.6</v>
       </c>
-      <c r="AF207">
+      <c r="AG207">
         <v>20698.900000000001</v>
       </c>
-      <c r="AG207">
+      <c r="AH207">
         <v>8516.6</v>
       </c>
     </row>
-    <row r="208" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A208" s="1">
         <v>46052</v>
       </c>
@@ -17076,17 +17082,17 @@
       <c r="AD208" s="3">
         <v>5.608866788664936E-3</v>
       </c>
-      <c r="AE208">
+      <c r="AF208">
         <v>20989.1</v>
       </c>
-      <c r="AF208">
+      <c r="AG208">
         <v>20698.900000000001</v>
       </c>
-      <c r="AG208">
+      <c r="AH208">
         <v>8556.6</v>
       </c>
     </row>
-    <row r="209" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A209" s="1">
         <v>46055</v>
       </c>
@@ -17171,17 +17177,17 @@
       <c r="AD209" s="3">
         <v>5.5856376936657967E-3</v>
       </c>
-      <c r="AE209">
+      <c r="AF209">
         <v>20989.1</v>
       </c>
-      <c r="AF209">
+      <c r="AG209">
         <v>20234.699999999997</v>
       </c>
-      <c r="AG209">
+      <c r="AH209">
         <v>8652.85</v>
       </c>
     </row>
-    <row r="210" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A210" s="1">
         <v>46056</v>
       </c>
@@ -17266,17 +17272,17 @@
       <c r="AD210" s="3">
         <v>5.5783349570580863E-3</v>
       </c>
-      <c r="AE210">
+      <c r="AF210">
         <v>21773.5</v>
       </c>
-      <c r="AF210">
+      <c r="AG210">
         <v>20698.900000000001</v>
       </c>
-      <c r="AG210">
+      <c r="AH210">
         <v>8798.2000000000007</v>
       </c>
     </row>
-    <row r="211" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A211" s="1">
         <v>46057</v>
       </c>
@@ -17361,17 +17367,17 @@
       <c r="AD211" s="3">
         <v>5.5800348691289157E-3</v>
       </c>
-      <c r="AE211">
+      <c r="AF211">
         <v>24845.1</v>
       </c>
-      <c r="AF211">
+      <c r="AG211">
         <v>20989.1</v>
       </c>
-      <c r="AG211">
+      <c r="AH211">
         <v>8798.2000000000007</v>
       </c>
     </row>
-    <row r="212" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A212" s="1">
         <v>46058</v>
       </c>
@@ -17456,17 +17462,17 @@
       <c r="AD212" s="3">
         <v>5.5664685095821627E-3</v>
       </c>
-      <c r="AE212">
+      <c r="AF212">
         <v>24845.1</v>
       </c>
-      <c r="AF212">
+      <c r="AG212">
         <v>21236.620000000003</v>
       </c>
-      <c r="AG212">
+      <c r="AH212">
         <v>8798.2000000000007</v>
       </c>
     </row>
-    <row r="213" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A213" s="1">
         <v>46059</v>
       </c>
@@ -17551,17 +17557,17 @@
       <c r="AD213" s="3">
         <v>5.5718248218207308E-3</v>
       </c>
-      <c r="AE213">
+      <c r="AF213">
         <v>28786.97</v>
       </c>
-      <c r="AF213">
+      <c r="AG213">
         <v>21996.120000000003</v>
       </c>
-      <c r="AG213">
+      <c r="AH213">
         <v>8798.2000000000007</v>
       </c>
     </row>
-    <row r="214" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A214" s="1">
         <v>46062</v>
       </c>
@@ -17646,17 +17652,17 @@
       <c r="AD214" s="3">
         <v>5.5923566213196768E-3</v>
       </c>
-      <c r="AE214">
+      <c r="AF214">
         <v>24845.1</v>
       </c>
-      <c r="AF214">
+      <c r="AG214">
         <v>21236.620000000003</v>
       </c>
-      <c r="AG214">
+      <c r="AH214">
         <v>8798.2000000000007</v>
       </c>
     </row>
-    <row r="215" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A215" s="1">
         <v>46063</v>
       </c>
@@ -17741,17 +17747,17 @@
       <c r="AD215" s="3">
         <v>5.5832884325340637E-3</v>
       </c>
-      <c r="AE215">
+      <c r="AF215">
         <v>24085.599999999999</v>
       </c>
-      <c r="AF215">
+      <c r="AG215">
         <v>20989.1</v>
       </c>
-      <c r="AG215">
+      <c r="AH215">
         <v>8798.2000000000007</v>
       </c>
     </row>
-    <row r="216" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A216" s="1">
         <v>46064</v>
       </c>
@@ -17836,17 +17842,17 @@
       <c r="AD216" s="3">
         <v>5.5414072481505061E-3</v>
       </c>
-      <c r="AE216">
+      <c r="AF216">
         <v>24085.599999999999</v>
       </c>
-      <c r="AF216">
+      <c r="AG216">
         <v>20989.1</v>
       </c>
-      <c r="AG216">
+      <c r="AH216">
         <v>8875.35</v>
       </c>
     </row>
-    <row r="217" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A217" s="1">
         <v>46065</v>
       </c>
@@ -17931,17 +17937,17 @@
       <c r="AD217" s="3">
         <v>5.5340420075112749E-3</v>
       </c>
-      <c r="AE217">
+      <c r="AF217">
         <v>24085.599999999999</v>
       </c>
-      <c r="AF217">
+      <c r="AG217">
         <v>20989.1</v>
       </c>
-      <c r="AG217">
+      <c r="AH217">
         <v>8885.9</v>
       </c>
     </row>
-    <row r="218" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A218" s="1">
         <v>46066</v>
       </c>
@@ -18026,17 +18032,17 @@
       <c r="AD218" s="3">
         <v>5.54650964503672E-3</v>
       </c>
-      <c r="AE218">
+      <c r="AF218">
         <v>24085.599999999999</v>
       </c>
-      <c r="AF218">
+      <c r="AG218">
         <v>20989.1</v>
       </c>
-      <c r="AG218">
+      <c r="AH218">
         <v>9058.75</v>
       </c>
     </row>
-    <row r="219" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A219" s="1">
         <v>46069</v>
       </c>
@@ -18121,17 +18127,17 @@
       <c r="AD219" s="3">
         <v>5.5505246403589458E-3</v>
       </c>
-      <c r="AE219">
+      <c r="AF219">
         <v>24085.599999999999</v>
       </c>
-      <c r="AF219">
+      <c r="AG219">
         <v>20908.2</v>
       </c>
-      <c r="AG219">
+      <c r="AH219">
         <v>8885.9</v>
       </c>
     </row>
-    <row r="220" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A220" s="1">
         <v>46070</v>
       </c>
@@ -18216,17 +18222,17 @@
       <c r="AD220" s="3">
         <v>5.5655686216554796E-3</v>
       </c>
-      <c r="AE220">
+      <c r="AF220">
         <v>30882.6</v>
       </c>
-      <c r="AF220">
+      <c r="AG220">
         <v>20989.1</v>
       </c>
-      <c r="AG220">
+      <c r="AH220">
         <v>9058.75</v>
       </c>
     </row>
-    <row r="221" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A221" s="1">
         <v>46071</v>
       </c>
@@ -18311,17 +18317,17 @@
       <c r="AD221" s="3">
         <v>5.5160074223845161E-3</v>
       </c>
-      <c r="AE221">
+      <c r="AF221">
         <v>30882.6</v>
       </c>
-      <c r="AF221">
+      <c r="AG221">
         <v>20989.1</v>
       </c>
-      <c r="AG221">
+      <c r="AH221">
         <v>9273.0499999999993</v>
       </c>
     </row>
-    <row r="222" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A222" s="1">
         <v>46072</v>
       </c>
@@ -18406,17 +18412,17 @@
       <c r="AD222" s="3">
         <v>5.4981295809144702E-3</v>
       </c>
-      <c r="AE222">
+      <c r="AF222">
         <v>35207.4</v>
       </c>
-      <c r="AF222">
+      <c r="AG222">
         <v>21236.620000000003</v>
       </c>
-      <c r="AG222">
+      <c r="AH222">
         <v>9436.9</v>
       </c>
     </row>
-    <row r="223" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A223" s="1">
         <v>46073</v>
       </c>
@@ -18501,17 +18507,17 @@
       <c r="AD223" s="3">
         <v>5.4847464605634862E-3</v>
       </c>
-      <c r="AE223">
+      <c r="AF223">
         <v>36713.100000000006</v>
       </c>
-      <c r="AF223">
+      <c r="AG223">
         <v>21996.120000000003</v>
       </c>
-      <c r="AG223">
+      <c r="AH223">
         <v>9691.5750000000007</v>
       </c>
     </row>
-    <row r="224" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A224" s="1">
         <v>46076</v>
       </c>
@@ -18596,17 +18602,17 @@
       <c r="AD224" s="3">
         <v>5.4890279736227437E-3</v>
       </c>
-      <c r="AE224">
+      <c r="AF224">
         <v>36713.100000000006</v>
       </c>
-      <c r="AF224">
+      <c r="AG224">
         <v>21996.120000000003</v>
       </c>
-      <c r="AG224">
+      <c r="AH224">
         <v>9877.625</v>
       </c>
     </row>
-    <row r="225" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A225" s="1">
         <v>46077</v>
       </c>
@@ -18691,17 +18697,17 @@
       <c r="AD225" s="3">
         <v>5.4317229457712772E-3</v>
       </c>
-      <c r="AE225">
+      <c r="AF225">
         <v>29354.25</v>
       </c>
-      <c r="AF225">
+      <c r="AG225">
         <v>22717.35</v>
       </c>
-      <c r="AG225">
+      <c r="AH225">
         <v>9877.625</v>
       </c>
     </row>
-    <row r="226" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A226" s="1">
         <v>46078</v>
       </c>
@@ -18786,17 +18792,17 @@
       <c r="AD226" s="3">
         <v>5.3763951665175497E-3</v>
       </c>
-      <c r="AE226">
+      <c r="AF226">
         <v>29354.25</v>
       </c>
-      <c r="AF226">
+      <c r="AG226">
         <v>22717.35</v>
       </c>
-      <c r="AG226">
+      <c r="AH226">
         <v>10102.25</v>
       </c>
     </row>
-    <row r="227" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A227" s="1">
         <v>46079</v>
       </c>
@@ -18881,17 +18887,17 @@
       <c r="AD227" s="3">
         <v>5.4016423998062739E-3</v>
       </c>
-      <c r="AE227">
+      <c r="AF227">
         <v>21957.85</v>
       </c>
-      <c r="AF227">
+      <c r="AG227">
         <v>22717.35</v>
       </c>
-      <c r="AG227">
+      <c r="AH227">
         <v>10248.25</v>
       </c>
     </row>
-    <row r="228" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A228" s="1">
         <v>46080</v>
       </c>
@@ -18976,17 +18982,17 @@
       <c r="AD228" s="3">
         <v>5.3392973734732764E-3</v>
       </c>
-      <c r="AE228">
+      <c r="AF228">
         <v>21957.85</v>
       </c>
-      <c r="AF228">
+      <c r="AG228">
         <v>22717.35</v>
       </c>
-      <c r="AG228">
+      <c r="AH228">
         <v>10583</v>
       </c>
     </row>
-    <row r="229" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A229" s="1">
         <v>46083</v>
       </c>
@@ -19071,17 +19077,17 @@
       <c r="AD229" s="3">
         <v>5.3471418101097047E-3</v>
       </c>
-      <c r="AE229">
+      <c r="AF229">
         <v>20933.099999999999</v>
       </c>
-      <c r="AF229">
+      <c r="AG229">
         <v>22717.35</v>
       </c>
-      <c r="AG229">
+      <c r="AH229">
         <v>10633.9</v>
       </c>
     </row>
-    <row r="230" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A230" s="1">
         <v>46084</v>
       </c>
@@ -19166,17 +19172,17 @@
       <c r="AD230" s="3">
         <v>5.3617193946910776E-3</v>
       </c>
-      <c r="AE230">
+      <c r="AF230">
         <v>20933.099999999999</v>
       </c>
-      <c r="AF230">
+      <c r="AG230">
         <v>22717.35</v>
       </c>
-      <c r="AG230">
+      <c r="AH230">
         <v>10633.9</v>
       </c>
     </row>
-    <row r="231" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A231" s="1">
         <v>46085</v>
       </c>
@@ -19261,17 +19267,17 @@
       <c r="AD231" s="3">
         <v>5.2754737851529836E-3</v>
       </c>
-      <c r="AE231">
+      <c r="AF231">
         <v>19063.245000000003</v>
       </c>
-      <c r="AF231">
+      <c r="AG231">
         <v>22271.1</v>
       </c>
-      <c r="AG231">
+      <c r="AH231">
         <v>10772.25</v>
       </c>
     </row>
-    <row r="232" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A232" s="1">
         <v>46086</v>
       </c>
@@ -19356,17 +19362,17 @@
       <c r="AD232" s="3">
         <v>5.2316582770151531E-3</v>
       </c>
-      <c r="AE232">
+      <c r="AF232">
         <v>19063.245000000003</v>
       </c>
-      <c r="AF232">
+      <c r="AG232">
         <v>21511.599999999999</v>
       </c>
-      <c r="AG232">
+      <c r="AH232">
         <v>10876.900000000001</v>
       </c>
     </row>
-    <row r="233" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A233" s="1">
         <v>46087</v>
       </c>
@@ -19451,17 +19457,17 @@
       <c r="AD233" s="3">
         <v>5.2230174566701097E-3</v>
       </c>
-      <c r="AE233">
+      <c r="AF233">
         <v>20933.099999999999</v>
       </c>
-      <c r="AF233">
+      <c r="AG233">
         <v>21511.599999999999</v>
       </c>
-      <c r="AG233">
+      <c r="AH233">
         <v>10876.900000000001</v>
       </c>
     </row>
-    <row r="234" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A234" s="1">
         <v>46090</v>
       </c>
@@ -19546,17 +19552,17 @@
       <c r="AD234" s="3">
         <v>5.1350139356579035E-3</v>
       </c>
-      <c r="AE234">
+      <c r="AF234">
         <v>21511.599999999999</v>
       </c>
-      <c r="AF234">
+      <c r="AG234">
         <v>22271.1</v>
       </c>
-      <c r="AG234">
+      <c r="AH234">
         <v>10922.7</v>
       </c>
     </row>
-    <row r="235" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A235" s="1">
         <v>46091</v>
       </c>
@@ -19641,17 +19647,17 @@
       <c r="AD235" s="3">
         <v>5.1174457466450062E-3</v>
       </c>
-      <c r="AE235">
+      <c r="AF235">
         <v>22455.45</v>
       </c>
-      <c r="AF235">
+      <c r="AG235">
         <v>22717.35</v>
       </c>
-      <c r="AG235">
+      <c r="AH235">
         <v>10985.099999999999</v>
       </c>
     </row>
-    <row r="236" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A236" s="1">
         <v>46092</v>
       </c>
@@ -19736,17 +19742,17 @@
       <c r="AD236" s="3">
         <v>5.0473067089231577E-3</v>
       </c>
-      <c r="AE236">
+      <c r="AF236">
         <v>22455.45</v>
       </c>
-      <c r="AF236">
+      <c r="AG236">
         <v>22271.1</v>
       </c>
-      <c r="AG236">
+      <c r="AH236">
         <v>10985.099999999999</v>
       </c>
     </row>
-    <row r="237" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A237" s="1">
         <v>46093</v>
       </c>
@@ -19831,17 +19837,17 @@
       <c r="AD237" s="3">
         <v>5.0560923609963533E-3</v>
       </c>
-      <c r="AE237">
+      <c r="AF237">
         <v>28269.599999999999</v>
       </c>
-      <c r="AF237">
+      <c r="AG237">
         <v>22717.35</v>
       </c>
-      <c r="AG237">
+      <c r="AH237">
         <v>11084.099999999999</v>
       </c>
     </row>
-    <row r="238" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A238" s="1">
         <v>46094</v>
       </c>
@@ -19926,17 +19932,17 @@
       <c r="AD238" s="3">
         <v>5.0006589651745382E-3</v>
       </c>
-      <c r="AE238">
+      <c r="AF238">
         <v>32133.5</v>
       </c>
-      <c r="AF238">
+      <c r="AG238">
         <v>22717.35</v>
       </c>
-      <c r="AG238">
+      <c r="AH238">
         <v>11249.65</v>
       </c>
     </row>
-    <row r="239" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A239" s="1">
         <v>46097</v>
       </c>
@@ -20021,17 +20027,17 @@
       <c r="AD239" s="3">
         <v>5.058606587516677E-3</v>
       </c>
-      <c r="AE239">
+      <c r="AF239">
         <v>32133.5</v>
       </c>
-      <c r="AF239">
+      <c r="AG239">
         <v>22717.35</v>
       </c>
-      <c r="AG239">
+      <c r="AH239">
         <v>11249.65</v>
       </c>
     </row>
-    <row r="240" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A240" s="1">
         <v>46098</v>
       </c>
@@ -20116,17 +20122,17 @@
       <c r="AD240" s="3">
         <v>4.9640750033947949E-3</v>
       </c>
-      <c r="AE240">
+      <c r="AF240">
         <v>32133.5</v>
       </c>
-      <c r="AF240">
+      <c r="AG240">
         <v>25029.45</v>
       </c>
-      <c r="AG240">
+      <c r="AH240">
         <v>11347.4</v>
       </c>
     </row>
-    <row r="241" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A241" s="1">
         <v>46099</v>
       </c>
@@ -20211,17 +20217,17 @@
       <c r="AD241" s="3">
         <v>4.9514803837900859E-3</v>
       </c>
-      <c r="AE241">
+      <c r="AF241">
         <v>26765.599999999999</v>
       </c>
-      <c r="AF241">
+      <c r="AG241">
         <v>25029.45</v>
       </c>
-      <c r="AG241">
+      <c r="AH241">
         <v>11249.65</v>
       </c>
     </row>
-    <row r="242" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A242" s="1">
         <v>46100</v>
       </c>
@@ -20306,17 +20312,17 @@
       <c r="AD242" s="3">
         <v>4.9485095191674783E-3</v>
       </c>
-      <c r="AE242">
+      <c r="AF242">
         <v>22455.45</v>
       </c>
-      <c r="AF242">
+      <c r="AG242">
         <v>22717.35</v>
       </c>
-      <c r="AG242">
+      <c r="AH242">
         <v>11249.65</v>
       </c>
     </row>
-    <row r="243" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A243" s="1">
         <v>46101</v>
       </c>
@@ -20401,17 +20407,17 @@
       <c r="AD243" s="3">
         <v>4.9707047282680555E-3</v>
       </c>
-      <c r="AE243">
+      <c r="AF243">
         <v>22455.45</v>
       </c>
-      <c r="AF243">
+      <c r="AG243">
         <v>25029.45</v>
       </c>
-      <c r="AG243">
+      <c r="AH243">
         <v>11347.4</v>
       </c>
     </row>
-    <row r="244" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A244" s="1">
         <v>46104</v>
       </c>
@@ -20496,17 +20502,17 @@
       <c r="AD244" s="3">
         <v>4.9936678542408068E-3</v>
       </c>
-      <c r="AE244">
+      <c r="AF244">
         <v>26765.599999999999</v>
       </c>
-      <c r="AF244">
+      <c r="AG244">
         <v>25029.45</v>
       </c>
-      <c r="AG244">
+      <c r="AH244">
         <v>11347.4</v>
       </c>
     </row>
-    <row r="245" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A245" s="1">
         <v>46105</v>
       </c>
@@ -20591,17 +20597,17 @@
       <c r="AD245" s="3">
         <v>5.0179044066625917E-3</v>
       </c>
-      <c r="AE245">
+      <c r="AF245">
         <v>26765.599999999999</v>
       </c>
-      <c r="AF245">
+      <c r="AG245">
         <v>25029.45</v>
       </c>
-      <c r="AG245">
+      <c r="AH245">
         <v>11347.4</v>
       </c>
     </row>
-    <row r="246" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A246" s="1">
         <v>46106</v>
       </c>
@@ -20686,17 +20692,17 @@
       <c r="AD246" s="3">
         <v>5.0012658424732669E-3</v>
       </c>
-      <c r="AE246">
+      <c r="AF246">
         <v>26765.599999999999</v>
       </c>
-      <c r="AF246">
+      <c r="AG246">
         <v>25029.45</v>
       </c>
-      <c r="AG246">
+      <c r="AH246">
         <v>11363.849999999999</v>
       </c>
     </row>
-    <row r="247" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A247" s="1">
         <v>46107</v>
       </c>
@@ -20781,17 +20787,17 @@
       <c r="AD247" s="3">
         <v>5.0689975931600727E-3</v>
       </c>
-      <c r="AE247">
+      <c r="AF247">
         <v>26765.599999999999</v>
       </c>
-      <c r="AF247">
+      <c r="AG247">
         <v>25029.45</v>
       </c>
-      <c r="AG247">
+      <c r="AH247">
         <v>11531.099999999999</v>
       </c>
     </row>
-    <row r="248" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A248" s="1">
         <v>46108</v>
       </c>
@@ -20876,17 +20882,17 @@
       <c r="AD248" s="3">
         <v>5.0536742637268253E-3</v>
       </c>
-      <c r="AE248">
-        <v>22455.45</v>
-      </c>
       <c r="AF248">
         <v>22455.45</v>
       </c>
       <c r="AG248">
+        <v>22455.45</v>
+      </c>
+      <c r="AH248">
         <v>11531.099999999999</v>
       </c>
     </row>
-    <row r="249" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A249" s="1">
         <v>46111</v>
       </c>
@@ -20971,17 +20977,17 @@
       <c r="AD249" s="3">
         <v>5.0934459904542415E-3</v>
       </c>
-      <c r="AE249">
+      <c r="AF249">
         <v>26765.599999999999</v>
       </c>
-      <c r="AF249">
+      <c r="AG249">
         <v>25029.45</v>
       </c>
-      <c r="AG249">
+      <c r="AH249">
         <v>11709.8</v>
       </c>
     </row>
-    <row r="250" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A250" s="1">
         <v>46112</v>
       </c>
@@ -21066,17 +21072,17 @@
       <c r="AD250" s="3">
         <v>5.0466305126773883E-3</v>
       </c>
-      <c r="AE250">
+      <c r="AF250">
         <v>22455.45</v>
       </c>
-      <c r="AF250">
+      <c r="AG250">
         <v>25029.45</v>
       </c>
-      <c r="AG250">
+      <c r="AH250">
         <v>11709.8</v>
       </c>
     </row>
-    <row r="251" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A251" s="1">
         <v>46113</v>
       </c>
@@ -21161,17 +21167,17 @@
       <c r="AD251" s="3">
         <v>5.0898294879673329E-3</v>
       </c>
-      <c r="AE251">
+      <c r="AF251">
         <v>22455.45</v>
       </c>
-      <c r="AF251">
+      <c r="AG251">
         <v>25029.45</v>
       </c>
-      <c r="AG251">
+      <c r="AH251">
         <v>11709.8</v>
       </c>
     </row>
-    <row r="252" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A252" s="1">
         <v>46118</v>
       </c>
@@ -21256,17 +21262,17 @@
       <c r="AD252" s="3">
         <v>5.0424453136991938E-3</v>
       </c>
-      <c r="AE252">
+      <c r="AF252">
         <v>22455.45</v>
       </c>
-      <c r="AF252">
+      <c r="AG252">
         <v>28893.35</v>
       </c>
-      <c r="AG252">
+      <c r="AH252">
         <v>11806.5</v>
       </c>
     </row>
-    <row r="253" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A253" s="1">
         <v>46119</v>
       </c>
@@ -21351,17 +21357,17 @@
       <c r="AD253" s="3">
         <v>5.0307924168098376E-3</v>
       </c>
-      <c r="AE253">
+      <c r="AF253">
         <v>22455.45</v>
       </c>
-      <c r="AF253">
+      <c r="AG253">
         <v>28893.35</v>
       </c>
-      <c r="AG253">
+      <c r="AH253">
         <v>11897.55</v>
       </c>
     </row>
-    <row r="254" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A254" s="1">
         <v>46120</v>
       </c>
@@ -21446,17 +21452,17 @@
       <c r="AD254" s="3">
         <v>5.0374082740628715E-3</v>
       </c>
-      <c r="AE254">
+      <c r="AF254">
         <v>26765.599999999999</v>
       </c>
-      <c r="AF254">
+      <c r="AG254">
         <v>30932.75</v>
       </c>
-      <c r="AG254">
+      <c r="AH254">
         <v>12104.119999999999</v>
       </c>
     </row>
-    <row r="255" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A255" s="1">
         <v>46121</v>
       </c>
@@ -21541,17 +21547,17 @@
       <c r="AD255" s="3">
         <v>5.017359530113309E-3</v>
       </c>
-      <c r="AE255">
+      <c r="AF255">
         <v>26319.35</v>
       </c>
-      <c r="AF255">
+      <c r="AG255">
         <v>26765.599999999999</v>
       </c>
-      <c r="AG255">
+      <c r="AH255">
         <v>12104.119999999999</v>
       </c>
     </row>
-    <row r="256" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A256" s="1">
         <v>46122</v>
       </c>
@@ -21636,17 +21642,17 @@
       <c r="AD256" s="3">
         <v>4.999026012383845E-3</v>
       </c>
-      <c r="AE256">
+      <c r="AF256">
         <v>19641.745000000003</v>
       </c>
-      <c r="AF256">
+      <c r="AG256">
         <v>22455.45</v>
       </c>
-      <c r="AG256">
+      <c r="AH256">
         <v>12104.119999999999</v>
       </c>
     </row>
-    <row r="257" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A257" s="1">
         <v>46125</v>
       </c>
@@ -21731,17 +21737,17 @@
       <c r="AD257" s="3">
         <v>5.0031704095379039E-3</v>
       </c>
-      <c r="AE257">
+      <c r="AF257">
         <v>19641.745000000003</v>
       </c>
-      <c r="AF257">
+      <c r="AG257">
         <v>21511.599999999999</v>
       </c>
-      <c r="AG257">
+      <c r="AH257">
         <v>12104.119999999999</v>
       </c>
     </row>
-    <row r="258" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A258" s="1">
         <v>46126</v>
       </c>
@@ -21826,17 +21832,17 @@
       <c r="AD258" s="3">
         <v>4.9923720698541608E-3</v>
       </c>
-      <c r="AE258">
+      <c r="AF258">
         <v>19641.745000000003</v>
       </c>
-      <c r="AF258">
+      <c r="AG258">
         <v>21511.599999999999</v>
       </c>
-      <c r="AG258">
+      <c r="AH258">
         <v>12331.92</v>
       </c>
     </row>
-    <row r="259" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A259" s="1">
         <v>46127</v>
       </c>
@@ -21921,17 +21927,17 @@
       <c r="AD259" s="3">
         <v>4.9616001553278713E-3</v>
       </c>
-      <c r="AE259">
+      <c r="AF259">
         <v>19404.599999999999</v>
       </c>
-      <c r="AF259">
+      <c r="AG259">
         <v>20933.099999999999</v>
       </c>
-      <c r="AG259">
+      <c r="AH259">
         <v>12331.92</v>
       </c>
     </row>
-    <row r="260" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A260" s="1">
         <v>46128</v>
       </c>
@@ -22016,17 +22022,17 @@
       <c r="AD260" s="3">
         <v>4.9161729327108668E-3</v>
       </c>
-      <c r="AE260">
+      <c r="AF260">
         <v>23714.75</v>
       </c>
-      <c r="AF260">
+      <c r="AG260">
         <v>20933.099999999999</v>
       </c>
-      <c r="AG260">
+      <c r="AH260">
         <v>12565.375</v>
       </c>
     </row>
-    <row r="261" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A261" s="1">
         <v>46129</v>
       </c>
@@ -22111,17 +22117,17 @@
       <c r="AD261" s="3">
         <v>4.8863386094979777E-3</v>
       </c>
-      <c r="AE261">
+      <c r="AF261">
         <v>23714.75</v>
       </c>
-      <c r="AF261">
+      <c r="AG261">
         <v>19063.245000000003</v>
       </c>
-      <c r="AG261">
+      <c r="AH261">
         <v>12565.375</v>
       </c>
     </row>
-    <row r="262" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A262" s="1">
         <v>46132</v>
       </c>
@@ -22206,17 +22212,17 @@
       <c r="AD262" s="3">
         <v>4.8557211580727662E-3</v>
       </c>
-      <c r="AE262">
+      <c r="AF262">
         <v>23714.75</v>
       </c>
-      <c r="AF262">
+      <c r="AG262">
         <v>19063.245000000003</v>
       </c>
-      <c r="AG262">
+      <c r="AH262">
         <v>12565.375</v>
       </c>
     </row>
-    <row r="263" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A263" s="1">
         <v>46133</v>
       </c>
@@ -22301,17 +22307,17 @@
       <c r="AD263" s="3">
         <v>4.8130016476069055E-3</v>
       </c>
-      <c r="AE263">
+      <c r="AF263">
         <v>16079.75</v>
       </c>
-      <c r="AF263">
+      <c r="AG263">
         <v>19063.245000000003</v>
       </c>
-      <c r="AG263">
+      <c r="AH263">
         <v>12565.375</v>
       </c>
     </row>
-    <row r="264" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A264" s="1">
         <v>46134</v>
       </c>
@@ -22396,17 +22402,17 @@
       <c r="AD264" s="3">
         <v>4.8180023547613141E-3</v>
       </c>
-      <c r="AE264">
+      <c r="AF264">
         <v>16079.75</v>
       </c>
-      <c r="AF264">
+      <c r="AG264">
         <v>20933.099999999999</v>
       </c>
-      <c r="AG264">
+      <c r="AH264">
         <v>12882.725</v>
       </c>
     </row>
-    <row r="265" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A265" s="1">
         <v>46135</v>
       </c>
@@ -22491,17 +22497,17 @@
       <c r="AD265" s="3">
         <v>4.734652091505827E-3</v>
       </c>
-      <c r="AE265">
+      <c r="AF265">
         <v>16079.75</v>
       </c>
-      <c r="AF265">
+      <c r="AG265">
         <v>21511.599999999999</v>
       </c>
-      <c r="AG265">
+      <c r="AH265">
         <v>13007.6</v>
       </c>
     </row>
-    <row r="266" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A266" s="1">
         <v>46136</v>
       </c>
@@ -22586,17 +22592,17 @@
       <c r="AD266" s="3">
         <v>4.6993789892427629E-3</v>
       </c>
-      <c r="AE266">
+      <c r="AF266">
         <v>21860.47</v>
       </c>
-      <c r="AF266">
+      <c r="AG266">
         <v>22455.45</v>
       </c>
-      <c r="AG266">
+      <c r="AH266">
         <v>13345.05</v>
       </c>
     </row>
-    <row r="267" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A267" s="1">
         <v>46139</v>
       </c>
@@ -22681,17 +22687,17 @@
       <c r="AD267" s="3">
         <v>4.6166342460954362E-3</v>
       </c>
-      <c r="AE267">
+      <c r="AF267">
         <v>13028.4</v>
       </c>
-      <c r="AF267">
+      <c r="AG267">
         <v>22455.45</v>
       </c>
-      <c r="AG267">
+      <c r="AH267">
         <v>13345.05</v>
       </c>
     </row>
-    <row r="268" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A268" s="1">
         <v>46140</v>
       </c>
@@ -22776,17 +22782,17 @@
       <c r="AD268" s="3">
         <v>4.6175629526826311E-3</v>
       </c>
-      <c r="AE268">
+      <c r="AF268">
         <v>9177.9</v>
       </c>
-      <c r="AF268">
+      <c r="AG268">
         <v>22455.45</v>
       </c>
-      <c r="AG268">
+      <c r="AH268">
         <v>13345.05</v>
       </c>
     </row>
-    <row r="269" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A269" s="1">
         <v>46141</v>
       </c>
@@ -22871,17 +22877,17 @@
       <c r="AD269" s="3">
         <v>4.5950321556245685E-3</v>
       </c>
-      <c r="AE269">
+      <c r="AF269">
         <v>9177.9</v>
       </c>
-      <c r="AF269">
+      <c r="AG269">
         <v>22455.45</v>
       </c>
-      <c r="AG269">
+      <c r="AH269">
         <v>13340.150000000001</v>
       </c>
     </row>
-    <row r="270" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A270" s="1">
         <v>46142</v>
       </c>
@@ -22966,17 +22972,17 @@
       <c r="AD270" s="3">
         <v>4.6001179748321923E-3</v>
       </c>
-      <c r="AE270">
+      <c r="AF270">
         <v>8906.5</v>
       </c>
-      <c r="AF270">
+      <c r="AG270">
         <v>21430.7</v>
       </c>
-      <c r="AG270">
+      <c r="AH270">
         <v>12882.725</v>
       </c>
     </row>
-    <row r="271" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A271" s="1">
         <v>46146</v>
       </c>
@@ -23061,17 +23067,17 @@
       <c r="AD271" s="3">
         <v>4.6011919952771378E-3</v>
       </c>
-      <c r="AE271">
+      <c r="AF271">
         <v>8688.1</v>
       </c>
-      <c r="AF271">
+      <c r="AG271">
         <v>19063.245000000003</v>
       </c>
-      <c r="AG271">
+      <c r="AH271">
         <v>12882.725</v>
       </c>
     </row>
-    <row r="272" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A272" s="1">
         <v>46147</v>
       </c>
@@ -23156,17 +23162,17 @@
       <c r="AD272" s="3">
         <v>4.6119765851653253E-3</v>
       </c>
-      <c r="AE272">
+      <c r="AF272">
         <v>8906.5</v>
       </c>
-      <c r="AF272">
+      <c r="AG272">
         <v>17037.145</v>
       </c>
-      <c r="AG272">
+      <c r="AH272">
         <v>12882.725</v>
       </c>
     </row>
-    <row r="273" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A273" s="1">
         <v>46148</v>
       </c>
@@ -23251,17 +23257,17 @@
       <c r="AD273" s="3">
         <v>4.6135006599929028E-3</v>
       </c>
-      <c r="AE273">
+      <c r="AF273">
         <v>8688.1</v>
       </c>
-      <c r="AF273">
+      <c r="AG273">
         <v>16539.5</v>
       </c>
-      <c r="AG273">
+      <c r="AH273">
         <v>12882.725</v>
       </c>
     </row>
-    <row r="274" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A274" s="1">
         <v>46149</v>
       </c>
@@ -23346,17 +23352,17 @@
       <c r="AD274" s="3">
         <v>4.6015965326199849E-3</v>
       </c>
-      <c r="AE274">
+      <c r="AF274">
         <v>8688.1</v>
       </c>
-      <c r="AF274">
+      <c r="AG274">
         <v>16539.5</v>
       </c>
-      <c r="AG274">
+      <c r="AH274">
         <v>13340.150000000001</v>
       </c>
     </row>
-    <row r="275" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A275" s="1">
         <v>46150</v>
       </c>
@@ -23441,17 +23447,17 @@
       <c r="AD275" s="3">
         <v>4.6043700909960458E-3</v>
       </c>
-      <c r="AE275">
+      <c r="AF275">
         <v>8605</v>
       </c>
-      <c r="AF275">
+      <c r="AG275">
         <v>16539.5</v>
       </c>
-      <c r="AG275">
+      <c r="AH275">
         <v>13340.150000000001</v>
       </c>
     </row>
-    <row r="276" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A276" s="1">
         <v>46153</v>
       </c>
@@ -23536,17 +23542,17 @@
       <c r="AD276" s="3">
         <v>4.5943852557129503E-3</v>
       </c>
-      <c r="AE276">
+      <c r="AF276">
         <v>8384.2999999999993</v>
       </c>
-      <c r="AF276">
+      <c r="AG276">
         <v>16539.5</v>
       </c>
-      <c r="AG276">
+      <c r="AH276">
         <v>13340.150000000001</v>
       </c>
     </row>
-    <row r="277" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A277" s="1">
         <v>46154</v>
       </c>
@@ -23631,17 +23637,17 @@
       <c r="AD277" s="3">
         <v>4.5997249702182975E-3</v>
       </c>
-      <c r="AE277">
+      <c r="AF277">
         <v>7669.8</v>
       </c>
-      <c r="AF277">
+      <c r="AG277">
         <v>15819.25</v>
       </c>
-      <c r="AG277">
+      <c r="AH277">
         <v>13340.150000000001</v>
       </c>
     </row>
-    <row r="278" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A278" s="1">
         <v>46155</v>
       </c>
@@ -23726,17 +23732,17 @@
       <c r="AD278" s="3">
         <v>4.504615748813421E-3</v>
       </c>
-      <c r="AE278">
+      <c r="AF278">
         <v>8384.2999999999993</v>
       </c>
-      <c r="AF278">
+      <c r="AG278">
         <v>15819.25</v>
       </c>
-      <c r="AG278">
+      <c r="AH278">
         <v>13701.3</v>
       </c>
     </row>
-    <row r="279" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A279" s="1">
         <v>46156</v>
       </c>
@@ -23821,17 +23827,17 @@
       <c r="AD279" s="3">
         <v>4.475302845887397E-3</v>
       </c>
-      <c r="AE279">
+      <c r="AF279">
         <v>7669.8</v>
       </c>
-      <c r="AF279">
+      <c r="AG279">
         <v>15819.25</v>
       </c>
-      <c r="AG279">
+      <c r="AH279">
         <v>13701.3</v>
       </c>
     </row>
-    <row r="280" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A280" s="1">
         <v>46157</v>
       </c>
@@ -23916,17 +23922,17 @@
       <c r="AD280" s="3">
         <v>4.4677770685527581E-3</v>
       </c>
-      <c r="AE280">
+      <c r="AF280">
         <v>7669.8</v>
       </c>
-      <c r="AF280">
+      <c r="AG280">
         <v>15819.25</v>
       </c>
-      <c r="AG280">
+      <c r="AH280">
         <v>13799.6</v>
       </c>
     </row>
-    <row r="281" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A281" s="1">
         <v>46160</v>
       </c>
@@ -24011,17 +24017,17 @@
       <c r="AD281" s="3">
         <v>4.4728399919980698E-3</v>
       </c>
-      <c r="AE281">
+      <c r="AF281">
         <v>7066.5</v>
       </c>
-      <c r="AF281">
+      <c r="AG281">
         <v>15819.25</v>
       </c>
-      <c r="AG281">
+      <c r="AH281">
         <v>13701.3</v>
       </c>
     </row>
-    <row r="282" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A282" s="1">
         <v>46161</v>
       </c>
@@ -24106,17 +24112,17 @@
       <c r="AD282" s="3">
         <v>4.4696476416920634E-3</v>
       </c>
-      <c r="AE282">
+      <c r="AF282">
         <v>7066.5</v>
       </c>
-      <c r="AF282">
+      <c r="AG282">
         <v>15819.25</v>
       </c>
-      <c r="AG282">
+      <c r="AH282">
         <v>13799.6</v>
       </c>
     </row>
-    <row r="283" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A283" s="1">
         <v>46162</v>
       </c>
@@ -24201,17 +24207,17 @@
       <c r="AD283" s="3">
         <v>4.4362260528086174E-3</v>
       </c>
-      <c r="AE283">
+      <c r="AF283">
         <v>7045.3</v>
       </c>
-      <c r="AF283">
+      <c r="AG283">
         <v>15205.65</v>
       </c>
-      <c r="AG283">
+      <c r="AH283">
         <v>13799.6</v>
       </c>
     </row>
-    <row r="284" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A284" s="1">
         <v>46163</v>
       </c>
@@ -24296,17 +24302,17 @@
       <c r="AD284" s="3">
         <v>4.3598826663542884E-3</v>
       </c>
-      <c r="AE284">
+      <c r="AF284">
         <v>7045.3</v>
       </c>
-      <c r="AF284">
+      <c r="AG284">
         <v>15819.25</v>
       </c>
-      <c r="AG284">
+      <c r="AH284">
         <v>14013.900000000001</v>
       </c>
     </row>
-    <row r="285" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A285" s="1">
         <v>46164</v>
       </c>
@@ -24391,17 +24397,17 @@
       <c r="AD285" s="3">
         <v>4.3631468606001251E-3</v>
       </c>
-      <c r="AE285">
+      <c r="AF285">
         <v>7045.3</v>
       </c>
-      <c r="AF285">
+      <c r="AG285">
         <v>15205.65</v>
       </c>
-      <c r="AG285">
+      <c r="AH285">
         <v>14321.875</v>
       </c>
     </row>
-    <row r="286" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A286" s="1">
         <v>46167</v>
       </c>
@@ -24486,17 +24492,17 @@
       <c r="AD286" s="3">
         <v>4.3318257296920968E-3</v>
       </c>
-      <c r="AE286">
+      <c r="AF286">
         <v>7045.8</v>
       </c>
-      <c r="AF286">
+      <c r="AG286">
         <v>14831.3</v>
       </c>
-      <c r="AG286">
+      <c r="AH286">
         <v>14013.900000000001</v>
       </c>
     </row>
-    <row r="287" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A287" s="1">
         <v>46168</v>
       </c>
@@ -24581,17 +24587,17 @@
       <c r="AD287" s="3">
         <v>4.3011381517608759E-3</v>
       </c>
-      <c r="AE287">
+      <c r="AF287">
         <v>7445.3</v>
       </c>
-      <c r="AF287">
+      <c r="AG287">
         <v>13300.599999999999</v>
       </c>
-      <c r="AG287">
+      <c r="AH287">
         <v>14013.900000000001</v>
       </c>
     </row>
-    <row r="288" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A288" s="1">
         <v>46169</v>
       </c>
@@ -24676,17 +24682,17 @@
       <c r="AD288" s="3">
         <v>4.3177289832038177E-3</v>
       </c>
-      <c r="AE288">
+      <c r="AF288">
         <v>6954.375</v>
       </c>
-      <c r="AF288">
+      <c r="AG288">
         <v>11860.349999999999</v>
       </c>
-      <c r="AG288">
+      <c r="AH288">
         <v>14013.900000000001</v>
       </c>
     </row>
-    <row r="289" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A289" s="1">
         <v>46170</v>
       </c>
@@ -24771,17 +24777,17 @@
       <c r="AD289" s="3">
         <v>4.3661630303743195E-3</v>
       </c>
-      <c r="AE289">
+      <c r="AF289">
         <v>7445.3</v>
       </c>
-      <c r="AF289">
+      <c r="AG289">
         <v>11860.349999999999</v>
       </c>
-      <c r="AG289">
+      <c r="AH289">
         <v>14321.875</v>
       </c>
     </row>
-    <row r="290" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A290" s="1">
         <v>46171</v>
       </c>
@@ -24866,17 +24872,17 @@
       <c r="AD290" s="3">
         <v>4.3812275752133532E-3</v>
       </c>
-      <c r="AE290">
+      <c r="AF290">
         <v>7445.3</v>
       </c>
-      <c r="AF290">
+      <c r="AG290">
         <v>11860.349999999999</v>
       </c>
-      <c r="AG290">
+      <c r="AH290">
         <v>14321.875</v>
       </c>
     </row>
-    <row r="291" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A291" s="1">
         <v>46174</v>
       </c>
@@ -24961,17 +24967,17 @@
       <c r="AD291" s="3">
         <v>4.4053629682954971E-3</v>
       </c>
-      <c r="AE291">
+      <c r="AF291">
         <v>8069.3</v>
       </c>
-      <c r="AF291">
+      <c r="AG291">
         <v>11117.65</v>
       </c>
-      <c r="AG291">
+      <c r="AH291">
         <v>14321.875</v>
       </c>
     </row>
-    <row r="292" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A292" s="1">
         <v>46175</v>
       </c>
@@ -25056,17 +25062,17 @@
       <c r="AD292" s="3">
         <v>4.4205111759050199E-3</v>
       </c>
-      <c r="AE292">
+      <c r="AF292">
         <v>8069.3</v>
       </c>
-      <c r="AF292">
+      <c r="AG292">
         <v>9750.8499999999985</v>
       </c>
-      <c r="AG292">
+      <c r="AH292">
         <v>14013.900000000001</v>
       </c>
     </row>
-    <row r="293" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A293" s="1">
         <v>46176</v>
       </c>
@@ -25151,17 +25157,17 @@
       <c r="AD293" s="3">
         <v>4.4427623717123652E-3</v>
       </c>
-      <c r="AE293">
+      <c r="AF293">
         <v>8524.2999999999993</v>
       </c>
-      <c r="AF293">
+      <c r="AG293">
         <v>9750.8499999999985</v>
       </c>
-      <c r="AG293">
+      <c r="AH293">
         <v>14013.900000000001</v>
       </c>
     </row>
-    <row r="294" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A294" s="1">
         <v>46177</v>
       </c>
@@ -25246,17 +25252,17 @@
       <c r="AD294" s="3">
         <v>4.4325367629727049E-3</v>
       </c>
-      <c r="AE294">
+      <c r="AF294">
         <v>8510.5499999999993</v>
       </c>
-      <c r="AF294">
+      <c r="AG294">
         <v>9177.9</v>
       </c>
-      <c r="AG294">
+      <c r="AH294">
         <v>14013.900000000001</v>
       </c>
     </row>
-    <row r="295" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A295" s="1">
         <v>46178</v>
       </c>
@@ -25341,17 +25347,17 @@
       <c r="AD295" s="3">
         <v>4.3803690024608521E-3</v>
       </c>
-      <c r="AE295">
+      <c r="AF295">
         <v>8510.5499999999993</v>
       </c>
-      <c r="AF295">
+      <c r="AG295">
         <v>9177.9</v>
       </c>
-      <c r="AG295">
+      <c r="AH295">
         <v>14013.900000000001</v>
       </c>
     </row>
-    <row r="296" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A296" s="1">
         <v>46181</v>
       </c>
@@ -25436,17 +25442,17 @@
       <c r="AD296" s="3">
         <v>4.39146949030568E-3</v>
       </c>
-      <c r="AE296">
+      <c r="AF296">
         <v>8510.5499999999993</v>
       </c>
-      <c r="AF296">
+      <c r="AG296">
         <v>9177.9</v>
       </c>
-      <c r="AG296">
+      <c r="AH296">
         <v>14321.875</v>
       </c>
     </row>
-    <row r="297" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A297" s="1">
         <v>46182</v>
       </c>
@@ -25531,17 +25537,17 @@
       <c r="AD297" s="3">
         <v>4.439212687896139E-3</v>
       </c>
-      <c r="AE297">
+      <c r="AF297">
         <v>8510.5499999999993</v>
       </c>
-      <c r="AF297">
+      <c r="AG297">
         <v>8937.5</v>
       </c>
-      <c r="AG297">
+      <c r="AH297">
         <v>14321.875</v>
       </c>
     </row>
-    <row r="298" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A298" s="1">
         <v>46183</v>
       </c>
@@ -25626,17 +25632,17 @@
       <c r="AD298" s="3">
         <v>4.4313449707803773E-3</v>
       </c>
-      <c r="AE298">
+      <c r="AF298">
         <v>8510.5499999999993</v>
       </c>
-      <c r="AF298">
+      <c r="AG298">
         <v>8762.25</v>
       </c>
-      <c r="AG298">
+      <c r="AH298">
         <v>14321.875</v>
       </c>
     </row>
-    <row r="299" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A299" s="1">
         <v>46184</v>
       </c>
@@ -25721,17 +25727,17 @@
       <c r="AD299" s="3">
         <v>4.407464832995589E-3</v>
       </c>
-      <c r="AE299">
+      <c r="AF299">
         <v>8510.5499999999993</v>
       </c>
-      <c r="AF299">
+      <c r="AG299">
         <v>8762.25</v>
       </c>
-      <c r="AG299">
+      <c r="AH299">
         <v>14321.875</v>
       </c>
     </row>
-    <row r="300" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A300" s="1">
         <v>46185</v>
       </c>
@@ -25816,17 +25822,17 @@
       <c r="AD300" s="3">
         <v>4.4284303586206207E-3</v>
       </c>
-      <c r="AE300">
-        <v>8762.25</v>
-      </c>
       <c r="AF300">
         <v>8762.25</v>
       </c>
       <c r="AG300">
+        <v>8762.25</v>
+      </c>
+      <c r="AH300">
         <v>14321.875</v>
       </c>
     </row>
-    <row r="301" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A301" s="1">
         <v>46188</v>
       </c>
@@ -25911,17 +25917,17 @@
       <c r="AD301" s="3">
         <v>4.4353907571351965E-3</v>
       </c>
-      <c r="AE301">
+      <c r="AF301">
         <v>9510.4500000000007</v>
       </c>
-      <c r="AF301">
+      <c r="AG301">
         <v>8762.25</v>
       </c>
-      <c r="AG301">
+      <c r="AH301">
         <v>14550.474999999999</v>
       </c>
     </row>
-    <row r="302" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A302" s="1">
         <v>46189</v>
       </c>
@@ -26006,17 +26012,17 @@
       <c r="AD302" s="3">
         <v>4.4265794227736259E-3</v>
       </c>
-      <c r="AE302">
+      <c r="AF302">
         <v>10383.200000000001</v>
       </c>
-      <c r="AF302">
+      <c r="AG302">
         <v>8937.5</v>
       </c>
-      <c r="AG302">
+      <c r="AH302">
         <v>14550.474999999999</v>
       </c>
     </row>
-    <row r="303" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A303" s="1">
         <v>46190</v>
       </c>
@@ -26101,17 +26107,17 @@
       <c r="AD303" s="3">
         <v>4.4070703520019761E-3</v>
       </c>
-      <c r="AE303">
+      <c r="AF303">
         <v>10383.200000000001</v>
       </c>
-      <c r="AF303">
+      <c r="AG303">
         <v>8762.25</v>
       </c>
-      <c r="AG303">
+      <c r="AH303">
         <v>14550.474999999999</v>
       </c>
     </row>
-    <row r="304" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A304" s="1">
         <v>46191</v>
       </c>
@@ -26196,17 +26202,17 @@
       <c r="AD304" s="3">
         <v>4.4001923652234242E-3</v>
       </c>
-      <c r="AE304">
+      <c r="AF304">
         <v>10383.200000000001</v>
       </c>
-      <c r="AF304">
+      <c r="AG304">
         <v>8762.25</v>
       </c>
-      <c r="AG304">
+      <c r="AH304">
         <v>14806.474999999999</v>
       </c>
     </row>
-    <row r="305" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A305" s="1">
         <v>46192</v>
       </c>
@@ -26291,17 +26297,17 @@
       <c r="AD305" s="3">
         <v>4.4083142449644818E-3</v>
       </c>
-      <c r="AE305">
+      <c r="AF305">
         <v>10530.2</v>
       </c>
-      <c r="AF305">
+      <c r="AG305">
         <v>8923</v>
       </c>
-      <c r="AG305">
+      <c r="AH305">
         <v>14806.474999999999</v>
       </c>
     </row>
-    <row r="306" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A306" s="1">
         <v>46195</v>
       </c>
@@ -26386,17 +26392,17 @@
       <c r="AD306" s="3">
         <v>4.4259185822734387E-3</v>
       </c>
-      <c r="AE306">
+      <c r="AF306">
         <v>10530.2</v>
       </c>
-      <c r="AF306">
+      <c r="AG306">
         <v>8762.25</v>
       </c>
-      <c r="AG306">
+      <c r="AH306">
         <v>14550.474999999999</v>
       </c>
     </row>
-    <row r="307" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A307" s="1">
         <v>46196</v>
       </c>
@@ -26481,17 +26487,17 @@
       <c r="AD307" s="3">
         <v>4.4247903513708799E-3</v>
       </c>
-      <c r="AE307">
+      <c r="AF307">
         <v>10746.8</v>
       </c>
-      <c r="AF307">
+      <c r="AG307">
         <v>8762.25</v>
       </c>
-      <c r="AG307">
+      <c r="AH307">
         <v>14550.474999999999</v>
       </c>
     </row>
-    <row r="308" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A308" s="1">
         <v>46197</v>
       </c>
@@ -26576,17 +26582,17 @@
       <c r="AD308" s="3">
         <v>4.4109850913732025E-3</v>
       </c>
-      <c r="AE308">
+      <c r="AF308">
         <v>9286.6</v>
       </c>
-      <c r="AF308">
+      <c r="AG308">
         <v>8762.25</v>
       </c>
-      <c r="AG308">
+      <c r="AH308">
         <v>14321.875</v>
       </c>
     </row>
-    <row r="309" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A309" s="1">
         <v>46198</v>
       </c>
@@ -26671,17 +26677,17 @@
       <c r="AD309" s="3">
         <v>4.4198831704141588E-3</v>
       </c>
-      <c r="AE309">
+      <c r="AF309">
         <v>9286.6</v>
       </c>
-      <c r="AF309">
+      <c r="AG309">
         <v>8731.25</v>
       </c>
-      <c r="AG309">
+      <c r="AH309">
         <v>14321.875</v>
       </c>
     </row>
-    <row r="310" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A310" s="1">
         <v>46199</v>
       </c>
@@ -26766,17 +26772,17 @@
       <c r="AD310" s="3">
         <v>4.4270894021327918E-3</v>
       </c>
-      <c r="AE310">
+      <c r="AF310">
         <v>8923</v>
       </c>
-      <c r="AF310">
+      <c r="AG310">
         <v>8622.25</v>
       </c>
-      <c r="AG310">
+      <c r="AH310">
         <v>14321.875</v>
       </c>
     </row>
-    <row r="311" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A311" s="1">
         <v>46203</v>
       </c>
@@ -26861,17 +26867,17 @@
       <c r="AD311" s="3">
         <v>4.4341780405581701E-3</v>
       </c>
-      <c r="AE311">
+      <c r="AF311">
         <v>9286.6</v>
       </c>
-      <c r="AF311">
+      <c r="AG311">
         <v>8762.25</v>
       </c>
-      <c r="AG311">
+      <c r="AH311">
         <v>14550.474999999999</v>
       </c>
     </row>
-    <row r="312" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A312" s="1">
         <v>46204</v>
       </c>
@@ -26956,17 +26962,17 @@
       <c r="AD312" s="3">
         <v>4.414078096307731E-3</v>
       </c>
-      <c r="AE312">
+      <c r="AF312">
         <v>9286.6</v>
       </c>
-      <c r="AF312">
+      <c r="AG312">
         <v>8762.25</v>
       </c>
-      <c r="AG312">
+      <c r="AH312">
         <v>14550.474999999999</v>
       </c>
     </row>
-    <row r="313" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A313" s="1">
         <v>46205</v>
       </c>
@@ -27051,17 +27057,17 @@
       <c r="AD313" s="3">
         <v>4.4128004170828636E-3</v>
       </c>
-      <c r="AE313">
+      <c r="AF313">
         <v>9858.9750000000004</v>
       </c>
-      <c r="AF313">
+      <c r="AG313">
         <v>8762.25</v>
       </c>
-      <c r="AG313">
+      <c r="AH313">
         <v>14806.474999999999</v>
       </c>
     </row>
-    <row r="314" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A314" s="1">
         <v>46206</v>
       </c>
@@ -27146,17 +27152,17 @@
       <c r="AD314" s="3">
         <v>4.4356846285938719E-3</v>
       </c>
-      <c r="AE314">
+      <c r="AF314">
         <v>9858.9750000000004</v>
       </c>
-      <c r="AF314">
+      <c r="AG314">
         <v>8762.25</v>
       </c>
-      <c r="AG314">
+      <c r="AH314">
         <v>14806.474999999999</v>
       </c>
     </row>
-    <row r="315" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A315" s="1">
         <v>46209</v>
       </c>
@@ -27241,17 +27247,17 @@
       <c r="AD315" s="3">
         <v>4.4151962751246381E-3</v>
       </c>
-      <c r="AE315">
+      <c r="AF315">
         <v>9562.39</v>
       </c>
-      <c r="AF315">
+      <c r="AG315">
         <v>8762.25</v>
       </c>
-      <c r="AG315">
+      <c r="AH315">
         <v>14806.474999999999</v>
       </c>
     </row>
-    <row r="316" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A316" s="1">
         <v>46210</v>
       </c>
@@ -27336,17 +27342,17 @@
       <c r="AD316" s="3">
         <v>4.4066205415318567E-3</v>
       </c>
-      <c r="AE316">
+      <c r="AF316">
         <v>9562.39</v>
       </c>
-      <c r="AF316">
+      <c r="AG316">
         <v>8923</v>
       </c>
-      <c r="AG316">
+      <c r="AH316">
         <v>14806.474999999999</v>
       </c>
     </row>
-    <row r="317" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A317" s="1">
         <v>46211</v>
       </c>
@@ -27431,17 +27437,17 @@
       <c r="AD317" s="3">
         <v>4.3914584660437921E-3</v>
       </c>
-      <c r="AE317">
+      <c r="AF317">
         <v>9918.1650000000009</v>
       </c>
-      <c r="AF317">
+      <c r="AG317">
         <v>9286.6</v>
       </c>
-      <c r="AG317">
+      <c r="AH317">
         <v>14806.474999999999</v>
       </c>
     </row>
-    <row r="318" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A318" s="1">
         <v>46212</v>
       </c>
@@ -27526,17 +27532,17 @@
       <c r="AD318" s="3">
         <v>4.4220013945017742E-3</v>
       </c>
-      <c r="AE318">
+      <c r="AF318">
         <v>10369.674999999999</v>
       </c>
-      <c r="AF318">
+      <c r="AG318">
         <v>9286.6</v>
       </c>
-      <c r="AG318">
+      <c r="AH318">
         <v>15026.974999999999</v>
       </c>
     </row>
-    <row r="319" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A319" s="1">
         <v>46213</v>
       </c>
@@ -27621,17 +27627,17 @@
       <c r="AD319" s="3">
         <v>4.4315152871542288E-3</v>
       </c>
-      <c r="AE319">
+      <c r="AF319">
         <v>10369.674999999999</v>
       </c>
-      <c r="AF319">
+      <c r="AG319">
         <v>9562.39</v>
       </c>
-      <c r="AG319">
+      <c r="AH319">
         <v>15026.974999999999</v>
       </c>
     </row>
-    <row r="320" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A320" s="1">
         <v>46216</v>
       </c>
@@ -27716,17 +27722,17 @@
       <c r="AD320" s="3">
         <v>4.4355424585292985E-3</v>
       </c>
-      <c r="AE320">
+      <c r="AF320">
         <v>10369.674999999999</v>
       </c>
-      <c r="AF320">
+      <c r="AG320">
         <v>9562.39</v>
       </c>
-      <c r="AG320">
+      <c r="AH320">
         <v>15205.65</v>
       </c>
     </row>
-    <row r="321" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A321" s="1">
         <v>46217</v>
       </c>
@@ -27811,17 +27817,17 @@
       <c r="AD321" s="3">
         <v>4.4182750371925383E-3</v>
       </c>
-      <c r="AE321">
+      <c r="AF321">
         <v>10581.865</v>
       </c>
-      <c r="AF321">
+      <c r="AG321">
         <v>9918.1650000000009</v>
       </c>
-      <c r="AG321">
+      <c r="AH321">
         <v>15370.55</v>
       </c>
     </row>
-    <row r="322" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A322" s="1">
         <v>46218</v>
       </c>
@@ -27906,17 +27912,17 @@
       <c r="AD322" s="3">
         <v>4.4347975202651772E-3</v>
       </c>
-      <c r="AE322">
+      <c r="AF322">
         <v>11224.14</v>
       </c>
-      <c r="AF322">
+      <c r="AG322">
         <v>10229.825000000001</v>
       </c>
-      <c r="AG322">
+      <c r="AH322">
         <v>15799.95</v>
       </c>
     </row>
-    <row r="323" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A323" s="1">
         <v>46219</v>
       </c>
@@ -28001,17 +28007,17 @@
       <c r="AD323" s="3">
         <v>4.3850466102320724E-3</v>
       </c>
-      <c r="AE323">
+      <c r="AF323">
         <v>10581.865</v>
       </c>
-      <c r="AF323">
+      <c r="AG323">
         <v>10229.825000000001</v>
       </c>
-      <c r="AG323">
+      <c r="AH323">
         <v>15799.95</v>
       </c>
     </row>
-    <row r="324" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A324" s="1">
         <v>46220</v>
       </c>
@@ -28096,17 +28102,17 @@
       <c r="AD324" s="3">
         <v>4.3645308440761971E-3</v>
       </c>
-      <c r="AE324">
+      <c r="AF324">
         <v>11224.14</v>
       </c>
-      <c r="AF324">
+      <c r="AG324">
         <v>10229.825000000001</v>
       </c>
-      <c r="AG324">
+      <c r="AH324">
         <v>16223.75</v>
       </c>
     </row>
-    <row r="325" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A325" s="1">
         <v>46223</v>
       </c>
@@ -28191,17 +28197,17 @@
       <c r="AD325" s="3">
         <v>4.3522902190965846E-3</v>
       </c>
-      <c r="AE325">
+      <c r="AF325">
         <v>11224.14</v>
       </c>
-      <c r="AF325">
+      <c r="AG325">
         <v>10229.825000000001</v>
       </c>
-      <c r="AG325">
+      <c r="AH325">
         <v>15805.400000000001</v>
       </c>
     </row>
-    <row r="326" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A326" s="1">
         <v>46224</v>
       </c>
@@ -28286,17 +28292,17 @@
       <c r="AD326" s="3">
         <v>4.3095754420263855E-3</v>
       </c>
-      <c r="AE326">
+      <c r="AF326">
         <v>11224.14</v>
       </c>
-      <c r="AF326">
+      <c r="AG326">
         <v>10229.825000000001</v>
       </c>
-      <c r="AG326">
+      <c r="AH326">
         <v>15805.400000000001</v>
       </c>
     </row>
-    <row r="327" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A327" s="1">
         <v>46225</v>
       </c>
@@ -28381,17 +28387,17 @@
       <c r="AD327" s="3">
         <v>4.2885532521210641E-3</v>
       </c>
-      <c r="AE327">
+      <c r="AF327">
         <v>11224.14</v>
       </c>
-      <c r="AF327">
+      <c r="AG327">
         <v>10229.825000000001</v>
       </c>
-      <c r="AG327">
+      <c r="AH327">
         <v>15805.400000000001</v>
       </c>
     </row>
-    <row r="328" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A328" s="1">
         <v>46227</v>
       </c>
@@ -28476,17 +28482,17 @@
       <c r="AD328" s="3">
         <v>4.2802586496971436E-3</v>
       </c>
-      <c r="AE328">
+      <c r="AF328">
         <v>11224.14</v>
       </c>
-      <c r="AF328">
+      <c r="AG328">
         <v>10229.825000000001</v>
       </c>
-      <c r="AG328">
+      <c r="AH328">
         <v>15370.55</v>
       </c>
     </row>
-    <row r="329" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A329" s="1">
         <v>46230</v>
       </c>
@@ -28571,17 +28577,17 @@
       <c r="AD329" s="3">
         <v>4.2558589124322343E-3</v>
       </c>
-      <c r="AE329">
+      <c r="AF329">
         <v>11224.14</v>
       </c>
-      <c r="AF329">
+      <c r="AG329">
         <v>10229.825000000001</v>
       </c>
-      <c r="AG329">
+      <c r="AH329">
         <v>15205.65</v>
       </c>
     </row>
-    <row r="330" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A330" s="1">
         <v>46233</v>
       </c>
@@ -28666,17 +28672,17 @@
       <c r="AD330" s="3">
         <v>4.2825410541806191E-3</v>
       </c>
-      <c r="AE330">
+      <c r="AF330">
         <v>11224.14</v>
       </c>
-      <c r="AF330">
+      <c r="AG330">
         <v>10384.75</v>
       </c>
-      <c r="AG330">
+      <c r="AH330">
         <v>15370.55</v>
       </c>
     </row>
-    <row r="331" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A331" s="1">
         <v>46234</v>
       </c>
@@ -28761,17 +28767,17 @@
       <c r="AD331" s="3">
         <v>4.2758801956083413E-3</v>
       </c>
-      <c r="AE331">
+      <c r="AF331">
         <v>10581.865</v>
       </c>
-      <c r="AF331">
+      <c r="AG331">
         <v>10384.75</v>
       </c>
-      <c r="AG331">
+      <c r="AH331">
         <v>15370.55</v>
       </c>
     </row>
-    <row r="332" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A332" s="1">
         <v>46237</v>
       </c>
@@ -28856,17 +28862,17 @@
       <c r="AD332" s="3">
         <v>4.2418866666079072E-3</v>
       </c>
-      <c r="AE332">
-        <v>10581.865</v>
-      </c>
       <c r="AF332">
         <v>10581.865</v>
       </c>
       <c r="AG332">
+        <v>10581.865</v>
+      </c>
+      <c r="AH332">
         <v>15805.400000000001</v>
       </c>
     </row>
-    <row r="333" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A333" s="1">
         <v>46238</v>
       </c>
@@ -28951,17 +28957,17 @@
       <c r="AD333" s="3">
         <v>4.226411865269065E-3</v>
       </c>
-      <c r="AE333">
-        <v>11224.14</v>
-      </c>
       <c r="AF333">
         <v>11224.14</v>
       </c>
       <c r="AG333">
+        <v>11224.14</v>
+      </c>
+      <c r="AH333">
         <v>16021.7</v>
       </c>
     </row>
-    <row r="334" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A334" s="1">
         <v>46239</v>
       </c>
@@ -29046,17 +29052,17 @@
       <c r="AD334" s="3">
         <v>4.252177166176617E-3</v>
       </c>
-      <c r="AE334">
-        <v>10634.04</v>
-      </c>
       <c r="AF334">
         <v>10634.04</v>
       </c>
       <c r="AG334">
+        <v>10634.04</v>
+      </c>
+      <c r="AH334">
         <v>15597.900000000001</v>
       </c>
     </row>
-    <row r="335" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A335" s="1">
         <v>46241</v>
       </c>
@@ -29141,17 +29147,17 @@
       <c r="AD335" s="3">
         <v>4.3021570951269324E-3</v>
       </c>
-      <c r="AE335">
-        <v>11224.14</v>
-      </c>
       <c r="AF335">
         <v>11224.14</v>
       </c>
       <c r="AG335">
+        <v>11224.14</v>
+      </c>
+      <c r="AH335">
         <v>15370.55</v>
       </c>
     </row>
-    <row r="336" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A336" s="1">
         <v>46244</v>
       </c>
@@ -29236,17 +29242,17 @@
       <c r="AD336" s="3">
         <v>4.2940967576935735E-3</v>
       </c>
-      <c r="AE336">
+      <c r="AF336">
         <v>12257.775</v>
       </c>
-      <c r="AF336">
+      <c r="AG336">
         <v>11899.775</v>
       </c>
-      <c r="AG336">
+      <c r="AH336">
         <v>15370.55</v>
       </c>
     </row>
-    <row r="337" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A337" s="1">
         <v>46245</v>
       </c>
@@ -29331,17 +29337,17 @@
       <c r="AD337" s="3">
         <v>4.2920240104816305E-3</v>
       </c>
-      <c r="AE337">
+      <c r="AF337">
         <v>12257.775</v>
       </c>
-      <c r="AF337">
+      <c r="AG337">
         <v>11899.775</v>
       </c>
-      <c r="AG337">
+      <c r="AH337">
         <v>15319.65</v>
       </c>
     </row>
-    <row r="338" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A338" s="1">
         <v>46246</v>
       </c>
@@ -29426,17 +29432,17 @@
       <c r="AD338" s="3">
         <v>4.2973127044256664E-3</v>
       </c>
-      <c r="AE338">
+      <c r="AF338">
         <v>12257.775</v>
       </c>
-      <c r="AF338">
+      <c r="AG338">
         <v>11224.14</v>
       </c>
-      <c r="AG338">
+      <c r="AH338">
         <v>15213.34</v>
       </c>
     </row>
-    <row r="339" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A339" s="1">
         <v>46247</v>
       </c>
@@ -29521,17 +29527,17 @@
       <c r="AD339" s="3">
         <v>4.3006795222758683E-3</v>
       </c>
-      <c r="AE339">
+      <c r="AF339">
         <v>13631.424999999999</v>
       </c>
-      <c r="AF339">
+      <c r="AG339">
         <v>11899.775</v>
       </c>
-      <c r="AG339">
+      <c r="AH339">
         <v>15213.34</v>
       </c>
     </row>
-    <row r="340" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A340" s="1">
         <v>46248</v>
       </c>
@@ -29616,17 +29622,17 @@
       <c r="AD340" s="3">
         <v>4.3184225006470097E-3</v>
       </c>
-      <c r="AE340">
+      <c r="AF340">
         <v>13742.025000000001</v>
       </c>
-      <c r="AF340">
+      <c r="AG340">
         <v>11899.775</v>
       </c>
-      <c r="AG340">
+      <c r="AH340">
         <v>15213.34</v>
       </c>
     </row>
-    <row r="341" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A341" s="1">
         <v>46251</v>
       </c>
@@ -29711,17 +29717,17 @@
       <c r="AD341" s="3">
         <v>4.3138671498323131E-3</v>
       </c>
-      <c r="AE341">
+      <c r="AF341">
         <v>12817</v>
       </c>
-      <c r="AF341">
+      <c r="AG341">
         <v>11899.775</v>
       </c>
-      <c r="AG341">
+      <c r="AH341">
         <v>15213.34</v>
       </c>
     </row>
-    <row r="342" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A342" s="1">
         <v>46252</v>
       </c>
@@ -29806,17 +29812,17 @@
       <c r="AD342" s="3">
         <v>4.3339980867472937E-3</v>
       </c>
-      <c r="AE342">
+      <c r="AF342">
         <v>12817</v>
       </c>
-      <c r="AF342">
+      <c r="AG342">
         <v>11860.42</v>
       </c>
-      <c r="AG342">
+      <c r="AH342">
         <v>15213.34</v>
       </c>
     </row>
-    <row r="343" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A343" s="1">
         <v>46253</v>
       </c>
@@ -29901,17 +29907,17 @@
       <c r="AD343" s="3">
         <v>4.3146105479269937E-3</v>
       </c>
-      <c r="AE343">
+      <c r="AF343">
         <v>12817</v>
       </c>
-      <c r="AF343">
+      <c r="AG343">
         <v>11951.045</v>
       </c>
-      <c r="AG343">
+      <c r="AH343">
         <v>15319.65</v>
       </c>
     </row>
-    <row r="344" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A344" s="1">
         <v>46254</v>
       </c>
@@ -29996,17 +30002,17 @@
       <c r="AD344" s="3">
         <v>4.32889834199497E-3</v>
       </c>
-      <c r="AE344">
+      <c r="AF344">
         <v>12817</v>
       </c>
-      <c r="AF344">
+      <c r="AG344">
         <v>11951.045</v>
       </c>
-      <c r="AG344">
+      <c r="AH344">
         <v>15319.65</v>
       </c>
     </row>
-    <row r="345" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A345" s="1">
         <v>46255</v>
       </c>
@@ -30091,17 +30097,17 @@
       <c r="AD345" s="3">
         <v>4.3451409109198291E-3</v>
       </c>
-      <c r="AE345">
+      <c r="AF345">
         <v>12817</v>
       </c>
-      <c r="AF345">
+      <c r="AG345">
         <v>11860.42</v>
       </c>
-      <c r="AG345">
+      <c r="AH345">
         <v>15319.65</v>
       </c>
     </row>
-    <row r="346" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A346" s="1">
         <v>46258</v>
       </c>
@@ -30186,17 +30192,17 @@
       <c r="AD346" s="3">
         <v>4.3730180136099658E-3</v>
       </c>
-      <c r="AE346">
+      <c r="AF346">
         <v>13742.025000000001</v>
       </c>
-      <c r="AF346">
+      <c r="AG346">
         <v>11860.42</v>
       </c>
-      <c r="AG346">
+      <c r="AH346">
         <v>15319.65</v>
       </c>
     </row>
-    <row r="347" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A347" s="1">
         <v>46259</v>
       </c>
@@ -30281,17 +30287,17 @@
       <c r="AD347" s="3">
         <v>4.3819000534491082E-3</v>
       </c>
-      <c r="AE347">
+      <c r="AF347">
         <v>13742.025000000001</v>
       </c>
-      <c r="AF347">
+      <c r="AG347">
         <v>11860.42</v>
       </c>
-      <c r="AG347">
+      <c r="AH347">
         <v>15213.34</v>
       </c>
     </row>
-    <row r="348" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A348" s="1">
         <v>46260</v>
       </c>
@@ -30376,17 +30382,17 @@
       <c r="AD348" s="3">
         <v>4.4099527058061704E-3</v>
       </c>
-      <c r="AE348">
+      <c r="AF348">
         <v>12817</v>
       </c>
-      <c r="AF348">
+      <c r="AG348">
         <v>11860.42</v>
       </c>
-      <c r="AG348">
+      <c r="AH348">
         <v>15099.34</v>
       </c>
     </row>
-    <row r="349" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A349" s="1">
         <v>46261</v>
       </c>
@@ -30471,17 +30477,17 @@
       <c r="AD349" s="3">
         <v>4.4365927689549878E-3</v>
       </c>
-      <c r="AE349">
+      <c r="AF349">
         <v>12817</v>
       </c>
-      <c r="AF349">
+      <c r="AG349">
         <v>11224.14</v>
       </c>
-      <c r="AG349">
+      <c r="AH349">
         <v>15099.34</v>
       </c>
     </row>
-    <row r="350" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A350" s="1">
         <v>46262</v>
       </c>
@@ -30566,17 +30572,17 @@
       <c r="AD350" s="3">
         <v>4.4639649849087448E-3</v>
       </c>
-      <c r="AE350">
+      <c r="AF350">
         <v>12817</v>
       </c>
-      <c r="AF350">
+      <c r="AG350">
         <v>11224.14</v>
       </c>
-      <c r="AG350">
+      <c r="AH350">
         <v>15213.34</v>
       </c>
     </row>
-    <row r="351" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A351" s="1">
         <v>46265</v>
       </c>
@@ -30661,17 +30667,17 @@
       <c r="AD351" s="3">
         <v>4.4509239525573688E-3</v>
       </c>
-      <c r="AE351">
+      <c r="AF351">
         <v>12309.045</v>
       </c>
-      <c r="AF351">
+      <c r="AG351">
         <v>11281.305</v>
       </c>
-      <c r="AG351">
+      <c r="AH351">
         <v>15099.34</v>
       </c>
     </row>
-    <row r="352" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A352" s="1">
         <v>46266</v>
       </c>
@@ -30756,17 +30762,17 @@
       <c r="AD352" s="3">
         <v>4.4469262750659747E-3</v>
       </c>
-      <c r="AE352">
+      <c r="AF352">
         <v>12309.045</v>
       </c>
-      <c r="AF352">
+      <c r="AG352">
         <v>11860.42</v>
       </c>
-      <c r="AG352">
+      <c r="AH352">
         <v>15099.34</v>
       </c>
     </row>
-    <row r="353" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A353" s="1">
         <v>46267</v>
       </c>
@@ -30851,17 +30857,17 @@
       <c r="AD353" s="3">
         <v>4.4279744643727359E-3</v>
       </c>
-      <c r="AE353">
+      <c r="AF353">
         <v>12309.045</v>
       </c>
-      <c r="AF353">
+      <c r="AG353">
         <v>11281.305</v>
       </c>
-      <c r="AG353">
+      <c r="AH353">
         <v>15026.974999999999</v>
       </c>
     </row>
-    <row r="354" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A354" s="1">
         <v>46268</v>
       </c>
@@ -30946,17 +30952,17 @@
       <c r="AD354" s="3">
         <v>4.3381653107259248E-3</v>
       </c>
-      <c r="AE354">
+      <c r="AF354">
         <v>11332.575000000001</v>
       </c>
-      <c r="AF354">
+      <c r="AG354">
         <v>11281.305</v>
       </c>
-      <c r="AG354">
+      <c r="AH354">
         <v>15026.974999999999</v>
       </c>
     </row>
-    <row r="355" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A355" s="1">
         <v>46269</v>
       </c>
@@ -31041,17 +31047,17 @@
       <c r="AD355" s="3">
         <v>4.3174597247044588E-3</v>
       </c>
-      <c r="AE355">
+      <c r="AF355">
         <v>11332.575000000001</v>
       </c>
-      <c r="AF355">
+      <c r="AG355">
         <v>11281.305</v>
       </c>
-      <c r="AG355">
+      <c r="AH355">
         <v>15099.34</v>
       </c>
     </row>
-    <row r="356" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A356" s="1">
         <v>46272</v>
       </c>
@@ -31136,17 +31142,17 @@
       <c r="AD356" s="3">
         <v>4.3003425724526248E-3</v>
       </c>
-      <c r="AE356">
+      <c r="AF356">
         <v>10691.205</v>
       </c>
-      <c r="AF356">
+      <c r="AG356">
         <v>10696.294999999998</v>
       </c>
-      <c r="AG356">
+      <c r="AH356">
         <v>15026.974999999999</v>
       </c>
     </row>
-    <row r="357" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A357" s="1">
         <v>46273</v>
       </c>
@@ -31231,17 +31237,17 @@
       <c r="AD357" s="3">
         <v>4.3090953150103466E-3</v>
       </c>
-      <c r="AE357">
+      <c r="AF357">
         <v>10691.205</v>
       </c>
-      <c r="AF357">
+      <c r="AG357">
         <v>10696.294999999998</v>
       </c>
-      <c r="AG357">
+      <c r="AH357">
         <v>15026.974999999999</v>
       </c>
     </row>
-    <row r="358" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A358" s="1">
         <v>46274</v>
       </c>
@@ -31326,17 +31332,17 @@
       <c r="AD358" s="3">
         <v>4.3140984870874803E-3</v>
       </c>
-      <c r="AE358">
+      <c r="AF358">
         <v>10691.205</v>
       </c>
-      <c r="AF358">
+      <c r="AG358">
         <v>10696.294999999998</v>
       </c>
-      <c r="AG358">
+      <c r="AH358">
         <v>14806.474999999999</v>
       </c>
     </row>
-    <row r="359" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A359" s="1">
         <v>46275</v>
       </c>
@@ -31421,17 +31427,17 @@
       <c r="AD359" s="3">
         <v>4.3600937548831107E-3</v>
       </c>
-      <c r="AE359">
+      <c r="AF359">
         <v>10691.205</v>
       </c>
-      <c r="AF359">
+      <c r="AG359">
         <v>10696.294999999998</v>
       </c>
-      <c r="AG359">
+      <c r="AH359">
         <v>14806.474999999999</v>
       </c>
     </row>
-    <row r="360" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A360" s="1">
         <v>46276</v>
       </c>
@@ -31522,17 +31528,17 @@
       <c r="AD360" s="3">
         <v>4.3961724609996337E-3</v>
       </c>
-      <c r="AE360">
+      <c r="AF360">
         <v>10365.225</v>
       </c>
-      <c r="AF360">
+      <c r="AG360">
         <v>10634.04</v>
       </c>
-      <c r="AG360">
+      <c r="AH360">
         <v>14583.625</v>
       </c>
     </row>
-    <row r="361" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A361" s="1">
         <v>46279</v>
       </c>
@@ -31623,17 +31629,17 @@
       <c r="AD361" s="3">
         <v>4.4234507089234813E-3</v>
       </c>
-      <c r="AE361">
+      <c r="AF361">
         <v>10365.225</v>
       </c>
-      <c r="AF361">
+      <c r="AG361">
         <v>10576.775000000001</v>
       </c>
-      <c r="AG361">
+      <c r="AH361">
         <v>14583.625</v>
       </c>
     </row>
-    <row r="362" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A362" s="1">
         <v>46280</v>
       </c>
@@ -31724,17 +31730,20 @@
       <c r="AD362" s="3">
         <v>4.4248186069120688E-3</v>
       </c>
-      <c r="AE362">
+      <c r="AE362" s="3">
+        <v>5.067531715319421E-3</v>
+      </c>
+      <c r="AF362">
         <v>10365.225</v>
       </c>
-      <c r="AF362">
+      <c r="AG362">
         <v>10576.775000000001</v>
       </c>
-      <c r="AG362">
+      <c r="AH362">
         <v>14523.3</v>
       </c>
     </row>
-    <row r="363" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A363" s="1">
         <v>46281</v>
       </c>
@@ -31825,17 +31834,20 @@
       <c r="AD363" s="3">
         <v>4.4933743447705E-3</v>
       </c>
-      <c r="AE363">
+      <c r="AE363" s="3">
+        <v>5.0780246920304247E-3</v>
+      </c>
+      <c r="AF363">
         <v>10365.225</v>
       </c>
-      <c r="AF363">
+      <c r="AG363">
         <v>10634.04</v>
       </c>
-      <c r="AG363">
+      <c r="AH363">
         <v>14583.625</v>
       </c>
     </row>
-    <row r="364" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A364" s="1">
         <v>46282</v>
       </c>
@@ -31926,17 +31938,20 @@
       <c r="AD364" s="3">
         <v>4.5289865051120152E-3</v>
       </c>
-      <c r="AE364">
+      <c r="AE364" s="3">
+        <v>5.0831681096143106E-3</v>
+      </c>
+      <c r="AF364">
         <v>10047.755000000001</v>
       </c>
-      <c r="AF364">
+      <c r="AG364">
         <v>10576.775000000001</v>
       </c>
-      <c r="AG364">
+      <c r="AH364">
         <v>14523.3</v>
       </c>
     </row>
-    <row r="365" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A365" s="1">
         <v>46283</v>
       </c>
@@ -32027,17 +32042,20 @@
       <c r="AD365" s="3">
         <v>4.5941489689594866E-3</v>
       </c>
-      <c r="AE365">
+      <c r="AE365" s="3">
+        <v>5.0965084356062269E-3</v>
+      </c>
+      <c r="AF365">
         <v>9703.1049999999996</v>
       </c>
-      <c r="AF365">
+      <c r="AG365">
         <v>10576.775000000001</v>
       </c>
-      <c r="AG365">
+      <c r="AH365">
         <v>14321.875</v>
       </c>
     </row>
-    <row r="366" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A366" s="1">
         <v>46286</v>
       </c>
@@ -32128,17 +32146,20 @@
       <c r="AD366" s="3">
         <v>4.6658288249278946E-3</v>
       </c>
-      <c r="AE366">
+      <c r="AE366" s="3">
+        <v>5.1051661980878755E-3</v>
+      </c>
+      <c r="AF366">
         <v>9703.1049999999996</v>
       </c>
-      <c r="AF366">
+      <c r="AG366">
         <v>10634.04</v>
       </c>
-      <c r="AG366">
+      <c r="AH366">
         <v>14523.3</v>
       </c>
     </row>
-    <row r="367" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A367" s="1">
         <v>46287</v>
       </c>
@@ -32229,13 +32250,16 @@
       <c r="AD367" s="3">
         <v>4.7392286830733087E-3</v>
       </c>
-      <c r="AE367">
+      <c r="AE367" s="3">
+        <v>5.1114920139901671E-3</v>
+      </c>
+      <c r="AF367">
         <v>10047.755000000001</v>
       </c>
-      <c r="AF367">
+      <c r="AG367">
         <v>10696.294999999998</v>
       </c>
-      <c r="AG367">
+      <c r="AH367">
         <v>14321.875</v>
       </c>
     </row>

--- a/Data/Data-ETFPESOV.xlsx
+++ b/Data/Data-ETFPESOV.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Desktop\Dashboards\ETFPESOV\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B9CE4C2-8AFF-4B35-95B7-1892C6BCBAD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6ADAB20C-CF59-4CDA-90D1-19D939734D26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{F6F75CCC-009E-413C-B55D-A670828334F1}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="36">
   <si>
     <t>Fecha</t>
   </si>
@@ -144,6 +144,9 @@
   </si>
   <si>
     <t>Dislocation 360 días</t>
+  </si>
+  <si>
+    <t>Vol Mediana 360 días</t>
   </si>
 </sst>
 </file>
@@ -527,13 +530,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E89EACC1-FF2B-4ECD-9B28-49A6BC374F12}">
-  <dimension ref="A1:AH367"/>
+  <dimension ref="A1:AI367"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="27" max="31" width="11.5546875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -636,8 +639,11 @@
       <c r="AH1" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="2" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AI1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>45748</v>
       </c>
@@ -683,14 +689,20 @@
       <c r="O2">
         <v>6.569</v>
       </c>
+      <c r="X2">
+        <v>100.01</v>
+      </c>
       <c r="Y2" s="2">
         <v>0</v>
       </c>
       <c r="Z2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AA2" s="3">
+        <v>9.5943256973129998E-4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>45749</v>
       </c>
@@ -749,7 +761,7 @@
         <v>1.2143671677051771E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>45750</v>
       </c>
@@ -808,7 +820,7 @@
         <v>9.1175034119250764E-3</v>
       </c>
     </row>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>45751</v>
       </c>
@@ -867,7 +879,7 @@
         <v>1.1159691476292588E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>45754</v>
       </c>
@@ -926,7 +938,7 @@
         <v>1.3318351860941879E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>45755</v>
       </c>
@@ -985,7 +997,7 @@
         <v>1.4496105894190592E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>45756</v>
       </c>
@@ -1044,7 +1056,7 @@
         <v>1.059531283173043E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>45757</v>
       </c>
@@ -1103,7 +1115,7 @@
         <v>9.5170229436190024E-3</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>45758</v>
       </c>
@@ -1162,7 +1174,7 @@
         <v>1.2588309241094331E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>45761</v>
       </c>
@@ -1221,7 +1233,7 @@
         <v>3.6875895667234371E-3</v>
       </c>
     </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>45762</v>
       </c>
@@ -1280,7 +1292,7 @@
         <v>4.4103347852244568E-3</v>
       </c>
     </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>45763</v>
       </c>
@@ -1339,7 +1351,7 @@
         <v>1.069542784982902E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>45768</v>
       </c>
@@ -1398,7 +1410,7 @@
         <v>3.2775521211678704E-3</v>
       </c>
     </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>45769</v>
       </c>
@@ -1457,7 +1469,7 @@
         <v>8.2411514863298674E-3</v>
       </c>
     </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>45770</v>
       </c>
@@ -2344,6 +2356,9 @@
       <c r="AA30" s="3">
         <v>5.6980368512211665E-3</v>
       </c>
+      <c r="AF30">
+        <v>9647.375</v>
+      </c>
     </row>
     <row r="31" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
@@ -2409,8 +2424,11 @@
       <c r="AA31" s="3">
         <v>4.8608982705755643E-4</v>
       </c>
+      <c r="AB31" s="3">
+        <v>6.1691606704048236E-3</v>
+      </c>
       <c r="AF31">
-        <v>9647.375</v>
+        <v>10502.5</v>
       </c>
     </row>
     <row r="32" spans="1:32" x14ac:dyDescent="0.3">
@@ -2481,7 +2499,7 @@
         <v>6.2665012949956562E-3</v>
       </c>
       <c r="AF32">
-        <v>10502.5</v>
+        <v>9670</v>
       </c>
     </row>
     <row r="33" spans="1:32" x14ac:dyDescent="0.3">
@@ -2549,7 +2567,7 @@
         <v>3.0592671624141143E-3</v>
       </c>
       <c r="AB33" s="3">
-        <v>6.1630421294285092E-3</v>
+        <v>5.9636878111744007E-3</v>
       </c>
       <c r="AF33">
         <v>9670</v>
@@ -2620,7 +2638,7 @@
         <v>4.8167779345216211E-3</v>
       </c>
       <c r="AB34" s="3">
-        <v>5.9266907183791497E-3</v>
+        <v>5.8203302952609523E-3</v>
       </c>
       <c r="AF34">
         <v>9670</v>
@@ -2691,10 +2709,10 @@
         <v>1.6616003810829838E-3</v>
       </c>
       <c r="AB35" s="3">
-        <v>5.6861777173842437E-3</v>
+        <v>5.5037272587539652E-3</v>
       </c>
       <c r="AF35">
-        <v>9670</v>
+        <v>9151.625</v>
       </c>
     </row>
     <row r="36" spans="1:32" x14ac:dyDescent="0.3">
@@ -2762,10 +2780,10 @@
         <v>8.1452331859104277E-3</v>
       </c>
       <c r="AB36" s="3">
-        <v>5.5889371273719155E-3</v>
+        <v>5.3312899695862502E-3</v>
       </c>
       <c r="AF36">
-        <v>9151.625</v>
+        <v>8644.5</v>
       </c>
     </row>
     <row r="37" spans="1:32" x14ac:dyDescent="0.3">
@@ -2833,10 +2851,10 @@
         <v>3.0982578989338094E-3</v>
       </c>
       <c r="AB37" s="3">
-        <v>5.259256676984559E-3</v>
+        <v>4.9513617030776912E-3</v>
       </c>
       <c r="AF37">
-        <v>8644.5</v>
+        <v>7933</v>
       </c>
     </row>
     <row r="38" spans="1:32" x14ac:dyDescent="0.3">
@@ -2904,7 +2922,7 @@
         <v>1.9101435813166923E-3</v>
       </c>
       <c r="AB38" s="3">
-        <v>4.8532578926983039E-3</v>
+        <v>4.6618560613972326E-3</v>
       </c>
       <c r="AF38">
         <v>7933</v>
@@ -2975,10 +2993,10 @@
         <v>5.186648952267503E-3</v>
       </c>
       <c r="AB39" s="3">
-        <v>4.6787848643285324E-3</v>
+        <v>4.5175102616855168E-3</v>
       </c>
       <c r="AF39">
-        <v>7933</v>
+        <v>7645.5</v>
       </c>
     </row>
     <row r="40" spans="1:32" x14ac:dyDescent="0.3">
@@ -3046,7 +3064,7 @@
         <v>2.7796600195073573E-4</v>
       </c>
       <c r="AB40" s="3">
-        <v>4.3807507694360072E-3</v>
+        <v>4.1071654870473966E-3</v>
       </c>
       <c r="AF40">
         <v>7645.5</v>
@@ -3117,7 +3135,7 @@
         <v>1.2061844537269328E-2</v>
       </c>
       <c r="AB41" s="3">
-        <v>4.3637680370545552E-3</v>
+        <v>4.3863073193989265E-3</v>
       </c>
       <c r="AF41">
         <v>7645.5</v>
@@ -3188,10 +3206,10 @@
         <v>4.6197709700190881E-3</v>
       </c>
       <c r="AB42" s="3">
-        <v>4.393838404902802E-3</v>
+        <v>4.3932885255587471E-3</v>
       </c>
       <c r="AF42">
-        <v>7645.5</v>
+        <v>7498.4</v>
       </c>
     </row>
     <row r="43" spans="1:32" x14ac:dyDescent="0.3">
@@ -3259,7 +3277,7 @@
         <v>5.5373914082157416E-3</v>
       </c>
       <c r="AB43" s="3">
-        <v>4.4301950701605862E-3</v>
+        <v>4.2213539775049717E-3</v>
       </c>
       <c r="AF43">
         <v>7498.4</v>
@@ -3330,10 +3348,10 @@
         <v>1.6322361831814236E-3</v>
       </c>
       <c r="AB44" s="3">
-        <v>4.137834048655825E-3</v>
+        <v>4.1665101129054229E-3</v>
       </c>
       <c r="AF44">
-        <v>7498.4</v>
+        <v>7645.5</v>
       </c>
     </row>
     <row r="45" spans="1:32" x14ac:dyDescent="0.3">
@@ -3401,10 +3419,10 @@
         <v>1.3174188091285788E-2</v>
       </c>
       <c r="AB45" s="3">
-        <v>4.4570803702725318E-3</v>
+        <v>4.3309446664039535E-3</v>
       </c>
       <c r="AF45">
-        <v>7645.5</v>
+        <v>7498.4</v>
       </c>
     </row>
     <row r="46" spans="1:32" x14ac:dyDescent="0.3">
@@ -3472,7 +3490,7 @@
         <v>1.3175386305022463E-2</v>
       </c>
       <c r="AB46" s="3">
-        <v>4.6162492353916474E-3</v>
+        <v>4.4425912442717539E-3</v>
       </c>
       <c r="AF46">
         <v>7498.4</v>
@@ -3543,10 +3561,10 @@
         <v>7.1279548175617879E-4</v>
       </c>
       <c r="AB47" s="3">
-        <v>4.3222752519325421E-3</v>
+        <v>4.2614250451117148E-3</v>
       </c>
       <c r="AF47">
-        <v>7498.4</v>
+        <v>7293.4</v>
       </c>
     </row>
     <row r="48" spans="1:32" x14ac:dyDescent="0.3">
@@ -3614,10 +3632,10 @@
         <v>1.738935209842829E-2</v>
       </c>
       <c r="AB48" s="3">
-        <v>4.6849065629606364E-3</v>
+        <v>4.585352463007941E-3</v>
       </c>
       <c r="AF48">
-        <v>7293.4</v>
+        <v>7134.1</v>
       </c>
     </row>
     <row r="49" spans="1:33" x14ac:dyDescent="0.3">
@@ -3685,10 +3703,10 @@
         <v>6.2320122930968891E-3</v>
       </c>
       <c r="AB49" s="3">
-        <v>4.6384705220430689E-3</v>
+        <v>4.7719936208826348E-3</v>
       </c>
       <c r="AF49">
-        <v>7134.1</v>
+        <v>7293.4</v>
       </c>
     </row>
     <row r="50" spans="1:33" x14ac:dyDescent="0.3">
@@ -3756,10 +3774,10 @@
         <v>1.4989923102427527E-3</v>
       </c>
       <c r="AB50" s="3">
-        <v>4.6664129334426383E-3</v>
+        <v>4.749115656668087E-3</v>
       </c>
       <c r="AF50">
-        <v>7293.4</v>
+        <v>7134.1</v>
       </c>
     </row>
     <row r="51" spans="1:33" x14ac:dyDescent="0.3">
@@ -3827,7 +3845,7 @@
         <v>2.0820899514965463E-2</v>
       </c>
       <c r="AB51" s="3">
-        <v>5.2675602972583249E-3</v>
+        <v>5.441450655600707E-3</v>
       </c>
       <c r="AF51">
         <v>7134.1</v>
@@ -3898,7 +3916,7 @@
         <v>8.1658328094259547E-3</v>
       </c>
       <c r="AB52" s="3">
-        <v>5.5293339508853921E-3</v>
+        <v>5.536739343429316E-3</v>
       </c>
       <c r="AF52">
         <v>7134.1</v>
@@ -3969,10 +3987,10 @@
         <v>4.82401223979112E-3</v>
       </c>
       <c r="AB53" s="3">
-        <v>5.5137481465377617E-3</v>
+        <v>5.6466869656863171E-3</v>
       </c>
       <c r="AF53">
-        <v>7134.1</v>
+        <v>7293.4</v>
       </c>
     </row>
     <row r="54" spans="1:33" x14ac:dyDescent="0.3">
@@ -4040,7 +4058,7 @@
         <v>1.7424001747646689E-2</v>
       </c>
       <c r="AB54" s="3">
-        <v>6.0266003457495549E-3</v>
+        <v>6.2022388839658603E-3</v>
       </c>
       <c r="AF54">
         <v>7293.4</v>
@@ -4111,7 +4129,7 @@
         <v>4.6253260771513816E-3</v>
       </c>
       <c r="AB55" s="3">
-        <v>6.1513707289073292E-3</v>
+        <v>6.2435876076077403E-3</v>
       </c>
       <c r="AF55">
         <v>7293.4</v>
@@ -4182,10 +4200,10 @@
         <v>1.6456215444858424E-2</v>
       </c>
       <c r="AB56" s="3">
-        <v>6.5730272152609882E-3</v>
+        <v>6.7046016180196972E-3</v>
       </c>
       <c r="AF56">
-        <v>7293.4</v>
+        <v>7454.7749999999996</v>
       </c>
     </row>
     <row r="57" spans="1:33" x14ac:dyDescent="0.3">
@@ -4253,10 +4271,10 @@
         <v>1.7918053081034113E-3</v>
       </c>
       <c r="AB57" s="3">
-        <v>6.5461243176998174E-3</v>
+        <v>6.5879057413351467E-3</v>
       </c>
       <c r="AF57">
-        <v>7454.7749999999996</v>
+        <v>7293.4</v>
       </c>
     </row>
     <row r="58" spans="1:33" x14ac:dyDescent="0.3">
@@ -4324,10 +4342,10 @@
         <v>1.6153696097455206E-2</v>
       </c>
       <c r="AB58" s="3">
-        <v>6.8964796237906325E-3</v>
+        <v>7.023272136394961E-3</v>
       </c>
       <c r="AF58">
-        <v>7293.4</v>
+        <v>7310.0249999999996</v>
       </c>
     </row>
     <row r="59" spans="1:33" x14ac:dyDescent="0.3">
@@ -4395,7 +4413,7 @@
         <v>1.1027921919692929E-3</v>
       </c>
       <c r="AB59" s="3">
-        <v>6.8322889123812293E-3</v>
+        <v>6.8539408064672586E-3</v>
       </c>
       <c r="AF59">
         <v>7310.0249999999996</v>
@@ -4469,10 +4487,13 @@
         <v>2.1037111933324137E-2</v>
       </c>
       <c r="AB60" s="3">
-        <v>7.3114624557207063E-3</v>
+        <v>7.3652433092040248E-3</v>
       </c>
       <c r="AF60">
         <v>7310.0249999999996</v>
+      </c>
+      <c r="AG60">
+        <v>7645.5</v>
       </c>
     </row>
     <row r="61" spans="1:33" x14ac:dyDescent="0.3">
@@ -4546,10 +4567,13 @@
         <v>7.9213053128057709E-3</v>
       </c>
       <c r="AB61" s="3">
-        <v>7.3831807931911773E-3</v>
+        <v>7.6130838253956317E-3</v>
+      </c>
+      <c r="AC61" s="3">
+        <v>6.8911222479002276E-3</v>
       </c>
       <c r="AF61">
-        <v>7310.0249999999996</v>
+        <v>7191.625</v>
       </c>
       <c r="AG61">
         <v>7645.5</v>
@@ -4626,16 +4650,16 @@
         <v>1.5854809244144619E-3</v>
       </c>
       <c r="AB62" s="3">
-        <v>7.4186450221381747E-3</v>
+        <v>7.5366114792942383E-3</v>
       </c>
       <c r="AC62" s="3">
         <v>6.9015563871449468E-3</v>
       </c>
       <c r="AF62">
-        <v>7191.625</v>
+        <v>6920.8600000000006</v>
       </c>
       <c r="AG62">
-        <v>7645.5</v>
+        <v>7541.375</v>
       </c>
     </row>
     <row r="63" spans="1:33" x14ac:dyDescent="0.3">
@@ -4709,7 +4733,7 @@
         <v>7.4023049905880267E-4</v>
       </c>
       <c r="AB63" s="3">
-        <v>7.317373383157611E-3</v>
+        <v>7.4593102571823946E-3</v>
       </c>
       <c r="AC63" s="3">
         <v>6.7114990341783972E-3</v>
@@ -4792,16 +4816,16 @@
         <v>1.0746087298207918E-4</v>
       </c>
       <c r="AB64" s="3">
-        <v>7.2221538254339974E-3</v>
+        <v>7.3023330217977427E-3</v>
       </c>
       <c r="AC64" s="3">
         <v>6.5613316585293475E-3</v>
       </c>
       <c r="AF64">
-        <v>6920.8600000000006</v>
+        <v>6652.2350000000006</v>
       </c>
       <c r="AG64">
-        <v>7541.375</v>
+        <v>7454.7749999999996</v>
       </c>
     </row>
     <row r="65" spans="1:33" x14ac:dyDescent="0.3">
@@ -4875,7 +4899,7 @@
         <v>1.4181012409169025E-3</v>
       </c>
       <c r="AB65" s="3">
-        <v>7.1125190933822319E-3</v>
+        <v>7.2942163837922073E-3</v>
       </c>
       <c r="AC65" s="3">
         <v>6.3989718212730858E-3</v>
@@ -4884,7 +4908,7 @@
         <v>6652.2350000000006</v>
       </c>
       <c r="AG65">
-        <v>7454.7749999999996</v>
+        <v>7310.0249999999996</v>
       </c>
     </row>
     <row r="66" spans="1:33" x14ac:dyDescent="0.3">
@@ -4958,7 +4982,7 @@
         <v>1.1198104782309315E-2</v>
       </c>
       <c r="AB66" s="3">
-        <v>7.4201482676153393E-3</v>
+        <v>7.3959787703388362E-3</v>
       </c>
       <c r="AC66" s="3">
         <v>6.3636343699625432E-3</v>
@@ -5041,7 +5065,7 @@
         <v>7.7083296023894299E-4</v>
       </c>
       <c r="AB67" s="3">
-        <v>7.182264389367872E-3</v>
+        <v>7.3183979390490077E-3</v>
       </c>
       <c r="AC67" s="3">
         <v>6.1348798210633495E-3</v>
@@ -5050,7 +5074,7 @@
         <v>6652.2350000000006</v>
       </c>
       <c r="AG67">
-        <v>7310.0249999999996</v>
+        <v>7191.625</v>
       </c>
     </row>
     <row r="68" spans="1:33" x14ac:dyDescent="0.3">
@@ -5124,7 +5148,7 @@
         <v>1.5235141386212958E-2</v>
       </c>
       <c r="AB68" s="3">
-        <v>7.5737767599252642E-3</v>
+        <v>7.7625645325455498E-3</v>
       </c>
       <c r="AC68" s="3">
         <v>6.2122102969713912E-3</v>
@@ -5133,7 +5157,7 @@
         <v>6652.2350000000006</v>
       </c>
       <c r="AG68">
-        <v>7191.625</v>
+        <v>7134.1</v>
       </c>
     </row>
     <row r="69" spans="1:33" x14ac:dyDescent="0.3">
@@ -5207,7 +5231,7 @@
         <v>9.9434659466623998E-4</v>
       </c>
       <c r="AB69" s="3">
-        <v>7.5442349216462172E-3</v>
+        <v>7.622821120625508E-3</v>
       </c>
       <c r="AC69" s="3">
         <v>6.0701656911555119E-3</v>
@@ -5216,7 +5240,7 @@
         <v>6652.2350000000006</v>
       </c>
       <c r="AG69">
-        <v>7134.1</v>
+        <v>7040.1</v>
       </c>
     </row>
     <row r="70" spans="1:33" x14ac:dyDescent="0.3">
@@ -5290,13 +5314,13 @@
         <v>1.7749581425314909E-2</v>
       </c>
       <c r="AB70" s="3">
-        <v>7.9494908078735528E-3</v>
+        <v>8.2052083014043133E-3</v>
       </c>
       <c r="AC70" s="3">
         <v>6.1561868942258549E-3</v>
       </c>
       <c r="AF70">
-        <v>6652.2350000000006</v>
+        <v>6625.6100000000006</v>
       </c>
       <c r="AG70">
         <v>7040.1</v>
@@ -5373,7 +5397,7 @@
         <v>8.8946651819021838E-4</v>
       </c>
       <c r="AB71" s="3">
-        <v>7.9692166309780522E-3</v>
+        <v>7.8327957007683427E-3</v>
       </c>
       <c r="AC71" s="3">
         <v>6.1095515100836346E-3</v>
@@ -5456,16 +5480,16 @@
         <v>1.3620492971663456E-2</v>
       </c>
       <c r="AB72" s="3">
-        <v>8.0194956127327011E-3</v>
+        <v>8.1328197674898229E-3</v>
       </c>
       <c r="AC72" s="3">
         <v>6.2630541465242846E-3</v>
       </c>
       <c r="AF72">
-        <v>6625.6100000000006</v>
+        <v>6584</v>
       </c>
       <c r="AG72">
-        <v>7040.1</v>
+        <v>6942</v>
       </c>
     </row>
     <row r="73" spans="1:33" x14ac:dyDescent="0.3">
@@ -5539,7 +5563,7 @@
         <v>1.2677045054945824E-2</v>
       </c>
       <c r="AB73" s="3">
-        <v>8.2794076799884032E-3</v>
+        <v>8.3708082223808242E-3</v>
       </c>
       <c r="AC73" s="3">
         <v>6.296081099942898E-3</v>
@@ -5622,7 +5646,7 @@
         <v>2.1130175640990956E-3</v>
       </c>
       <c r="AB74" s="3">
-        <v>8.1689440075975433E-3</v>
+        <v>8.3868342684114139E-3</v>
       </c>
       <c r="AC74" s="3">
         <v>6.2766721906584184E-3</v>
@@ -5631,7 +5655,7 @@
         <v>6584</v>
       </c>
       <c r="AG74">
-        <v>6942</v>
+        <v>7040.1</v>
       </c>
     </row>
     <row r="75" spans="1:33" x14ac:dyDescent="0.3">
@@ -5705,16 +5729,16 @@
         <v>5.2101071453212189E-3</v>
       </c>
       <c r="AB75" s="3">
-        <v>8.284359199924634E-3</v>
+        <v>8.121364903545928E-3</v>
       </c>
       <c r="AC75" s="3">
         <v>6.2261547849749412E-3</v>
       </c>
       <c r="AF75">
-        <v>6584</v>
+        <v>6488.5</v>
       </c>
       <c r="AG75">
-        <v>7040.1</v>
+        <v>6942</v>
       </c>
     </row>
     <row r="76" spans="1:33" x14ac:dyDescent="0.3">
@@ -5788,7 +5812,7 @@
         <v>5.6631275262259972E-3</v>
       </c>
       <c r="AB76" s="3">
-        <v>8.0420669236323829E-3</v>
+        <v>7.8709562775860463E-3</v>
       </c>
       <c r="AC76" s="3">
         <v>6.1567737609288997E-3</v>
@@ -5871,16 +5895,16 @@
         <v>7.6669360929162433E-3</v>
       </c>
       <c r="AB77" s="3">
-        <v>7.8643749813063751E-3</v>
+        <v>8.1027609646247157E-3</v>
       </c>
       <c r="AC77" s="3">
         <v>6.1820930048682148E-3</v>
       </c>
       <c r="AF77">
-        <v>6488.5</v>
+        <v>6584</v>
       </c>
       <c r="AG77">
-        <v>6942</v>
+        <v>6852.875</v>
       </c>
     </row>
     <row r="78" spans="1:33" x14ac:dyDescent="0.3">
@@ -5954,7 +5978,7 @@
         <v>5.8544668889426443E-3</v>
       </c>
       <c r="AB78" s="3">
-        <v>8.0302353492801327E-3</v>
+        <v>7.7182647909751932E-3</v>
       </c>
       <c r="AC78" s="3">
         <v>6.1518086269915671E-3</v>
@@ -5963,7 +5987,7 @@
         <v>6584</v>
       </c>
       <c r="AG78">
-        <v>6852.875</v>
+        <v>6737.7350000000006</v>
       </c>
     </row>
     <row r="79" spans="1:33" x14ac:dyDescent="0.3">
@@ -6037,13 +6061,13 @@
         <v>9.6345373368735832E-3</v>
       </c>
       <c r="AB79" s="3">
-        <v>7.7800800343912702E-3</v>
+        <v>7.8316822924344165E-3</v>
       </c>
       <c r="AC79" s="3">
         <v>6.3018379566585252E-3</v>
       </c>
       <c r="AF79">
-        <v>6584</v>
+        <v>6495.5</v>
       </c>
       <c r="AG79">
         <v>6737.7350000000006</v>
@@ -6120,13 +6144,13 @@
         <v>8.6113497955747631E-3</v>
       </c>
       <c r="AB80" s="3">
-        <v>7.8568328570518473E-3</v>
+        <v>8.0687608752788176E-3</v>
       </c>
       <c r="AC80" s="3">
         <v>6.4089382659734519E-3</v>
       </c>
       <c r="AF80">
-        <v>6495.5</v>
+        <v>6584</v>
       </c>
       <c r="AG80">
         <v>6737.7350000000006</v>
@@ -6203,7 +6227,7 @@
         <v>1.4897036118562745E-2</v>
       </c>
       <c r="AB81" s="3">
-        <v>8.289027818610557E-3</v>
+        <v>7.8712987620653922E-3</v>
       </c>
       <c r="AC81" s="3">
         <v>6.65637470883305E-3</v>
@@ -6286,7 +6310,7 @@
         <v>1.6880287237661218E-2</v>
       </c>
       <c r="AB82" s="3">
-        <v>8.1619112935362257E-3</v>
+        <v>8.1617805763399016E-3</v>
       </c>
       <c r="AC82" s="3">
         <v>6.8492599598846092E-3</v>
@@ -6369,7 +6393,7 @@
         <v>1.633765551446742E-2</v>
       </c>
       <c r="AB83" s="3">
-        <v>8.4255184775698221E-3</v>
+        <v>8.5455686854957781E-3</v>
       </c>
       <c r="AC83" s="3">
         <v>7.0961278255910476E-3</v>
@@ -6378,7 +6402,7 @@
         <v>6584</v>
       </c>
       <c r="AG83">
-        <v>6737.7350000000006</v>
+        <v>6852.875</v>
       </c>
     </row>
     <row r="84" spans="1:33" x14ac:dyDescent="0.3">
@@ -6452,16 +6476,16 @@
         <v>4.7648494685091913E-3</v>
       </c>
       <c r="AB84" s="3">
-        <v>8.4236100010768554E-3</v>
+        <v>8.1235969428578615E-3</v>
       </c>
       <c r="AC84" s="3">
         <v>7.1629179134118613E-3</v>
       </c>
       <c r="AF84">
-        <v>6584</v>
+        <v>6495.5</v>
       </c>
       <c r="AG84">
-        <v>6852.875</v>
+        <v>6737.7350000000006</v>
       </c>
     </row>
     <row r="85" spans="1:33" x14ac:dyDescent="0.3">
@@ -6535,7 +6559,7 @@
         <v>1.9833305209906338E-2</v>
       </c>
       <c r="AB85" s="3">
-        <v>8.5013294676013606E-3</v>
+        <v>8.6305295806163602E-3</v>
       </c>
       <c r="AC85" s="3">
         <v>7.4370585941120502E-3</v>
@@ -6618,7 +6642,7 @@
         <v>7.1738092475146509E-3</v>
       </c>
       <c r="AB86" s="3">
-        <v>8.5835386021292075E-3</v>
+        <v>8.3211160407049012E-3</v>
       </c>
       <c r="AC86" s="3">
         <v>7.5128588293622992E-3</v>
@@ -6627,7 +6651,7 @@
         <v>6495.5</v>
       </c>
       <c r="AG86">
-        <v>6737.7350000000006</v>
+        <v>6808.45</v>
       </c>
     </row>
     <row r="87" spans="1:33" x14ac:dyDescent="0.3">
@@ -6701,13 +6725,13 @@
         <v>1.5129667444924277E-2</v>
       </c>
       <c r="AB87" s="3">
-        <v>8.5407467311635916E-3</v>
+        <v>8.7657114452655959E-3</v>
       </c>
       <c r="AC87" s="3">
         <v>7.6768085933003717E-3</v>
       </c>
       <c r="AF87">
-        <v>6495.5</v>
+        <v>6695.8249999999998</v>
       </c>
       <c r="AG87">
         <v>6808.45</v>
@@ -6784,7 +6808,7 @@
         <v>1.487955955605913E-3</v>
       </c>
       <c r="AB88" s="3">
-        <v>8.5309451391475423E-3</v>
+        <v>8.2768534405372862E-3</v>
       </c>
       <c r="AC88" s="3">
         <v>7.650062788466124E-3</v>
@@ -6793,7 +6817,7 @@
         <v>6695.8249999999998</v>
       </c>
       <c r="AG88">
-        <v>6808.45</v>
+        <v>6852.875</v>
       </c>
     </row>
     <row r="89" spans="1:33" x14ac:dyDescent="0.3">
@@ -6867,16 +6891,16 @@
         <v>5.553457335918055E-3</v>
       </c>
       <c r="AB89" s="3">
-        <v>8.1890019532915061E-3</v>
+        <v>8.4252089453355789E-3</v>
       </c>
       <c r="AC89" s="3">
         <v>7.6395748759014188E-3</v>
       </c>
       <c r="AF89">
-        <v>6695.8249999999998</v>
+        <v>6808.45</v>
       </c>
       <c r="AG89">
-        <v>6852.875</v>
+        <v>6942</v>
       </c>
     </row>
     <row r="90" spans="1:33" x14ac:dyDescent="0.3">
@@ -6950,16 +6974,16 @@
         <v>4.5864450717943983E-3</v>
       </c>
       <c r="AB90" s="3">
-        <v>8.3013778526407015E-3</v>
+        <v>7.8768533832845877E-3</v>
       </c>
       <c r="AC90" s="3">
         <v>7.6210483462443059E-3</v>
       </c>
       <c r="AF90">
-        <v>6808.45</v>
+        <v>6695.8249999999998</v>
       </c>
       <c r="AG90">
-        <v>6942</v>
+        <v>6852.875</v>
       </c>
     </row>
     <row r="91" spans="1:33" x14ac:dyDescent="0.3">
@@ -7033,7 +7057,7 @@
         <v>2.603154769207916E-3</v>
       </c>
       <c r="AB91" s="3">
-        <v>7.7067340731530824E-3</v>
+        <v>7.6995816984979926E-3</v>
       </c>
       <c r="AC91" s="3">
         <v>7.6563327619468121E-3</v>
@@ -7042,7 +7066,7 @@
         <v>6695.8249999999998</v>
       </c>
       <c r="AG91">
-        <v>6852.875</v>
+        <v>6808.45</v>
       </c>
     </row>
     <row r="92" spans="1:33" x14ac:dyDescent="0.3">
@@ -7116,13 +7140,13 @@
         <v>1.5727247322894211E-3</v>
       </c>
       <c r="AB92" s="3">
-        <v>7.5019411512009422E-3</v>
+        <v>7.6991564920938244E-3</v>
       </c>
       <c r="AC92" s="3">
         <v>7.6178839856940314E-3</v>
       </c>
       <c r="AF92">
-        <v>6695.8249999999998</v>
+        <v>6808.45</v>
       </c>
       <c r="AG92">
         <v>6808.45</v>
@@ -7199,16 +7223,16 @@
         <v>1.4021252325873146E-3</v>
       </c>
       <c r="AB93" s="3">
-        <v>7.4960264514645821E-3</v>
+        <v>7.7212196498781084E-3</v>
       </c>
       <c r="AC93" s="3">
         <v>7.5902649535302515E-3</v>
       </c>
       <c r="AF93">
-        <v>6808.45</v>
+        <v>6695.8249999999998</v>
       </c>
       <c r="AG93">
-        <v>6808.45</v>
+        <v>6737.4349999999995</v>
       </c>
     </row>
     <row r="94" spans="1:33" x14ac:dyDescent="0.3">
@@ -7282,7 +7306,7 @@
         <v>4.487858181390747E-3</v>
       </c>
       <c r="AB94" s="3">
-        <v>7.6169176670236776E-3</v>
+        <v>7.8672328934917303E-3</v>
       </c>
       <c r="AC94" s="3">
         <v>7.5847829576447369E-3</v>
@@ -7291,7 +7315,7 @@
         <v>6695.8249999999998</v>
       </c>
       <c r="AG94">
-        <v>6737.4349999999995</v>
+        <v>6652.2350000000006</v>
       </c>
     </row>
     <row r="95" spans="1:33" x14ac:dyDescent="0.3">
@@ -7365,7 +7389,7 @@
         <v>3.5258818548014048E-3</v>
       </c>
       <c r="AB95" s="3">
-        <v>7.7271893115984942E-3</v>
+        <v>7.9374922472878803E-3</v>
       </c>
       <c r="AC95" s="3">
         <v>7.6158543155400438E-3</v>
@@ -7448,7 +7472,7 @@
         <v>5.4264860316242114E-3</v>
       </c>
       <c r="AB96" s="3">
-        <v>7.8564920467826017E-3</v>
+        <v>7.7451049555983774E-3</v>
       </c>
       <c r="AC96" s="3">
         <v>7.5705418629686072E-3</v>
@@ -7531,13 +7555,13 @@
         <v>2.5129330622575274E-3</v>
       </c>
       <c r="AB97" s="3">
-        <v>7.5763252171035115E-3</v>
+        <v>7.8031749589989969E-3</v>
       </c>
       <c r="AC97" s="3">
         <v>7.5607864490240019E-3</v>
       </c>
       <c r="AF97">
-        <v>6695.8249999999998</v>
+        <v>6643.1749999999993</v>
       </c>
       <c r="AG97">
         <v>6652.2350000000006</v>
@@ -7614,7 +7638,7 @@
         <v>1.7530208026521832E-2</v>
       </c>
       <c r="AB98" s="3">
-        <v>8.1169502192416695E-3</v>
+        <v>7.8796771803426261E-3</v>
       </c>
       <c r="AC98" s="3">
         <v>7.8211208564440884E-3</v>
@@ -7697,16 +7721,16 @@
         <v>6.1604398766184065E-3</v>
       </c>
       <c r="AB99" s="3">
-        <v>7.8242179124805543E-3</v>
+        <v>8.0518802897410306E-3</v>
       </c>
       <c r="AC99" s="3">
         <v>7.8373507051832693E-3</v>
       </c>
       <c r="AF99">
-        <v>6643.1749999999993</v>
+        <v>6478.2</v>
       </c>
       <c r="AG99">
-        <v>6652.2350000000006</v>
+        <v>6611.125</v>
       </c>
     </row>
     <row r="100" spans="1:33" x14ac:dyDescent="0.3">
@@ -7780,16 +7804,16 @@
         <v>1.6069745742048891E-3</v>
       </c>
       <c r="AB100" s="3">
-        <v>7.843980105368898E-3</v>
+        <v>7.5137933947040303E-3</v>
       </c>
       <c r="AC100" s="3">
         <v>7.8595008480541722E-3</v>
       </c>
       <c r="AF100">
-        <v>6478.2</v>
+        <v>6643.1749999999993</v>
       </c>
       <c r="AG100">
-        <v>6611.125</v>
+        <v>6625.6100000000006</v>
       </c>
     </row>
     <row r="101" spans="1:33" x14ac:dyDescent="0.3">
@@ -7863,16 +7887,16 @@
         <v>1.6220207473618409E-3</v>
       </c>
       <c r="AB101" s="3">
-        <v>7.3237362125317023E-3</v>
+        <v>7.5382118690097517E-3</v>
       </c>
       <c r="AC101" s="3">
         <v>7.6855037848890476E-3</v>
       </c>
       <c r="AF101">
-        <v>6643.1749999999993</v>
+        <v>6808.45</v>
       </c>
       <c r="AG101">
-        <v>6625.6100000000006</v>
+        <v>6737.4349999999995</v>
       </c>
     </row>
     <row r="102" spans="1:33" x14ac:dyDescent="0.3">
@@ -7946,13 +7970,13 @@
         <v>1.3172145642288413E-3</v>
       </c>
       <c r="AB102" s="3">
-        <v>7.3375345365974641E-3</v>
+        <v>7.1281025887619306E-3</v>
       </c>
       <c r="AC102" s="3">
         <v>7.6304611781258767E-3</v>
       </c>
       <c r="AF102">
-        <v>6808.45</v>
+        <v>6902.375</v>
       </c>
       <c r="AG102">
         <v>6737.4349999999995</v>
@@ -8029,7 +8053,7 @@
         <v>6.9776764076672215E-3</v>
       </c>
       <c r="AB103" s="3">
-        <v>7.123250131307263E-3</v>
+        <v>6.938123633852644E-3</v>
       </c>
       <c r="AC103" s="3">
         <v>7.6544659281167346E-3</v>
@@ -8112,7 +8136,7 @@
         <v>1.6769460158606031E-2</v>
       </c>
       <c r="AB104" s="3">
-        <v>7.2552635217479145E-3</v>
+        <v>7.4266717203362084E-3</v>
       </c>
       <c r="AC104" s="3">
         <v>7.906752994373812E-3</v>
@@ -8195,16 +8219,16 @@
         <v>3.6344645588677338E-3</v>
       </c>
       <c r="AB105" s="3">
-        <v>7.3043424570630325E-3</v>
+        <v>7.3741503007877596E-3</v>
       </c>
       <c r="AC105" s="3">
         <v>7.7477576021668434E-3</v>
       </c>
       <c r="AF105">
-        <v>6902.375</v>
+        <v>7008.5</v>
       </c>
       <c r="AG105">
-        <v>6737.4349999999995</v>
+        <v>6808.45</v>
       </c>
     </row>
     <row r="106" spans="1:33" x14ac:dyDescent="0.3">
@@ -8278,7 +8302,7 @@
         <v>8.0696132066958581E-3</v>
       </c>
       <c r="AB106" s="3">
-        <v>7.3965845880751176E-3</v>
+        <v>7.4543664901367546E-3</v>
       </c>
       <c r="AC106" s="3">
         <v>7.6626613838614004E-3</v>
@@ -8361,16 +8385,16 @@
         <v>1.3103560690575944E-2</v>
       </c>
       <c r="AB107" s="3">
-        <v>7.6365985611186642E-3</v>
+        <v>7.6355873100587444E-3</v>
       </c>
       <c r="AC107" s="3">
         <v>7.8691741373417296E-3</v>
       </c>
       <c r="AF107">
-        <v>7008.5</v>
+        <v>7066.25</v>
       </c>
       <c r="AG107">
-        <v>6808.45</v>
+        <v>6852.875</v>
       </c>
     </row>
     <row r="108" spans="1:33" x14ac:dyDescent="0.3">
@@ -8444,16 +8468,16 @@
         <v>5.8839572020261688E-3</v>
       </c>
       <c r="AB108" s="3">
-        <v>7.5790831130254357E-3</v>
+        <v>7.6365703204948621E-3</v>
       </c>
       <c r="AC108" s="3">
         <v>7.6774175557350281E-3</v>
       </c>
       <c r="AF108">
-        <v>7066.25</v>
+        <v>7317.875</v>
       </c>
       <c r="AG108">
-        <v>6852.875</v>
+        <v>6942</v>
       </c>
     </row>
     <row r="109" spans="1:33" x14ac:dyDescent="0.3">
@@ -8527,13 +8551,13 @@
         <v>2.6764093233403452E-3</v>
       </c>
       <c r="AB109" s="3">
-        <v>7.4765651270382646E-3</v>
+        <v>7.4046327200437542E-3</v>
       </c>
       <c r="AC109" s="3">
         <v>7.6181575062390849E-3</v>
       </c>
       <c r="AF109">
-        <v>7317.875</v>
+        <v>7625.625</v>
       </c>
       <c r="AG109">
         <v>6942</v>
@@ -8610,7 +8634,7 @@
         <v>1.9212808992117303E-3</v>
       </c>
       <c r="AB110" s="3">
-        <v>7.2277504032427211E-3</v>
+        <v>7.1816304234983194E-3</v>
       </c>
       <c r="AC110" s="3">
         <v>7.6251956493885685E-3</v>
@@ -8619,7 +8643,7 @@
         <v>7625.625</v>
       </c>
       <c r="AG110">
-        <v>6942</v>
+        <v>6991.5</v>
       </c>
     </row>
     <row r="111" spans="1:33" x14ac:dyDescent="0.3">
@@ -8693,16 +8717,16 @@
         <v>3.0540068390657593E-3</v>
       </c>
       <c r="AB111" s="3">
-        <v>7.0484812756133981E-3</v>
+        <v>6.7868627808484201E-3</v>
       </c>
       <c r="AC111" s="3">
         <v>7.3290807714569061E-3</v>
       </c>
       <c r="AF111">
-        <v>7625.625</v>
+        <v>7876</v>
       </c>
       <c r="AG111">
-        <v>6991.5</v>
+        <v>7008.5</v>
       </c>
     </row>
     <row r="112" spans="1:33" x14ac:dyDescent="0.3">
@@ -8776,13 +8800,13 @@
         <v>1.0413481820414239E-2</v>
       </c>
       <c r="AB112" s="3">
-        <v>6.9038504918021559E-3</v>
+        <v>6.5713026002735212E-3</v>
       </c>
       <c r="AC112" s="3">
         <v>7.3665415883067114E-3</v>
       </c>
       <c r="AF112">
-        <v>7876</v>
+        <v>8153.3</v>
       </c>
       <c r="AG112">
         <v>7008.5</v>
@@ -8859,13 +8883,13 @@
         <v>1.1843554747921203E-3</v>
       </c>
       <c r="AB113" s="3">
-        <v>6.3975301123547663E-3</v>
+        <v>6.0661925989510109E-3</v>
       </c>
       <c r="AC113" s="3">
         <v>7.305880642223395E-3</v>
       </c>
       <c r="AF113">
-        <v>8153.3</v>
+        <v>8360.1</v>
       </c>
       <c r="AG113">
         <v>7008.5</v>
@@ -8942,16 +8966,16 @@
         <v>1.0241384099646034E-2</v>
       </c>
       <c r="AB114" s="3">
-        <v>6.2008761957476248E-3</v>
+        <v>6.248743753322239E-3</v>
       </c>
       <c r="AC114" s="3">
         <v>7.1861703480900502E-3</v>
       </c>
       <c r="AF114">
-        <v>8360.1</v>
+        <v>8451.2000000000007</v>
       </c>
       <c r="AG114">
-        <v>7008.5</v>
+        <v>7066.25</v>
       </c>
     </row>
     <row r="115" spans="1:33" x14ac:dyDescent="0.3">
@@ -9025,7 +9049,7 @@
         <v>1.0047577431659294E-2</v>
       </c>
       <c r="AB115" s="3">
-        <v>6.3712867752040792E-3</v>
+        <v>5.9225528273806711E-3</v>
       </c>
       <c r="AC115" s="3">
         <v>7.2765412039985152E-3</v>
@@ -9034,7 +9058,7 @@
         <v>8451.2000000000007</v>
       </c>
       <c r="AG115">
-        <v>7066.25</v>
+        <v>7008.5</v>
       </c>
     </row>
     <row r="116" spans="1:33" x14ac:dyDescent="0.3">
@@ -9108,7 +9132,7 @@
         <v>2.0196395597684713E-3</v>
       </c>
       <c r="AB116" s="3">
-        <v>5.7966523993931802E-3</v>
+        <v>5.7507471711224648E-3</v>
       </c>
       <c r="AC116" s="3">
         <v>7.0359316059136834E-3</v>
@@ -9191,7 +9215,7 @@
         <v>1.1148936298868151E-3</v>
       </c>
       <c r="AB117" s="3">
-        <v>5.6012035085019601E-3</v>
+        <v>5.2835880439545497E-3</v>
       </c>
       <c r="AC117" s="3">
         <v>7.0246497446100733E-3</v>
@@ -9200,7 +9224,7 @@
         <v>8451.2000000000007</v>
       </c>
       <c r="AG117">
-        <v>7008.5</v>
+        <v>7066.25</v>
       </c>
     </row>
     <row r="118" spans="1:33" x14ac:dyDescent="0.3">
@@ -9274,16 +9298,16 @@
         <v>3.4097607975973609E-3</v>
       </c>
       <c r="AB118" s="3">
-        <v>5.2231420037494791E-3</v>
+        <v>5.347648205354264E-3</v>
       </c>
       <c r="AC118" s="3">
         <v>6.8122508229457755E-3</v>
       </c>
       <c r="AF118">
-        <v>8451.2000000000007</v>
+        <v>8360.1</v>
       </c>
       <c r="AG118">
-        <v>7066.25</v>
+        <v>7008.5</v>
       </c>
     </row>
     <row r="119" spans="1:33" x14ac:dyDescent="0.3">
@@ -9357,7 +9381,7 @@
         <v>4.4550653807469143E-3</v>
       </c>
       <c r="AB119" s="3">
-        <v>5.3188552110120914E-3</v>
+        <v>5.3110351401818934E-3</v>
       </c>
       <c r="AC119" s="3">
         <v>6.8681220427587357E-3</v>
@@ -9366,7 +9390,7 @@
         <v>8360.1</v>
       </c>
       <c r="AG119">
-        <v>7008.5</v>
+        <v>7066.25</v>
       </c>
     </row>
     <row r="120" spans="1:33" x14ac:dyDescent="0.3">
@@ -9440,7 +9464,7 @@
         <v>9.245688010823816E-4</v>
       </c>
       <c r="AB120" s="3">
-        <v>5.1695362260173929E-3</v>
+        <v>5.1889725978248261E-3</v>
       </c>
       <c r="AC120" s="3">
         <v>6.5329129905547069E-3</v>
@@ -9449,7 +9473,7 @@
         <v>8360.1</v>
       </c>
       <c r="AG120">
-        <v>7066.25</v>
+        <v>7008.5</v>
       </c>
     </row>
     <row r="121" spans="1:33" x14ac:dyDescent="0.3">
@@ -9523,16 +9547,16 @@
         <v>2.4273289121188313E-3</v>
       </c>
       <c r="AB121" s="3">
-        <v>5.0998873176407618E-3</v>
+        <v>5.1831117359218562E-3</v>
       </c>
       <c r="AC121" s="3">
         <v>6.4413467172099248E-3</v>
       </c>
       <c r="AF121">
-        <v>8360.1</v>
+        <v>8451.2000000000007</v>
       </c>
       <c r="AG121">
-        <v>7008.5</v>
+        <v>7066.25</v>
       </c>
     </row>
     <row r="122" spans="1:33" x14ac:dyDescent="0.3">
@@ -9606,7 +9630,7 @@
         <v>2.9975275767898379E-3</v>
       </c>
       <c r="AB122" s="3">
-        <v>5.1126090211111464E-3</v>
+        <v>5.23060516407187E-3</v>
       </c>
       <c r="AC122" s="3">
         <v>6.4648808280828472E-3</v>
@@ -9615,7 +9639,7 @@
         <v>8451.2000000000007</v>
       </c>
       <c r="AG122">
-        <v>7066.25</v>
+        <v>7210.75</v>
       </c>
     </row>
     <row r="123" spans="1:33" x14ac:dyDescent="0.3">
@@ -9689,7 +9713,7 @@
         <v>4.3503473908199641E-3</v>
       </c>
       <c r="AB123" s="3">
-        <v>5.2022097520314859E-3</v>
+        <v>5.3288792360129582E-3</v>
       </c>
       <c r="AC123" s="3">
         <v>6.5250494429455333E-3</v>
@@ -9698,7 +9722,7 @@
         <v>8451.2000000000007</v>
       </c>
       <c r="AG123">
-        <v>7210.75</v>
+        <v>7066.25</v>
       </c>
     </row>
     <row r="124" spans="1:33" x14ac:dyDescent="0.3">
@@ -9772,16 +9796,16 @@
         <v>6.1841901141247435E-3</v>
       </c>
       <c r="AB124" s="3">
-        <v>5.356469909500435E-3</v>
+        <v>5.3854236337707584E-3</v>
       </c>
       <c r="AC124" s="3">
         <v>6.6263282636312443E-3</v>
       </c>
       <c r="AF124">
-        <v>8451.2000000000007</v>
+        <v>8522.9</v>
       </c>
       <c r="AG124">
-        <v>7066.25</v>
+        <v>7210.75</v>
       </c>
     </row>
     <row r="125" spans="1:33" x14ac:dyDescent="0.3">
@@ -9855,16 +9879,16 @@
         <v>1.8300239712322197E-3</v>
       </c>
       <c r="AB125" s="3">
-        <v>5.2707333220759671E-3</v>
+        <v>5.3288950376517855E-3</v>
       </c>
       <c r="AC125" s="3">
         <v>6.6331936424698333E-3</v>
       </c>
       <c r="AF125">
-        <v>8522.9</v>
+        <v>8652.85</v>
       </c>
       <c r="AG125">
-        <v>7210.75</v>
+        <v>7417.125</v>
       </c>
     </row>
     <row r="126" spans="1:33" x14ac:dyDescent="0.3">
@@ -9938,16 +9962,16 @@
         <v>2.3088101353491153E-3</v>
       </c>
       <c r="AB126" s="3">
-        <v>5.2314729440291188E-3</v>
+        <v>5.2249725077759494E-3</v>
       </c>
       <c r="AC126" s="3">
         <v>6.4850387316871634E-3</v>
       </c>
       <c r="AF126">
-        <v>8652.85</v>
+        <v>8522.9</v>
       </c>
       <c r="AG126">
-        <v>7417.125</v>
+        <v>7210.75</v>
       </c>
     </row>
     <row r="127" spans="1:33" x14ac:dyDescent="0.3">
@@ -10021,16 +10045,16 @@
         <v>8.2133078992363551E-4</v>
       </c>
       <c r="AB127" s="3">
-        <v>5.0829195491355521E-3</v>
+        <v>5.1685857653648191E-3</v>
       </c>
       <c r="AC127" s="3">
         <v>6.485880362181908E-3</v>
       </c>
       <c r="AF127">
-        <v>8522.9</v>
+        <v>8652.85</v>
       </c>
       <c r="AG127">
-        <v>7210.75</v>
+        <v>7417.125</v>
       </c>
     </row>
     <row r="128" spans="1:33" x14ac:dyDescent="0.3">
@@ -10104,7 +10128,7 @@
         <v>3.895609268950051E-3</v>
       </c>
       <c r="AB128" s="3">
-        <v>5.1275220074159557E-3</v>
+        <v>4.7140991401124262E-3</v>
       </c>
       <c r="AC128" s="3">
         <v>6.2968881602275262E-3</v>
@@ -10113,7 +10137,7 @@
         <v>8652.85</v>
       </c>
       <c r="AG128">
-        <v>7417.125</v>
+        <v>7525.25</v>
       </c>
     </row>
     <row r="129" spans="1:33" x14ac:dyDescent="0.3">
@@ -10187,7 +10211,7 @@
         <v>1.5660439079561161E-3</v>
       </c>
       <c r="AB129" s="3">
-        <v>4.6125489713331911E-3</v>
+        <v>4.5609526078236838E-3</v>
       </c>
       <c r="AC129" s="3">
         <v>6.3064164487823572E-3</v>
@@ -10270,13 +10294,13 @@
         <v>2.1296256675058522E-3</v>
       </c>
       <c r="AB130" s="3">
-        <v>4.4825227065231083E-3</v>
+        <v>4.5783743109337159E-3</v>
       </c>
       <c r="AC130" s="3">
         <v>6.0460838528188735E-3</v>
       </c>
       <c r="AF130">
-        <v>8652.85</v>
+        <v>8522.9</v>
       </c>
       <c r="AG130">
         <v>7525.25</v>
@@ -10353,7 +10377,7 @@
         <v>1.5324722662448664E-3</v>
       </c>
       <c r="AB131" s="3">
-        <v>4.4801194062663334E-3</v>
+        <v>4.5753893615631501E-3</v>
       </c>
       <c r="AC131" s="3">
         <v>6.0568006152864505E-3</v>
@@ -10436,13 +10460,13 @@
         <v>4.6621272251514689E-3</v>
       </c>
       <c r="AB132" s="3">
-        <v>4.5781873571627734E-3</v>
+        <v>4.6868864502605705E-3</v>
       </c>
       <c r="AC132" s="3">
         <v>5.907494519511251E-3</v>
       </c>
       <c r="AF132">
-        <v>8522.9</v>
+        <v>8451.2000000000007</v>
       </c>
       <c r="AG132">
         <v>7525.25</v>
@@ -10519,16 +10543,16 @@
         <v>1.0608226047201796E-3</v>
       </c>
       <c r="AB133" s="3">
-        <v>4.569916648791526E-3</v>
+        <v>4.489657990162336E-3</v>
       </c>
       <c r="AC133" s="3">
         <v>5.71389081200749E-3</v>
       </c>
       <c r="AF133">
-        <v>8451.2000000000007</v>
+        <v>8522.9</v>
       </c>
       <c r="AG133">
-        <v>7525.25</v>
+        <v>7619.625</v>
       </c>
     </row>
     <row r="134" spans="1:33" x14ac:dyDescent="0.3">
@@ -10602,7 +10626,7 @@
         <v>1.2435441829605764E-4</v>
       </c>
       <c r="AB134" s="3">
-        <v>4.3488417459085849E-3</v>
+        <v>3.9348211321520036E-3</v>
       </c>
       <c r="AC134" s="3">
         <v>5.6807464262441064E-3</v>
@@ -10611,7 +10635,7 @@
         <v>8522.9</v>
       </c>
       <c r="AG134">
-        <v>7619.625</v>
+        <v>7618.625</v>
       </c>
     </row>
     <row r="135" spans="1:33" x14ac:dyDescent="0.3">
@@ -10685,16 +10709,16 @@
         <v>6.802557874834303E-3</v>
       </c>
       <c r="AB135" s="3">
-        <v>4.0273287690127226E-3</v>
+        <v>4.0404242426842225E-3</v>
       </c>
       <c r="AC135" s="3">
         <v>5.7072872717359906E-3</v>
       </c>
       <c r="AF135">
-        <v>8522.9</v>
+        <v>8451.2000000000007</v>
       </c>
       <c r="AG135">
-        <v>7618.625</v>
+        <v>7720</v>
       </c>
     </row>
     <row r="136" spans="1:33" x14ac:dyDescent="0.3">
@@ -10768,13 +10792,13 @@
         <v>4.3638060585773353E-3</v>
       </c>
       <c r="AB136" s="3">
-        <v>4.0508559141646458E-3</v>
+        <v>3.9168973377469388E-3</v>
       </c>
       <c r="AC136" s="3">
         <v>5.6856319139418467E-3</v>
       </c>
       <c r="AF136">
-        <v>8451.2000000000007</v>
+        <v>8397.2999999999993</v>
       </c>
       <c r="AG136">
         <v>7720</v>
@@ -10851,13 +10875,13 @@
         <v>7.4235526023223031E-3</v>
       </c>
       <c r="AB137" s="3">
-        <v>4.0300152495074343E-3</v>
+        <v>3.7275637348051505E-3</v>
       </c>
       <c r="AC137" s="3">
         <v>5.6815755224319479E-3</v>
       </c>
       <c r="AF137">
-        <v>8397.2999999999993</v>
+        <v>8250.4</v>
       </c>
       <c r="AG137">
         <v>7720</v>
@@ -10934,13 +10958,13 @@
         <v>1.1310396162638181E-3</v>
       </c>
       <c r="AB138" s="3">
-        <v>3.6438048922715592E-3</v>
+        <v>3.5691331486130723E-3</v>
       </c>
       <c r="AC138" s="3">
         <v>5.602851734553967E-3</v>
       </c>
       <c r="AF138">
-        <v>8250.4</v>
+        <v>8131</v>
       </c>
       <c r="AG138">
         <v>7720</v>
@@ -11017,13 +11041,13 @@
         <v>7.5887242054661908E-4</v>
       </c>
       <c r="AB139" s="3">
-        <v>3.4784795767399605E-3</v>
+        <v>3.5052152518532812E-3</v>
       </c>
       <c r="AC139" s="3">
         <v>5.4549239859485177E-3</v>
       </c>
       <c r="AF139">
-        <v>8131</v>
+        <v>7915.1</v>
       </c>
       <c r="AG139">
         <v>7720</v>
@@ -11100,7 +11124,7 @@
         <v>1.0953632300265692E-3</v>
       </c>
       <c r="AB140" s="3">
-        <v>3.4274780898588711E-3</v>
+        <v>3.4776846628804424E-3</v>
       </c>
       <c r="AC140" s="3">
         <v>5.3296575431893813E-3</v>
@@ -11183,7 +11207,7 @@
         <v>4.3458700792639027E-3</v>
       </c>
       <c r="AB141" s="3">
-        <v>3.5056906440541027E-3</v>
+        <v>3.5207467708870473E-3</v>
       </c>
       <c r="AC141" s="3">
         <v>5.1538047758677335E-3</v>
@@ -11192,7 +11216,7 @@
         <v>7915.1</v>
       </c>
       <c r="AG141">
-        <v>7720</v>
+        <v>7876</v>
       </c>
     </row>
     <row r="142" spans="1:33" x14ac:dyDescent="0.3">
@@ -11266,16 +11290,16 @@
         <v>5.5768908711228971E-4</v>
       </c>
       <c r="AB142" s="3">
-        <v>3.4251642649588293E-3</v>
+        <v>3.1922203464436489E-3</v>
       </c>
       <c r="AC142" s="3">
         <v>4.8817614733585851E-3</v>
       </c>
       <c r="AF142">
-        <v>7915.1</v>
+        <v>7744.5</v>
       </c>
       <c r="AG142">
-        <v>7876</v>
+        <v>7900.5</v>
       </c>
     </row>
     <row r="143" spans="1:33" x14ac:dyDescent="0.3">
@@ -11349,13 +11373,13 @@
         <v>9.4289727394406553E-3</v>
       </c>
       <c r="AB143" s="3">
-        <v>3.3934059075080686E-3</v>
+        <v>3.4670409219319334E-3</v>
       </c>
       <c r="AC143" s="3">
         <v>4.7666167604414724E-3</v>
       </c>
       <c r="AF143">
-        <v>7744.5</v>
+        <v>7598</v>
       </c>
       <c r="AG143">
         <v>7900.5</v>
@@ -11432,7 +11456,7 @@
         <v>8.5929377791813533E-3</v>
       </c>
       <c r="AB144" s="3">
-        <v>3.6323924334561082E-3</v>
+        <v>3.4120927112497776E-3</v>
       </c>
       <c r="AC144" s="3">
         <v>4.8304182322860085E-3</v>
@@ -11441,7 +11465,7 @@
         <v>7598</v>
       </c>
       <c r="AG144">
-        <v>7900.5</v>
+        <v>8071.1</v>
       </c>
     </row>
     <row r="145" spans="1:33" x14ac:dyDescent="0.3">
@@ -11515,7 +11539,7 @@
         <v>3.2008633333439063E-3</v>
       </c>
       <c r="AB145" s="3">
-        <v>3.4052788603495883E-3</v>
+        <v>3.183868907972598E-3</v>
       </c>
       <c r="AC145" s="3">
         <v>4.5532108676766348E-3</v>
@@ -11598,7 +11622,7 @@
         <v>9.7428189403608867E-3</v>
       </c>
       <c r="AB146" s="3">
-        <v>3.3954479412754458E-3</v>
+        <v>3.4413082206590116E-3</v>
       </c>
       <c r="AC146" s="3">
         <v>4.5960276958907382E-3</v>
@@ -11681,7 +11705,7 @@
         <v>5.5120245961777226E-3</v>
       </c>
       <c r="AB147" s="3">
-        <v>3.508105523095099E-3</v>
+        <v>3.5878792528687086E-3</v>
       </c>
       <c r="AC147" s="3">
         <v>4.4357336484116289E-3</v>
@@ -11690,7 +11714,7 @@
         <v>7598</v>
       </c>
       <c r="AG147">
-        <v>8071.1</v>
+        <v>8131</v>
       </c>
     </row>
     <row r="148" spans="1:33" x14ac:dyDescent="0.3">
@@ -11764,13 +11788,13 @@
         <v>5.0838852499601739E-3</v>
       </c>
       <c r="AB148" s="3">
-        <v>3.636137510839401E-3</v>
+        <v>3.6436834012808024E-3</v>
       </c>
       <c r="AC148" s="3">
         <v>4.4956658033175334E-3</v>
       </c>
       <c r="AF148">
-        <v>7598</v>
+        <v>7744.5</v>
       </c>
       <c r="AG148">
         <v>8131</v>
@@ -11847,7 +11871,7 @@
         <v>5.9069475297151008E-3</v>
       </c>
       <c r="AB149" s="3">
-        <v>3.7166919215528764E-3</v>
+        <v>3.6920794729130755E-3</v>
       </c>
       <c r="AC149" s="3">
         <v>4.5015573065474842E-3</v>
@@ -11930,7 +11954,7 @@
         <v>2.9383746887057249E-4</v>
       </c>
       <c r="AB150" s="3">
-        <v>3.5824587631052528E-3</v>
+        <v>3.6710550951726817E-3</v>
       </c>
       <c r="AC150" s="3">
         <v>4.4300138464987539E-3</v>
@@ -12013,7 +12037,7 @@
         <v>2.1000663178836199E-3</v>
       </c>
       <c r="AB151" s="3">
-        <v>3.6203780378407766E-3</v>
+        <v>3.6601463420315081E-3</v>
       </c>
       <c r="AC151" s="3">
         <v>4.421629038976682E-3</v>
@@ -12022,7 +12046,7 @@
         <v>7744.5</v>
       </c>
       <c r="AG151">
-        <v>8131</v>
+        <v>8213.2000000000007</v>
       </c>
     </row>
     <row r="152" spans="1:33" x14ac:dyDescent="0.3">
@@ -12096,13 +12120,13 @@
         <v>7.9730085272785578E-3</v>
       </c>
       <c r="AB152" s="3">
-        <v>3.7992709286523807E-3</v>
+        <v>3.8259957070477988E-3</v>
       </c>
       <c r="AC152" s="3">
         <v>4.5283004355598346E-3</v>
       </c>
       <c r="AF152">
-        <v>7744.5</v>
+        <v>7629.5</v>
       </c>
       <c r="AG152">
         <v>8213.2000000000007</v>
@@ -12179,16 +12203,16 @@
         <v>3.0995539298286356E-3</v>
       </c>
       <c r="AB153" s="3">
-        <v>3.8025621013310514E-3</v>
+        <v>3.7843025916814211E-3</v>
       </c>
       <c r="AC153" s="3">
         <v>4.5565909138471899E-3</v>
       </c>
       <c r="AF153">
-        <v>7629.5</v>
+        <v>7946.6</v>
       </c>
       <c r="AG153">
-        <v>8213.2000000000007</v>
+        <v>8318.7999999999993</v>
       </c>
     </row>
     <row r="154" spans="1:33" x14ac:dyDescent="0.3">
@@ -12262,7 +12286,7 @@
         <v>5.5831176763078139E-3</v>
       </c>
       <c r="AB154" s="3">
-        <v>3.8423288847338854E-3</v>
+        <v>3.7642668437541898E-3</v>
       </c>
       <c r="AC154" s="3">
         <v>4.5748452387624743E-3</v>
@@ -12271,7 +12295,7 @@
         <v>7946.6</v>
       </c>
       <c r="AG154">
-        <v>8318.7999999999993</v>
+        <v>8397.2999999999993</v>
       </c>
     </row>
     <row r="155" spans="1:33" x14ac:dyDescent="0.3">
@@ -12345,13 +12369,13 @@
         <v>1.3145440088848659E-3</v>
       </c>
       <c r="AB155" s="3">
-        <v>3.6852435265003407E-3</v>
+        <v>3.7470841783426114E-3</v>
       </c>
       <c r="AC155" s="3">
         <v>4.5379896079971987E-3</v>
       </c>
       <c r="AF155">
-        <v>7946.6</v>
+        <v>7629.5</v>
       </c>
       <c r="AG155">
         <v>8397.2999999999993</v>
@@ -12428,13 +12452,13 @@
         <v>5.5526042970301948E-3</v>
       </c>
       <c r="AB156" s="3">
-        <v>3.8053267628164046E-3</v>
+        <v>3.8552106503986477E-3</v>
       </c>
       <c r="AC156" s="3">
         <v>4.5400915790872985E-3</v>
       </c>
       <c r="AF156">
-        <v>7629.5</v>
+        <v>7946.6</v>
       </c>
       <c r="AG156">
         <v>8397.2999999999993</v>
@@ -12511,7 +12535,7 @@
         <v>4.0308615205384424E-3</v>
       </c>
       <c r="AB157" s="3">
-        <v>3.8608768074999311E-3</v>
+        <v>3.962195008085808E-3</v>
       </c>
       <c r="AC157" s="3">
         <v>4.5653903867253131E-3</v>
@@ -12520,7 +12544,7 @@
         <v>7946.6</v>
       </c>
       <c r="AG157">
-        <v>8397.2999999999993</v>
+        <v>8451.2000000000007</v>
       </c>
     </row>
     <row r="158" spans="1:33" x14ac:dyDescent="0.3">
@@ -12594,7 +12618,7 @@
         <v>4.0546002555794658E-3</v>
       </c>
       <c r="AB158" s="3">
-        <v>3.9651758225210873E-3</v>
+        <v>3.9674947076401212E-3</v>
       </c>
       <c r="AC158" s="3">
         <v>4.3407969238762742E-3</v>
@@ -12677,16 +12701,16 @@
         <v>3.7235362162990615E-3</v>
       </c>
       <c r="AB159" s="3">
-        <v>3.9596250788871846E-3</v>
+        <v>4.03941111791822E-3</v>
       </c>
       <c r="AC159" s="3">
         <v>4.3001818628709519E-3</v>
       </c>
       <c r="AF159">
-        <v>7946.6</v>
+        <v>8236.6</v>
       </c>
       <c r="AG159">
-        <v>8451.2000000000007</v>
+        <v>8522.9</v>
       </c>
     </row>
     <row r="160" spans="1:33" x14ac:dyDescent="0.3">
@@ -12760,16 +12784,16 @@
         <v>1.3967953801554689E-3</v>
       </c>
       <c r="AB160" s="3">
-        <v>3.954165448958131E-3</v>
+        <v>4.0149834416732073E-3</v>
       </c>
       <c r="AC160" s="3">
         <v>4.2966788763034612E-3</v>
       </c>
       <c r="AF160">
-        <v>8236.6</v>
+        <v>8429</v>
       </c>
       <c r="AG160">
-        <v>8522.9</v>
+        <v>8482.9</v>
       </c>
     </row>
     <row r="161" spans="1:33" x14ac:dyDescent="0.3">
@@ -12843,7 +12867,7 @@
         <v>5.0768133510443736E-3</v>
       </c>
       <c r="AB161" s="3">
-        <v>4.0492360193948576E-3</v>
+        <v>4.1331281444998572E-3</v>
       </c>
       <c r="AC161" s="3">
         <v>4.3542587530315032E-3</v>
@@ -12926,13 +12950,13 @@
         <v>2.6420314539198353E-3</v>
       </c>
       <c r="AB162" s="3">
-        <v>4.0850282512553404E-3</v>
+        <v>4.0657916187921365E-3</v>
       </c>
       <c r="AC162" s="3">
         <v>4.3763390345263531E-3</v>
       </c>
       <c r="AF162">
-        <v>8429</v>
+        <v>8690</v>
       </c>
       <c r="AG162">
         <v>8482.9</v>
@@ -13009,7 +13033,7 @@
         <v>4.9639711170068601E-3</v>
       </c>
       <c r="AB163" s="3">
-        <v>4.094765150992611E-3</v>
+        <v>4.195896569201692E-3</v>
       </c>
       <c r="AC163" s="3">
         <v>4.3427772796820144E-3</v>
@@ -13018,7 +13042,7 @@
         <v>8690</v>
       </c>
       <c r="AG163">
-        <v>8482.9</v>
+        <v>8542</v>
       </c>
     </row>
     <row r="164" spans="1:33" x14ac:dyDescent="0.3">
@@ -13092,7 +13116,7 @@
         <v>3.7006281109173145E-3</v>
       </c>
       <c r="AB164" s="3">
-        <v>4.1799201673215509E-3</v>
+        <v>4.3151056922890677E-3</v>
       </c>
       <c r="AC164" s="3">
         <v>4.1249634122205352E-3</v>
@@ -13175,13 +13199,13 @@
         <v>5.9542295955604674E-3</v>
       </c>
       <c r="AB165" s="3">
-        <v>4.3679806569107251E-3</v>
+        <v>4.2868280829799392E-3</v>
       </c>
       <c r="AC165" s="3">
         <v>4.1636261628320813E-3</v>
       </c>
       <c r="AF165">
-        <v>8690</v>
+        <v>9725.5</v>
       </c>
       <c r="AG165">
         <v>8542</v>
@@ -13258,13 +13282,13 @@
         <v>2.2524252195806893E-3</v>
       </c>
       <c r="AB166" s="3">
-        <v>4.2212021841606089E-3</v>
+        <v>4.216448721680051E-3</v>
       </c>
       <c r="AC166" s="3">
         <v>4.0666730297134945E-3</v>
       </c>
       <c r="AF166">
-        <v>9725.5</v>
+        <v>10866.15</v>
       </c>
       <c r="AG166">
         <v>8542</v>
@@ -13341,16 +13365,16 @@
         <v>1.686915325729621E-3</v>
       </c>
       <c r="AB167" s="3">
-        <v>4.1348508701977791E-3</v>
+        <v>4.0252274791269622E-3</v>
       </c>
       <c r="AC167" s="3">
         <v>3.8763956069660563E-3</v>
       </c>
       <c r="AF167">
-        <v>10866.15</v>
+        <v>11249.65</v>
       </c>
       <c r="AG167">
-        <v>8542</v>
+        <v>8652.85</v>
       </c>
     </row>
     <row r="168" spans="1:33" x14ac:dyDescent="0.3">
@@ -13424,7 +13448,7 @@
         <v>1.291579062443482E-4</v>
       </c>
       <c r="AB168" s="3">
-        <v>3.8995478154855872E-3</v>
+        <v>3.9918314221263126E-3</v>
       </c>
       <c r="AC168" s="3">
         <v>3.7804822853696927E-3</v>
@@ -13507,13 +13531,13 @@
         <v>7.2192325903241983E-4</v>
       </c>
       <c r="AB169" s="3">
-        <v>3.8863505136394133E-3</v>
+        <v>3.9905997834091727E-3</v>
       </c>
       <c r="AC169" s="3">
         <v>3.7479075176312269E-3</v>
       </c>
       <c r="AF169">
-        <v>11249.65</v>
+        <v>11347.4</v>
       </c>
       <c r="AG169">
         <v>8652.85</v>
@@ -13590,16 +13614,16 @@
         <v>9.0208958024839969E-4</v>
       </c>
       <c r="AB170" s="3">
-        <v>3.8909704220168899E-3</v>
+        <v>3.9841573284165677E-3</v>
       </c>
       <c r="AC170" s="3">
         <v>3.730920995648505E-3</v>
       </c>
       <c r="AF170">
-        <v>11347.4</v>
+        <v>12178.75</v>
       </c>
       <c r="AG170">
-        <v>8652.85</v>
+        <v>8730</v>
       </c>
     </row>
     <row r="171" spans="1:33" x14ac:dyDescent="0.3">
@@ -13673,13 +13697,13 @@
         <v>2.6518649429400076E-3</v>
       </c>
       <c r="AB171" s="3">
-        <v>3.9411801546915173E-3</v>
+        <v>3.9276904905391043E-3</v>
       </c>
       <c r="AC171" s="3">
         <v>3.7242186307130756E-3</v>
       </c>
       <c r="AF171">
-        <v>12178.75</v>
+        <v>12539.9</v>
       </c>
       <c r="AG171">
         <v>8730</v>
@@ -13756,13 +13780,13 @@
         <v>2.9345500263284752E-3</v>
       </c>
       <c r="AB172" s="3">
-        <v>3.8956537013710192E-3</v>
+        <v>4.0069191885129772E-3</v>
       </c>
       <c r="AC172" s="3">
         <v>3.5995697674783131E-3</v>
       </c>
       <c r="AF172">
-        <v>12539.9</v>
+        <v>14971.65</v>
       </c>
       <c r="AG172">
         <v>8730</v>
@@ -13839,7 +13863,7 @@
         <v>5.3719893744639258E-3</v>
       </c>
       <c r="AB173" s="3">
-        <v>4.0509537106404271E-3</v>
+        <v>3.8716864096804194E-3</v>
       </c>
       <c r="AC173" s="3">
         <v>3.6693636658061764E-3</v>
@@ -13922,16 +13946,16 @@
         <v>1.71261266959708E-2</v>
       </c>
       <c r="AB174" s="3">
-        <v>4.2992489995607539E-3</v>
+        <v>4.1561260402400678E-3</v>
       </c>
       <c r="AC174" s="3">
         <v>3.7841093757449225E-3</v>
       </c>
       <c r="AF174">
-        <v>14971.65</v>
+        <v>12539.9</v>
       </c>
       <c r="AG174">
-        <v>8730</v>
+        <v>8542</v>
       </c>
     </row>
     <row r="175" spans="1:33" x14ac:dyDescent="0.3">
@@ -14005,16 +14029,16 @@
         <v>6.2557888992891275E-3</v>
       </c>
       <c r="AB175" s="3">
-        <v>4.2238571002093921E-3</v>
+        <v>4.2579568924382416E-3</v>
       </c>
       <c r="AC175" s="3">
         <v>3.7209129002054196E-3</v>
       </c>
       <c r="AF175">
-        <v>12539.9</v>
+        <v>16880.400000000001</v>
       </c>
       <c r="AG175">
-        <v>8542</v>
+        <v>8730</v>
       </c>
     </row>
     <row r="176" spans="1:33" x14ac:dyDescent="0.3">
@@ -14088,7 +14112,7 @@
         <v>3.2486185397118117E-3</v>
       </c>
       <c r="AB176" s="3">
-        <v>4.2253975907373892E-3</v>
+        <v>4.0414835457499394E-3</v>
       </c>
       <c r="AC176" s="3">
         <v>3.7413958832044755E-3</v>
@@ -14097,7 +14121,7 @@
         <v>16880.400000000001</v>
       </c>
       <c r="AG176">
-        <v>8730</v>
+        <v>8885.9</v>
       </c>
     </row>
     <row r="177" spans="1:34" x14ac:dyDescent="0.3">
@@ -14171,7 +14195,7 @@
         <v>9.4103276409907011E-4</v>
       </c>
       <c r="AB177" s="3">
-        <v>3.9414690044063628E-3</v>
+        <v>3.8891171513473172E-3</v>
       </c>
       <c r="AC177" s="3">
         <v>3.7384982021080129E-3</v>
@@ -14180,7 +14204,7 @@
         <v>16880.400000000001</v>
       </c>
       <c r="AG177">
-        <v>8885.9</v>
+        <v>9733.4</v>
       </c>
     </row>
     <row r="178" spans="1:34" x14ac:dyDescent="0.3">
@@ -14254,16 +14278,16 @@
         <v>9.5197770178279129E-4</v>
       </c>
       <c r="AB178" s="3">
-        <v>3.794370717490397E-3</v>
+        <v>3.7513868997414044E-3</v>
       </c>
       <c r="AC178" s="3">
         <v>3.6975351505111036E-3</v>
       </c>
       <c r="AF178">
-        <v>16880.400000000001</v>
+        <v>13701.3</v>
       </c>
       <c r="AG178">
-        <v>9733.4</v>
+        <v>10623.9</v>
       </c>
     </row>
     <row r="179" spans="1:34" x14ac:dyDescent="0.3">
@@ -14337,13 +14361,13 @@
         <v>1.2579077720935583E-3</v>
       </c>
       <c r="AB179" s="3">
-        <v>3.6709520891721192E-3</v>
+        <v>3.5964189078206863E-3</v>
       </c>
       <c r="AC179" s="3">
         <v>3.6442491903668811E-3</v>
       </c>
       <c r="AF179">
-        <v>13701.3</v>
+        <v>16036.1</v>
       </c>
       <c r="AG179">
         <v>10623.9</v>
@@ -14423,7 +14447,7 @@
         <v>5.6026314740376115E-4</v>
       </c>
       <c r="AB180" s="3">
-        <v>3.4984783994201404E-3</v>
+        <v>3.605299763771793E-3</v>
       </c>
       <c r="AC180" s="3">
         <v>3.6381774294722371E-3</v>
@@ -14433,6 +14457,9 @@
       </c>
       <c r="AG180">
         <v>10623.9</v>
+      </c>
+      <c r="AH180">
+        <v>8081.85</v>
       </c>
     </row>
     <row r="181" spans="1:34" x14ac:dyDescent="0.3">
@@ -14512,19 +14539,22 @@
         <v>2.4963280280003719E-3</v>
       </c>
       <c r="AB181" s="3">
-        <v>3.5695264819727147E-3</v>
+        <v>3.6185084874423511E-3</v>
       </c>
       <c r="AC181" s="3">
         <v>3.6393274147369296E-3</v>
       </c>
+      <c r="AD181" s="3">
+        <v>5.6572654599490275E-3</v>
+      </c>
       <c r="AF181">
-        <v>16036.1</v>
+        <v>19191.5</v>
       </c>
       <c r="AG181">
         <v>10623.9</v>
       </c>
       <c r="AH181">
-        <v>8081.85</v>
+        <v>8131</v>
       </c>
     </row>
     <row r="182" spans="1:34" x14ac:dyDescent="0.3">
@@ -14604,7 +14634,7 @@
         <v>1.0495718049725156E-2</v>
       </c>
       <c r="AB182" s="3">
-        <v>3.8403539571934095E-3</v>
+        <v>3.7025988048572378E-3</v>
       </c>
       <c r="AC182" s="3">
         <v>3.7642972559525181E-3</v>
@@ -14699,7 +14729,7 @@
         <v>3.5811104784955194E-3</v>
       </c>
       <c r="AB183" s="3">
-        <v>3.6986798265875049E-3</v>
+        <v>3.7186506898128006E-3</v>
       </c>
       <c r="AC183" s="3">
         <v>3.7514766407471109E-3</v>
@@ -14711,7 +14741,7 @@
         <v>19191.5</v>
       </c>
       <c r="AG183">
-        <v>10623.9</v>
+        <v>10917.05</v>
       </c>
       <c r="AH183">
         <v>8131</v>
@@ -14794,7 +14824,7 @@
         <v>4.5589448806513388E-3</v>
       </c>
       <c r="AB184" s="3">
-        <v>3.7457569540333985E-3</v>
+        <v>3.6845115966242514E-3</v>
       </c>
       <c r="AC184" s="3">
         <v>3.7243892201892208E-3</v>
@@ -14806,7 +14836,7 @@
         <v>19191.5</v>
       </c>
       <c r="AG184">
-        <v>10917.05</v>
+        <v>11249.65</v>
       </c>
       <c r="AH184">
         <v>8131</v>
@@ -14889,7 +14919,7 @@
         <v>4.2329653408372803E-3</v>
       </c>
       <c r="AB185" s="3">
-        <v>3.7022036528891879E-3</v>
+        <v>3.7817923076893319E-3</v>
       </c>
       <c r="AC185" s="3">
         <v>3.7644382430159717E-3</v>
@@ -14901,7 +14931,7 @@
         <v>19191.5</v>
       </c>
       <c r="AG185">
-        <v>11249.65</v>
+        <v>11021.7</v>
       </c>
       <c r="AH185">
         <v>8131</v>
@@ -14984,7 +15014,7 @@
         <v>3.532772280022245E-3</v>
       </c>
       <c r="AB186" s="3">
-        <v>3.7737594035710388E-3</v>
+        <v>3.7144645737890668E-3</v>
       </c>
       <c r="AC186" s="3">
         <v>3.784837612093857E-3</v>
@@ -14996,7 +15026,7 @@
         <v>19191.5</v>
       </c>
       <c r="AG186">
-        <v>11021.7</v>
+        <v>11249.65</v>
       </c>
       <c r="AH186">
         <v>8131</v>
@@ -15079,7 +15109,7 @@
         <v>3.5614251528410801E-3</v>
       </c>
       <c r="AB187" s="3">
-        <v>3.7095278182746158E-3</v>
+        <v>3.6988166948658213E-3</v>
       </c>
       <c r="AC187" s="3">
         <v>3.8305058514758144E-3</v>
@@ -15174,7 +15204,7 @@
         <v>3.7027401202844867E-3</v>
       </c>
       <c r="AB188" s="3">
-        <v>3.6989432569761011E-3</v>
+        <v>3.687088023689322E-3</v>
       </c>
       <c r="AC188" s="3">
         <v>3.8272913656647221E-3</v>
@@ -15269,7 +15299,7 @@
         <v>5.9258819931569118E-3</v>
       </c>
       <c r="AB189" s="3">
-        <v>3.7593071839947282E-3</v>
+        <v>3.7604995495845841E-3</v>
       </c>
       <c r="AC189" s="3">
         <v>3.899955333751402E-3</v>
@@ -15281,7 +15311,7 @@
         <v>19191.5</v>
       </c>
       <c r="AG189">
-        <v>11249.65</v>
+        <v>11347.4</v>
       </c>
       <c r="AH189">
         <v>8131</v>
@@ -15364,7 +15394,7 @@
         <v>6.9769800979326835E-3</v>
       </c>
       <c r="AB190" s="3">
-        <v>3.8642569866280709E-3</v>
+        <v>3.9465057068438242E-3</v>
       </c>
       <c r="AC190" s="3">
         <v>3.9807445742585153E-3</v>
@@ -15376,10 +15406,10 @@
         <v>19191.5</v>
       </c>
       <c r="AG190">
-        <v>11347.4</v>
+        <v>11522.05</v>
       </c>
       <c r="AH190">
-        <v>8131</v>
+        <v>8152.4</v>
       </c>
     </row>
     <row r="191" spans="1:34" x14ac:dyDescent="0.3">
@@ -15459,7 +15489,7 @@
         <v>7.1703013452015796E-3</v>
       </c>
       <c r="AB191" s="3">
-        <v>4.0504991145327842E-3</v>
+        <v>4.0162886399823976E-3</v>
       </c>
       <c r="AC191" s="3">
         <v>4.0747083922411274E-3</v>
@@ -15468,13 +15498,13 @@
         <v>5.4136868392037378E-3</v>
       </c>
       <c r="AF191">
-        <v>19191.5</v>
+        <v>20234.699999999997</v>
       </c>
       <c r="AG191">
-        <v>11522.05</v>
+        <v>12346</v>
       </c>
       <c r="AH191">
-        <v>8152.4</v>
+        <v>8188.4250000000002</v>
       </c>
     </row>
     <row r="192" spans="1:34" x14ac:dyDescent="0.3">
@@ -15554,7 +15584,7 @@
         <v>9.3862849625692135E-3</v>
       </c>
       <c r="AB192" s="3">
-        <v>4.1895143278077793E-3</v>
+        <v>4.2410970902707103E-3</v>
       </c>
       <c r="AC192" s="3">
         <v>4.1534443545314234E-3</v>
@@ -15563,10 +15593,10 @@
         <v>5.441331006855653E-3</v>
       </c>
       <c r="AF192">
-        <v>20234.699999999997</v>
+        <v>20698.900000000001</v>
       </c>
       <c r="AG192">
-        <v>12346</v>
+        <v>13340.150000000001</v>
       </c>
       <c r="AH192">
         <v>8188.4250000000002</v>
@@ -15649,7 +15679,7 @@
         <v>6.4303083986219089E-3</v>
       </c>
       <c r="AB193" s="3">
-        <v>4.3117168098949429E-3</v>
+        <v>4.2899749996578784E-3</v>
       </c>
       <c r="AC193" s="3">
         <v>4.2429357844297856E-3</v>
@@ -15658,13 +15688,13 @@
         <v>5.4176358987933909E-3</v>
       </c>
       <c r="AF193">
-        <v>20698.900000000001</v>
+        <v>21211.72</v>
       </c>
       <c r="AG193">
         <v>13340.150000000001</v>
       </c>
       <c r="AH193">
-        <v>8188.4250000000002</v>
+        <v>8249.2250000000004</v>
       </c>
     </row>
     <row r="194" spans="1:34" x14ac:dyDescent="0.3">
@@ -15744,7 +15774,7 @@
         <v>1.143041769463804E-2</v>
       </c>
       <c r="AB194" s="3">
-        <v>4.5203118607862712E-3</v>
+        <v>4.54763465244857E-3</v>
       </c>
       <c r="AC194" s="3">
         <v>4.4313701723688185E-3</v>
@@ -15753,13 +15783,13 @@
         <v>5.4629295964237811E-3</v>
       </c>
       <c r="AF194">
-        <v>21211.72</v>
+        <v>21996.120000000003</v>
       </c>
       <c r="AG194">
-        <v>13340.150000000001</v>
+        <v>13701.3</v>
       </c>
       <c r="AH194">
-        <v>8249.2250000000004</v>
+        <v>8318.7999999999993</v>
       </c>
     </row>
     <row r="195" spans="1:34" x14ac:dyDescent="0.3">
@@ -15839,7 +15869,7 @@
         <v>1.1715782145426124E-2</v>
       </c>
       <c r="AB195" s="3">
-        <v>4.7788652167381684E-3</v>
+        <v>4.7396864041107578E-3</v>
       </c>
       <c r="AC195" s="3">
         <v>4.5132572435453485E-3</v>
@@ -15851,7 +15881,7 @@
         <v>21996.120000000003</v>
       </c>
       <c r="AG195">
-        <v>13701.3</v>
+        <v>13939.3</v>
       </c>
       <c r="AH195">
         <v>8318.7999999999993</v>
@@ -15934,7 +15964,7 @@
         <v>7.4940839791239888E-3</v>
       </c>
       <c r="AB196" s="3">
-        <v>4.8285379387886041E-3</v>
+        <v>4.9144083627622017E-3</v>
       </c>
       <c r="AC196" s="3">
         <v>4.5654285422211264E-3</v>
@@ -15943,10 +15973,10 @@
         <v>5.4692780723639579E-3</v>
       </c>
       <c r="AF196">
-        <v>21996.120000000003</v>
+        <v>24845.1</v>
       </c>
       <c r="AG196">
-        <v>13939.3</v>
+        <v>15185.95</v>
       </c>
       <c r="AH196">
         <v>8318.7999999999993</v>
@@ -16029,7 +16059,7 @@
         <v>8.1045438953866178E-3</v>
       </c>
       <c r="AB197" s="3">
-        <v>5.0173159605887956E-3</v>
+        <v>5.1283293150841012E-3</v>
       </c>
       <c r="AC197" s="3">
         <v>4.5767783971055317E-3</v>
@@ -16041,7 +16071,7 @@
         <v>24845.1</v>
       </c>
       <c r="AG197">
-        <v>15185.95</v>
+        <v>17282.75</v>
       </c>
       <c r="AH197">
         <v>8318.7999999999993</v>
@@ -16124,7 +16154,7 @@
         <v>9.242059627096344E-3</v>
       </c>
       <c r="AB198" s="3">
-        <v>5.2610302928909483E-3</v>
+        <v>5.4320927057791681E-3</v>
       </c>
       <c r="AC198" s="3">
         <v>4.7119620639527408E-3</v>
@@ -16133,10 +16163,10 @@
         <v>5.4888741418327586E-3</v>
       </c>
       <c r="AF198">
-        <v>24845.1</v>
+        <v>28786.97</v>
       </c>
       <c r="AG198">
-        <v>17282.75</v>
+        <v>19191.5</v>
       </c>
       <c r="AH198">
         <v>8318.7999999999993</v>
@@ -16219,7 +16249,7 @@
         <v>4.699640392408222E-3</v>
       </c>
       <c r="AB199" s="3">
-        <v>5.4084652117994602E-3</v>
+        <v>5.5646832768916944E-3</v>
       </c>
       <c r="AC199" s="3">
         <v>4.777641530150434E-3</v>
@@ -16228,13 +16258,13 @@
         <v>5.5114678242524926E-3</v>
       </c>
       <c r="AF199">
-        <v>28786.97</v>
+        <v>31332.370000000003</v>
       </c>
       <c r="AG199">
-        <v>19191.5</v>
+        <v>20234.699999999997</v>
       </c>
       <c r="AH199">
-        <v>8318.7999999999993</v>
+        <v>8367.4249999999993</v>
       </c>
     </row>
     <row r="200" spans="1:34" x14ac:dyDescent="0.3">
@@ -16314,7 +16344,7 @@
         <v>5.436779274995418E-3</v>
       </c>
       <c r="AB200" s="3">
-        <v>5.5605573413466539E-3</v>
+        <v>5.7158396000499285E-3</v>
       </c>
       <c r="AC200" s="3">
         <v>4.8499984642332477E-3</v>
@@ -16326,10 +16356,10 @@
         <v>31332.370000000003</v>
       </c>
       <c r="AG200">
-        <v>20234.699999999997</v>
+        <v>20698.900000000001</v>
       </c>
       <c r="AH200">
-        <v>8367.4249999999993</v>
+        <v>8408.7250000000004</v>
       </c>
     </row>
     <row r="201" spans="1:34" x14ac:dyDescent="0.3">
@@ -16409,7 +16439,7 @@
         <v>5.896597634786449E-3</v>
       </c>
       <c r="AB201" s="3">
-        <v>5.7216705043962677E-3</v>
+        <v>5.8239973564448103E-3</v>
       </c>
       <c r="AC201" s="3">
         <v>4.8758439234919569E-3</v>
@@ -16418,13 +16448,13 @@
         <v>5.5620078027309137E-3</v>
       </c>
       <c r="AF201">
-        <v>31332.370000000003</v>
+        <v>28786.97</v>
       </c>
       <c r="AG201">
         <v>20698.900000000001</v>
       </c>
       <c r="AH201">
-        <v>8408.7250000000004</v>
+        <v>8451.2000000000007</v>
       </c>
     </row>
     <row r="202" spans="1:34" x14ac:dyDescent="0.3">
@@ -16504,7 +16534,7 @@
         <v>3.346833268699223E-3</v>
       </c>
       <c r="AB202" s="3">
-        <v>5.7440888374852752E-3</v>
+        <v>5.8377401311905013E-3</v>
       </c>
       <c r="AC202" s="3">
         <v>4.9223296598517397E-3</v>
@@ -16513,7 +16543,7 @@
         <v>5.5511170310316446E-3</v>
       </c>
       <c r="AF202">
-        <v>28786.97</v>
+        <v>24845.1</v>
       </c>
       <c r="AG202">
         <v>20698.900000000001</v>
@@ -16599,7 +16629,7 @@
         <v>2.0997223961383149E-4</v>
       </c>
       <c r="AB203" s="3">
-        <v>5.6561992314622216E-3</v>
+        <v>5.6656728933621647E-3</v>
       </c>
       <c r="AC203" s="3">
         <v>4.7686796515212923E-3</v>
@@ -16614,7 +16644,7 @@
         <v>20698.900000000001</v>
       </c>
       <c r="AH203">
-        <v>8451.2000000000007</v>
+        <v>8482.9</v>
       </c>
     </row>
     <row r="204" spans="1:34" x14ac:dyDescent="0.3">
@@ -16694,7 +16724,7 @@
         <v>7.9275618584850882E-4</v>
       </c>
       <c r="AB204" s="3">
-        <v>5.5084820318294665E-3</v>
+        <v>5.1212272096914221E-3</v>
       </c>
       <c r="AC204" s="3">
         <v>4.6386766249657445E-3</v>
@@ -16709,7 +16739,7 @@
         <v>20698.900000000001</v>
       </c>
       <c r="AH204">
-        <v>8482.9</v>
+        <v>8516.6</v>
       </c>
     </row>
     <row r="205" spans="1:34" x14ac:dyDescent="0.3">
@@ -16789,7 +16819,7 @@
         <v>5.3454690849354947E-3</v>
       </c>
       <c r="AB205" s="3">
-        <v>5.1284608185702633E-3</v>
+        <v>5.0908832158796345E-3</v>
       </c>
       <c r="AC205" s="3">
         <v>4.6744200541589381E-3</v>
@@ -16798,13 +16828,13 @@
         <v>5.5548965053158744E-3</v>
       </c>
       <c r="AF205">
-        <v>24845.1</v>
+        <v>21748.6</v>
       </c>
       <c r="AG205">
         <v>20698.900000000001</v>
       </c>
       <c r="AH205">
-        <v>8516.6</v>
+        <v>8482.9</v>
       </c>
     </row>
     <row r="206" spans="1:34" x14ac:dyDescent="0.3">
@@ -16884,7 +16914,7 @@
         <v>7.3468432068716227E-3</v>
       </c>
       <c r="AB206" s="3">
-        <v>5.1636561188148598E-3</v>
+        <v>5.2274907047849617E-3</v>
       </c>
       <c r="AC206" s="3">
         <v>4.6344871252674506E-3</v>
@@ -16899,7 +16929,7 @@
         <v>20698.900000000001</v>
       </c>
       <c r="AH206">
-        <v>8482.9</v>
+        <v>8516.6</v>
       </c>
     </row>
     <row r="207" spans="1:34" x14ac:dyDescent="0.3">
@@ -16979,7 +17009,7 @@
         <v>7.5990462315105312E-3</v>
       </c>
       <c r="AB207" s="3">
-        <v>5.3039924959696573E-3</v>
+        <v>5.4494244870320098E-3</v>
       </c>
       <c r="AC207" s="3">
         <v>4.6692708191896637E-3</v>
@@ -16988,13 +17018,13 @@
         <v>5.593937686967222E-3</v>
       </c>
       <c r="AF207">
-        <v>21748.6</v>
+        <v>20989.1</v>
       </c>
       <c r="AG207">
         <v>20698.900000000001</v>
       </c>
       <c r="AH207">
-        <v>8516.6</v>
+        <v>8556.6</v>
       </c>
     </row>
     <row r="208" spans="1:34" x14ac:dyDescent="0.3">
@@ -17074,7 +17104,7 @@
         <v>5.7799425512493618E-3</v>
       </c>
       <c r="AB208" s="3">
-        <v>5.4600863600712795E-3</v>
+        <v>5.6103566486808958E-3</v>
       </c>
       <c r="AC208" s="3">
         <v>4.6808717742111506E-3</v>
@@ -17086,10 +17116,10 @@
         <v>20989.1</v>
       </c>
       <c r="AG208">
-        <v>20698.900000000001</v>
+        <v>20234.699999999997</v>
       </c>
       <c r="AH208">
-        <v>8556.6</v>
+        <v>8652.85</v>
       </c>
     </row>
     <row r="209" spans="1:34" x14ac:dyDescent="0.3">
@@ -17169,7 +17199,7 @@
         <v>2.0014949899551659E-3</v>
       </c>
       <c r="AB209" s="3">
-        <v>5.4939417564639371E-3</v>
+        <v>5.6351428892762829E-3</v>
       </c>
       <c r="AC209" s="3">
         <v>4.6157808985484846E-3</v>
@@ -17178,13 +17208,13 @@
         <v>5.5856376936657967E-3</v>
       </c>
       <c r="AF209">
-        <v>20989.1</v>
+        <v>21773.5</v>
       </c>
       <c r="AG209">
-        <v>20234.699999999997</v>
+        <v>20698.900000000001</v>
       </c>
       <c r="AH209">
-        <v>8652.85</v>
+        <v>8798.2000000000007</v>
       </c>
     </row>
     <row r="210" spans="1:34" x14ac:dyDescent="0.3">
@@ -17264,7 +17294,7 @@
         <v>4.3835442618335163E-3</v>
       </c>
       <c r="AB210" s="3">
-        <v>5.5947687400039357E-3</v>
+        <v>5.7625855930906076E-3</v>
       </c>
       <c r="AC210" s="3">
         <v>4.6839426784312001E-3</v>
@@ -17273,10 +17303,10 @@
         <v>5.5783349570580863E-3</v>
       </c>
       <c r="AF210">
-        <v>21773.5</v>
+        <v>24845.1</v>
       </c>
       <c r="AG210">
-        <v>20698.900000000001</v>
+        <v>20989.1</v>
       </c>
       <c r="AH210">
         <v>8798.2000000000007</v>
@@ -17359,7 +17389,7 @@
         <v>7.9207399980685267E-4</v>
       </c>
       <c r="AB211" s="3">
-        <v>5.6022465094362935E-3</v>
+        <v>5.7057771254841573E-3</v>
       </c>
       <c r="AC211" s="3">
         <v>4.662142806463254E-3</v>
@@ -17371,7 +17401,7 @@
         <v>24845.1</v>
       </c>
       <c r="AG211">
-        <v>20989.1</v>
+        <v>21236.620000000003</v>
       </c>
       <c r="AH211">
         <v>8798.2000000000007</v>
@@ -17454,7 +17484,7 @@
         <v>1.4377065890405216E-3</v>
       </c>
       <c r="AB212" s="3">
-        <v>5.568097430760169E-3</v>
+        <v>5.4038434101280029E-3</v>
       </c>
       <c r="AC212" s="3">
         <v>4.5532211074926204E-3</v>
@@ -17463,10 +17493,10 @@
         <v>5.5664685095821627E-3</v>
       </c>
       <c r="AF212">
-        <v>24845.1</v>
+        <v>28786.97</v>
       </c>
       <c r="AG212">
-        <v>21236.620000000003</v>
+        <v>21996.120000000003</v>
       </c>
       <c r="AH212">
         <v>8798.2000000000007</v>
@@ -17549,7 +17579,7 @@
         <v>4.0234033653563372E-3</v>
       </c>
       <c r="AB213" s="3">
-        <v>5.35931308610311E-3</v>
+        <v>5.4185865063566966E-3</v>
       </c>
       <c r="AC213" s="3">
         <v>4.5686185980847484E-3</v>
@@ -17558,10 +17588,10 @@
         <v>5.5718248218207308E-3</v>
       </c>
       <c r="AF213">
-        <v>28786.97</v>
+        <v>24845.1</v>
       </c>
       <c r="AG213">
-        <v>21996.120000000003</v>
+        <v>21236.620000000003</v>
       </c>
       <c r="AH213">
         <v>8798.2000000000007</v>
@@ -17644,7 +17674,7 @@
         <v>8.5125018443319433E-3</v>
       </c>
       <c r="AB214" s="3">
-        <v>5.5183902269365431E-3</v>
+        <v>5.5503717384793837E-3</v>
       </c>
       <c r="AC214" s="3">
         <v>4.6174416675518175E-3</v>
@@ -17653,10 +17683,10 @@
         <v>5.5923566213196768E-3</v>
       </c>
       <c r="AF214">
-        <v>24845.1</v>
+        <v>24085.599999999999</v>
       </c>
       <c r="AG214">
-        <v>21236.620000000003</v>
+        <v>20989.1</v>
       </c>
       <c r="AH214">
         <v>8798.2000000000007</v>
@@ -17739,7 +17769,7 @@
         <v>2.9326399672791048E-5</v>
       </c>
       <c r="AB215" s="3">
-        <v>5.3722735017436869E-3</v>
+        <v>5.410250440440567E-3</v>
       </c>
       <c r="AC215" s="3">
         <v>4.5960213740649496E-3</v>
@@ -17754,7 +17784,7 @@
         <v>20989.1</v>
       </c>
       <c r="AH215">
-        <v>8798.2000000000007</v>
+        <v>8875.35</v>
       </c>
     </row>
     <row r="216" spans="1:34" x14ac:dyDescent="0.3">
@@ -17834,7 +17864,7 @@
         <v>6.0661999686995038E-4</v>
       </c>
       <c r="AB216" s="3">
-        <v>5.2552946196802244E-3</v>
+        <v>5.3127120310021573E-3</v>
       </c>
       <c r="AC216" s="3">
         <v>4.5135883023956118E-3</v>
@@ -17849,7 +17879,7 @@
         <v>20989.1</v>
       </c>
       <c r="AH216">
-        <v>8875.35</v>
+        <v>8885.9</v>
       </c>
     </row>
     <row r="217" spans="1:34" x14ac:dyDescent="0.3">
@@ -17929,7 +17959,7 @@
         <v>1.7725145838722867E-3</v>
       </c>
       <c r="AB217" s="3">
-        <v>5.1985121133528069E-3</v>
+        <v>5.2530816787031975E-3</v>
       </c>
       <c r="AC217" s="3">
         <v>4.4759491867845096E-3</v>
@@ -17944,7 +17974,7 @@
         <v>20989.1</v>
       </c>
       <c r="AH217">
-        <v>8885.9</v>
+        <v>9058.75</v>
       </c>
     </row>
     <row r="218" spans="1:34" x14ac:dyDescent="0.3">
@@ -18024,7 +18054,7 @@
         <v>4.154318335896745E-3</v>
       </c>
       <c r="AB218" s="3">
-        <v>5.2176376999029895E-3</v>
+        <v>5.2681342858902731E-3</v>
       </c>
       <c r="AC218" s="3">
         <v>4.4776111547897976E-3</v>
@@ -18036,10 +18066,10 @@
         <v>24085.599999999999</v>
       </c>
       <c r="AG218">
-        <v>20989.1</v>
+        <v>20908.2</v>
       </c>
       <c r="AH218">
-        <v>9058.75</v>
+        <v>8885.9</v>
       </c>
     </row>
     <row r="219" spans="1:34" x14ac:dyDescent="0.3">
@@ -18119,7 +18149,7 @@
         <v>5.9093481102681089E-3</v>
       </c>
       <c r="AB219" s="3">
-        <v>5.2888186028056871E-3</v>
+        <v>5.2675831564606458E-3</v>
       </c>
       <c r="AC219" s="3">
         <v>4.5140413530226154E-3</v>
@@ -18128,13 +18158,13 @@
         <v>5.5505246403589458E-3</v>
       </c>
       <c r="AF219">
-        <v>24085.599999999999</v>
+        <v>30882.6</v>
       </c>
       <c r="AG219">
-        <v>20908.2</v>
+        <v>20989.1</v>
       </c>
       <c r="AH219">
-        <v>8885.9</v>
+        <v>9058.75</v>
       </c>
     </row>
     <row r="220" spans="1:34" x14ac:dyDescent="0.3">
@@ -18214,7 +18244,7 @@
         <v>2.985882635327064E-3</v>
       </c>
       <c r="AB220" s="3">
-        <v>5.1939799138434337E-3</v>
+        <v>5.1345465743737918E-3</v>
       </c>
       <c r="AC220" s="3">
         <v>4.540526140608808E-3</v>
@@ -18229,7 +18259,7 @@
         <v>20989.1</v>
       </c>
       <c r="AH220">
-        <v>9058.75</v>
+        <v>9273.0499999999993</v>
       </c>
     </row>
     <row r="221" spans="1:34" x14ac:dyDescent="0.3">
@@ -18309,7 +18339,7 @@
         <v>3.1408286684957432E-3</v>
       </c>
       <c r="AB221" s="3">
-        <v>5.0702330935390163E-3</v>
+        <v>5.0002308184835973E-3</v>
       </c>
       <c r="AC221" s="3">
         <v>4.5082597292329975E-3</v>
@@ -18318,13 +18348,13 @@
         <v>5.5160074223845161E-3</v>
       </c>
       <c r="AF221">
-        <v>30882.6</v>
+        <v>35207.4</v>
       </c>
       <c r="AG221">
-        <v>20989.1</v>
+        <v>21236.620000000003</v>
       </c>
       <c r="AH221">
-        <v>9273.0499999999993</v>
+        <v>9436.9</v>
       </c>
     </row>
     <row r="222" spans="1:34" x14ac:dyDescent="0.3">
@@ -18404,7 +18434,7 @@
         <v>1.4017595054107712E-3</v>
       </c>
       <c r="AB222" s="3">
-        <v>4.8841510987070545E-3</v>
+        <v>4.7340799699116497E-3</v>
       </c>
       <c r="AC222" s="3">
         <v>4.48758853009118E-3</v>
@@ -18413,13 +18443,13 @@
         <v>5.4981295809144702E-3</v>
       </c>
       <c r="AF222">
-        <v>35207.4</v>
+        <v>36713.100000000006</v>
       </c>
       <c r="AG222">
-        <v>21236.620000000003</v>
+        <v>21996.120000000003</v>
       </c>
       <c r="AH222">
-        <v>9436.9</v>
+        <v>9691.5750000000007</v>
       </c>
     </row>
     <row r="223" spans="1:34" x14ac:dyDescent="0.3">
@@ -18499,7 +18529,7 @@
         <v>3.1284297450386855E-3</v>
       </c>
       <c r="AB223" s="3">
-        <v>4.6822848013673606E-3</v>
+        <v>4.6240173481255416E-3</v>
       </c>
       <c r="AC223" s="3">
         <v>4.4569961738917105E-3</v>
@@ -18514,7 +18544,7 @@
         <v>21996.120000000003</v>
       </c>
       <c r="AH223">
-        <v>9691.5750000000007</v>
+        <v>9877.625</v>
       </c>
     </row>
     <row r="224" spans="1:34" x14ac:dyDescent="0.3">
@@ -18594,7 +18624,7 @@
         <v>2.4029085338477252E-3</v>
       </c>
       <c r="AB224" s="3">
-        <v>4.5523686766972254E-3</v>
+        <v>4.3231003760991985E-3</v>
       </c>
       <c r="AC224" s="3">
         <v>4.4353675142738839E-3</v>
@@ -18603,10 +18633,10 @@
         <v>5.4890279736227437E-3</v>
       </c>
       <c r="AF224">
-        <v>36713.100000000006</v>
+        <v>29354.25</v>
       </c>
       <c r="AG224">
-        <v>21996.120000000003</v>
+        <v>22717.35</v>
       </c>
       <c r="AH224">
         <v>9877.625</v>
@@ -18689,7 +18719,7 @@
         <v>2.859283078021857E-3</v>
       </c>
       <c r="AB225" s="3">
-        <v>4.2758804632579937E-3</v>
+        <v>4.0278837405190561E-3</v>
       </c>
       <c r="AC225" s="3">
         <v>4.383785072314907E-3</v>
@@ -18704,7 +18734,7 @@
         <v>22717.35</v>
       </c>
       <c r="AH225">
-        <v>9877.625</v>
+        <v>10102.25</v>
       </c>
     </row>
     <row r="226" spans="1:34" x14ac:dyDescent="0.3">
@@ -18784,7 +18814,7 @@
         <v>3.216386039351482E-3</v>
       </c>
       <c r="AB226" s="3">
-        <v>4.001706395320102E-3</v>
+        <v>3.8852938091933058E-3</v>
       </c>
       <c r="AC226" s="3">
         <v>4.3998510859777533E-3</v>
@@ -18793,13 +18823,13 @@
         <v>5.3763951665175497E-3</v>
       </c>
       <c r="AF226">
-        <v>29354.25</v>
+        <v>21957.85</v>
       </c>
       <c r="AG226">
         <v>22717.35</v>
       </c>
       <c r="AH226">
-        <v>10102.25</v>
+        <v>10248.25</v>
       </c>
     </row>
     <row r="227" spans="1:34" x14ac:dyDescent="0.3">
@@ -18879,7 +18909,7 @@
         <v>5.2572974737266076E-3</v>
       </c>
       <c r="AB227" s="3">
-        <v>3.9295519919201865E-3</v>
+        <v>3.7903855951379722E-3</v>
       </c>
       <c r="AC227" s="3">
         <v>4.4593574551110371E-3</v>
@@ -18894,7 +18924,7 @@
         <v>22717.35</v>
       </c>
       <c r="AH227">
-        <v>10248.25</v>
+        <v>10583</v>
       </c>
     </row>
     <row r="228" spans="1:34" x14ac:dyDescent="0.3">
@@ -18974,7 +19004,7 @@
         <v>6.1672473584886145E-3</v>
       </c>
       <c r="AB228" s="3">
-        <v>3.8670585552460575E-3</v>
+        <v>3.6878918528510476E-3</v>
       </c>
       <c r="AC228" s="3">
         <v>4.5599922793151081E-3</v>
@@ -18983,13 +19013,13 @@
         <v>5.3392973734732764E-3</v>
       </c>
       <c r="AF228">
-        <v>21957.85</v>
+        <v>20933.099999999999</v>
       </c>
       <c r="AG228">
         <v>22717.35</v>
       </c>
       <c r="AH228">
-        <v>10583</v>
+        <v>10633.9</v>
       </c>
     </row>
     <row r="229" spans="1:34" x14ac:dyDescent="0.3">
@@ -19069,7 +19099,7 @@
         <v>7.6440108876540958E-3</v>
       </c>
       <c r="AB229" s="3">
-        <v>3.8155085959092104E-3</v>
+        <v>3.7860375360259102E-3</v>
       </c>
       <c r="AC229" s="3">
         <v>4.6753604064588023E-3</v>
@@ -19164,7 +19194,7 @@
         <v>4.1229575348897818E-3</v>
       </c>
       <c r="AB230" s="3">
-        <v>3.7969059230860353E-3</v>
+        <v>3.7422434780223892E-3</v>
       </c>
       <c r="AC230" s="3">
         <v>4.7290415390361584E-3</v>
@@ -19173,13 +19203,13 @@
         <v>5.3617193946910776E-3</v>
       </c>
       <c r="AF230">
-        <v>20933.099999999999</v>
+        <v>19063.245000000003</v>
       </c>
       <c r="AG230">
-        <v>22717.35</v>
+        <v>22271.1</v>
       </c>
       <c r="AH230">
-        <v>10633.9</v>
+        <v>10772.25</v>
       </c>
     </row>
     <row r="231" spans="1:34" x14ac:dyDescent="0.3">
@@ -19259,7 +19289,7 @@
         <v>5.2966897981086003E-3</v>
       </c>
       <c r="AB231" s="3">
-        <v>3.7923869077025893E-3</v>
+        <v>3.7222465501331272E-3</v>
       </c>
       <c r="AC231" s="3">
         <v>4.7731219532889686E-3</v>
@@ -19271,10 +19301,10 @@
         <v>19063.245000000003</v>
       </c>
       <c r="AG231">
-        <v>22271.1</v>
+        <v>21511.599999999999</v>
       </c>
       <c r="AH231">
-        <v>10772.25</v>
+        <v>10876.900000000001</v>
       </c>
     </row>
     <row r="232" spans="1:34" x14ac:dyDescent="0.3">
@@ -19354,7 +19384,7 @@
         <v>2.790413446165374E-4</v>
       </c>
       <c r="AB232" s="3">
-        <v>3.6111754144713018E-3</v>
+        <v>3.6199868193303713E-3</v>
       </c>
       <c r="AC232" s="3">
         <v>4.7288634752604367E-3</v>
@@ -19363,7 +19393,7 @@
         <v>5.2316582770151531E-3</v>
       </c>
       <c r="AF232">
-        <v>19063.245000000003</v>
+        <v>20933.099999999999</v>
       </c>
       <c r="AG232">
         <v>21511.599999999999</v>
@@ -19449,7 +19479,7 @@
         <v>3.2686645776832668E-3</v>
       </c>
       <c r="AB233" s="3">
-        <v>3.6086538437933679E-3</v>
+        <v>3.7219432305993522E-3</v>
       </c>
       <c r="AC233" s="3">
         <v>4.6938080619807589E-3</v>
@@ -19458,13 +19488,13 @@
         <v>5.2230174566701097E-3</v>
       </c>
       <c r="AF233">
-        <v>20933.099999999999</v>
+        <v>21511.599999999999</v>
       </c>
       <c r="AG233">
-        <v>21511.599999999999</v>
+        <v>22271.1</v>
       </c>
       <c r="AH233">
-        <v>10876.900000000001</v>
+        <v>10922.7</v>
       </c>
     </row>
     <row r="234" spans="1:34" x14ac:dyDescent="0.3">
@@ -19544,7 +19574,7 @@
         <v>1.5833679654495558E-3</v>
       </c>
       <c r="AB234" s="3">
-        <v>3.6529569317235526E-3</v>
+        <v>3.7482969565860538E-3</v>
       </c>
       <c r="AC234" s="3">
         <v>4.4347620831387382E-3</v>
@@ -19553,13 +19583,13 @@
         <v>5.1350139356579035E-3</v>
       </c>
       <c r="AF234">
-        <v>21511.599999999999</v>
+        <v>22455.45</v>
       </c>
       <c r="AG234">
-        <v>22271.1</v>
+        <v>22717.35</v>
       </c>
       <c r="AH234">
-        <v>10922.7</v>
+        <v>10985.099999999999</v>
       </c>
     </row>
     <row r="235" spans="1:34" x14ac:dyDescent="0.3">
@@ -19639,7 +19669,7 @@
         <v>1.4630520548297721E-3</v>
       </c>
       <c r="AB235" s="3">
-        <v>3.6745793791100449E-3</v>
+        <v>3.6188830555825297E-3</v>
       </c>
       <c r="AC235" s="3">
         <v>4.3548831357310821E-3</v>
@@ -19651,7 +19681,7 @@
         <v>22455.45</v>
       </c>
       <c r="AG235">
-        <v>22717.35</v>
+        <v>22271.1</v>
       </c>
       <c r="AH235">
         <v>10985.099999999999</v>
@@ -19734,7 +19764,7 @@
         <v>3.8311886549257101E-3</v>
       </c>
       <c r="AB236" s="3">
-        <v>3.6257316233032776E-3</v>
+        <v>3.5016945705176662E-3</v>
       </c>
       <c r="AC236" s="3">
         <v>4.3645926376513133E-3</v>
@@ -19743,13 +19773,13 @@
         <v>5.0473067089231577E-3</v>
       </c>
       <c r="AF236">
-        <v>22455.45</v>
+        <v>28269.599999999999</v>
       </c>
       <c r="AG236">
-        <v>22271.1</v>
+        <v>22717.35</v>
       </c>
       <c r="AH236">
-        <v>10985.099999999999</v>
+        <v>11084.099999999999</v>
       </c>
     </row>
     <row r="237" spans="1:34" x14ac:dyDescent="0.3">
@@ -19829,7 +19859,7 @@
         <v>3.3732226812787092E-3</v>
       </c>
       <c r="AB237" s="3">
-        <v>3.4975503160260867E-3</v>
+        <v>3.3608337855099385E-3</v>
       </c>
       <c r="AC237" s="3">
         <v>4.4051291362709744E-3</v>
@@ -19838,13 +19868,13 @@
         <v>5.0560923609963533E-3</v>
       </c>
       <c r="AF237">
-        <v>28269.599999999999</v>
+        <v>32133.5</v>
       </c>
       <c r="AG237">
         <v>22717.35</v>
       </c>
       <c r="AH237">
-        <v>11084.099999999999</v>
+        <v>11249.65</v>
       </c>
     </row>
     <row r="238" spans="1:34" x14ac:dyDescent="0.3">
@@ -19924,7 +19954,7 @@
         <v>6.1756848495284622E-3</v>
       </c>
       <c r="AB238" s="3">
-        <v>3.4516354327363426E-3</v>
+        <v>3.3740251954525752E-3</v>
       </c>
       <c r="AC238" s="3">
         <v>4.4921909220667355E-3</v>
@@ -20019,7 +20049,7 @@
         <v>1.153336421355422E-2</v>
       </c>
       <c r="AB239" s="3">
-        <v>3.6372296799074672E-3</v>
+        <v>3.6917541695725437E-3</v>
       </c>
       <c r="AC239" s="3">
         <v>4.6634485294244129E-3</v>
@@ -20031,10 +20061,10 @@
         <v>32133.5</v>
       </c>
       <c r="AG239">
-        <v>22717.35</v>
+        <v>25029.45</v>
       </c>
       <c r="AH239">
-        <v>11249.65</v>
+        <v>11347.4</v>
       </c>
     </row>
     <row r="240" spans="1:34" x14ac:dyDescent="0.3">
@@ -20114,7 +20144,7 @@
         <v>4.0214267913853963E-3</v>
       </c>
       <c r="AB240" s="3">
-        <v>3.7023887702761844E-3</v>
+        <v>3.6796835872242731E-3</v>
       </c>
       <c r="AC240" s="3">
         <v>4.7211345901574404E-3</v>
@@ -20123,13 +20153,13 @@
         <v>4.9640750033947949E-3</v>
       </c>
       <c r="AF240">
-        <v>32133.5</v>
+        <v>26765.599999999999</v>
       </c>
       <c r="AG240">
         <v>25029.45</v>
       </c>
       <c r="AH240">
-        <v>11347.4</v>
+        <v>11249.65</v>
       </c>
     </row>
     <row r="241" spans="1:34" x14ac:dyDescent="0.3">
@@ -20209,7 +20239,7 @@
         <v>5.6542737839582191E-3</v>
       </c>
       <c r="AB241" s="3">
-        <v>3.7433800451834327E-3</v>
+        <v>3.841756913362652E-3</v>
       </c>
       <c r="AC241" s="3">
         <v>4.7737670194234047E-3</v>
@@ -20218,10 +20248,10 @@
         <v>4.9514803837900859E-3</v>
       </c>
       <c r="AF241">
-        <v>26765.599999999999</v>
+        <v>22455.45</v>
       </c>
       <c r="AG241">
-        <v>25029.45</v>
+        <v>22717.35</v>
       </c>
       <c r="AH241">
         <v>11249.65</v>
@@ -20304,7 +20334,7 @@
         <v>1.0507252923450672E-3</v>
       </c>
       <c r="AB242" s="3">
-        <v>3.7517236352653106E-3</v>
+        <v>3.828857536806137E-3</v>
       </c>
       <c r="AC242" s="3">
         <v>4.6163504734670702E-3</v>
@@ -20316,10 +20346,10 @@
         <v>22455.45</v>
       </c>
       <c r="AG242">
-        <v>22717.35</v>
+        <v>25029.45</v>
       </c>
       <c r="AH242">
-        <v>11249.65</v>
+        <v>11347.4</v>
       </c>
     </row>
     <row r="243" spans="1:34" x14ac:dyDescent="0.3">
@@ -20399,7 +20429,7 @@
         <v>4.7353681371626877E-3</v>
       </c>
       <c r="AB243" s="3">
-        <v>3.8580998142369932E-3</v>
+        <v>3.8525896958663485E-3</v>
       </c>
       <c r="AC243" s="3">
         <v>4.6355881011115223E-3</v>
@@ -20408,7 +20438,7 @@
         <v>4.9707047282680555E-3</v>
       </c>
       <c r="AF243">
-        <v>22455.45</v>
+        <v>26765.599999999999</v>
       </c>
       <c r="AG243">
         <v>25029.45</v>
@@ -20494,7 +20524,7 @@
         <v>4.2408235480773104E-3</v>
       </c>
       <c r="AB244" s="3">
-        <v>3.8651133685183151E-3</v>
+        <v>3.7102004193245277E-3</v>
       </c>
       <c r="AC244" s="3">
         <v>4.6302860789019552E-3</v>
@@ -20589,7 +20619,7 @@
         <v>5.7806806768381236E-3</v>
       </c>
       <c r="AB245" s="3">
-        <v>3.7769901050507724E-3</v>
+        <v>3.9019122285633718E-3</v>
       </c>
       <c r="AC245" s="3">
         <v>4.6560813345019698E-3</v>
@@ -20604,7 +20634,7 @@
         <v>25029.45</v>
       </c>
       <c r="AH245">
-        <v>11347.4</v>
+        <v>11363.849999999999</v>
       </c>
     </row>
     <row r="246" spans="1:34" x14ac:dyDescent="0.3">
@@ -20684,7 +20714,7 @@
         <v>8.2031632282308919E-3</v>
       </c>
       <c r="AB246" s="3">
-        <v>4.0406622608107111E-3</v>
+        <v>4.1551303362754033E-3</v>
       </c>
       <c r="AC246" s="3">
         <v>4.7339211836387807E-3</v>
@@ -20699,7 +20729,7 @@
         <v>25029.45</v>
       </c>
       <c r="AH246">
-        <v>11363.849999999999</v>
+        <v>11531.099999999999</v>
       </c>
     </row>
     <row r="247" spans="1:34" x14ac:dyDescent="0.3">
@@ -20779,7 +20809,7 @@
         <v>1.2962548083863989E-2</v>
       </c>
       <c r="AB247" s="3">
-        <v>4.4392405861976162E-3</v>
+        <v>4.5281314529417938E-3</v>
       </c>
       <c r="AC247" s="3">
         <v>4.8906065658224952E-3</v>
@@ -20788,10 +20818,10 @@
         <v>5.0689975931600727E-3</v>
       </c>
       <c r="AF247">
-        <v>26765.599999999999</v>
+        <v>22455.45</v>
       </c>
       <c r="AG247">
-        <v>25029.45</v>
+        <v>22455.45</v>
       </c>
       <c r="AH247">
         <v>11531.099999999999</v>
@@ -20874,7 +20904,7 @@
         <v>1.2476942088228471E-2</v>
       </c>
       <c r="AB248" s="3">
-        <v>4.7845446992413635E-3</v>
+        <v>4.8055522446861839E-3</v>
       </c>
       <c r="AC248" s="3">
         <v>5.0368432652882289E-3</v>
@@ -20883,13 +20913,13 @@
         <v>5.0536742637268253E-3</v>
       </c>
       <c r="AF248">
-        <v>22455.45</v>
+        <v>26765.599999999999</v>
       </c>
       <c r="AG248">
-        <v>22455.45</v>
+        <v>25029.45</v>
       </c>
       <c r="AH248">
-        <v>11531.099999999999</v>
+        <v>11709.8</v>
       </c>
     </row>
     <row r="249" spans="1:34" x14ac:dyDescent="0.3">
@@ -20969,7 +20999,7 @@
         <v>8.1532574056011331E-3</v>
       </c>
       <c r="AB249" s="3">
-        <v>4.9135427337479564E-3</v>
+        <v>4.8803492211972853E-3</v>
       </c>
       <c r="AC249" s="3">
         <v>5.0739661888289656E-3</v>
@@ -20978,7 +21008,7 @@
         <v>5.0934459904542415E-3</v>
       </c>
       <c r="AF249">
-        <v>26765.599999999999</v>
+        <v>22455.45</v>
       </c>
       <c r="AG249">
         <v>25029.45</v>
@@ -21064,7 +21094,7 @@
         <v>9.3227954254813117E-3</v>
       </c>
       <c r="AB250" s="3">
-        <v>5.0236539374645117E-3</v>
+        <v>5.09157964753576E-3</v>
       </c>
       <c r="AC250" s="3">
         <v>5.1130631109547759E-3</v>
@@ -21159,7 +21189,7 @@
         <v>8.6652820703803091E-3</v>
       </c>
       <c r="AB251" s="3">
-        <v>5.2068603708533261E-3</v>
+        <v>5.2757280942652453E-3</v>
       </c>
       <c r="AC251" s="3">
         <v>5.1379794563744217E-3</v>
@@ -21171,10 +21201,10 @@
         <v>22455.45</v>
       </c>
       <c r="AG251">
-        <v>25029.45</v>
+        <v>28893.35</v>
       </c>
       <c r="AH251">
-        <v>11709.8</v>
+        <v>11806.5</v>
       </c>
     </row>
     <row r="252" spans="1:34" x14ac:dyDescent="0.3">
@@ -21254,7 +21284,7 @@
         <v>5.0913416033984138E-3</v>
       </c>
       <c r="AB252" s="3">
-        <v>5.2697801429469606E-3</v>
+        <v>5.398714164198167E-3</v>
       </c>
       <c r="AC252" s="3">
         <v>5.0663970670549079E-3</v>
@@ -21269,7 +21299,7 @@
         <v>28893.35</v>
       </c>
       <c r="AH252">
-        <v>11806.5</v>
+        <v>11897.55</v>
       </c>
     </row>
     <row r="253" spans="1:34" x14ac:dyDescent="0.3">
@@ -21349,7 +21379,7 @@
         <v>1.0579523614861586E-2</v>
       </c>
       <c r="AB253" s="3">
-        <v>5.5658370497034381E-3</v>
+        <v>5.64708395985893E-3</v>
       </c>
       <c r="AC253" s="3">
         <v>5.1355506539922362E-3</v>
@@ -21358,13 +21388,13 @@
         <v>5.0307924168098376E-3</v>
       </c>
       <c r="AF253">
-        <v>22455.45</v>
+        <v>26765.599999999999</v>
       </c>
       <c r="AG253">
-        <v>28893.35</v>
+        <v>30932.75</v>
       </c>
       <c r="AH253">
-        <v>11897.55</v>
+        <v>12104.119999999999</v>
       </c>
     </row>
     <row r="254" spans="1:34" x14ac:dyDescent="0.3">
@@ -21444,7 +21474,7 @@
         <v>3.303871869645203E-3</v>
       </c>
       <c r="AB254" s="3">
-        <v>5.5714964730778421E-3</v>
+        <v>5.6771160710521792E-3</v>
       </c>
       <c r="AC254" s="3">
         <v>5.0001082235756888E-3</v>
@@ -21453,10 +21483,10 @@
         <v>5.0374082740628715E-3</v>
       </c>
       <c r="AF254">
+        <v>26319.35</v>
+      </c>
+      <c r="AG254">
         <v>26765.599999999999</v>
-      </c>
-      <c r="AG254">
-        <v>30932.75</v>
       </c>
       <c r="AH254">
         <v>12104.119999999999</v>
@@ -21539,7 +21569,7 @@
         <v>1.6013332344000375E-3</v>
       </c>
       <c r="AB255" s="3">
-        <v>5.5456392053537234E-3</v>
+        <v>5.635184409598119E-3</v>
       </c>
       <c r="AC255" s="3">
         <v>4.8315340750585871E-3</v>
@@ -21548,10 +21578,10 @@
         <v>5.017359530113309E-3</v>
       </c>
       <c r="AF255">
-        <v>26319.35</v>
+        <v>19641.745000000003</v>
       </c>
       <c r="AG255">
-        <v>26765.599999999999</v>
+        <v>22455.45</v>
       </c>
       <c r="AH255">
         <v>12104.119999999999</v>
@@ -21634,7 +21664,7 @@
         <v>2.3630943349224331E-3</v>
       </c>
       <c r="AB256" s="3">
-        <v>5.5296331168666448E-3</v>
+        <v>5.6067413527838171E-3</v>
       </c>
       <c r="AC256" s="3">
         <v>4.7460175809885619E-3</v>
@@ -21646,7 +21676,7 @@
         <v>19641.745000000003</v>
       </c>
       <c r="AG256">
-        <v>22455.45</v>
+        <v>21511.599999999999</v>
       </c>
       <c r="AH256">
         <v>12104.119999999999</v>
@@ -21729,7 +21759,7 @@
         <v>8.4129275806468229E-3</v>
       </c>
       <c r="AB257" s="3">
-        <v>5.6972634891664948E-3</v>
+        <v>5.7119290230144915E-3</v>
       </c>
       <c r="AC257" s="3">
         <v>4.7511573090762314E-3</v>
@@ -21744,7 +21774,7 @@
         <v>21511.599999999999</v>
       </c>
       <c r="AH257">
-        <v>12104.119999999999</v>
+        <v>12331.92</v>
       </c>
     </row>
     <row r="258" spans="1:34" x14ac:dyDescent="0.3">
@@ -21824,7 +21854,7 @@
         <v>3.9107657458690159E-3</v>
       </c>
       <c r="AB258" s="3">
-        <v>5.6538269818162496E-3</v>
+        <v>5.6367129692605046E-3</v>
       </c>
       <c r="AC258" s="3">
         <v>4.6623024110557763E-3</v>
@@ -21833,10 +21863,10 @@
         <v>4.9923720698541608E-3</v>
       </c>
       <c r="AF258">
-        <v>19641.745000000003</v>
+        <v>19404.599999999999</v>
       </c>
       <c r="AG258">
-        <v>21511.599999999999</v>
+        <v>20933.099999999999</v>
       </c>
       <c r="AH258">
         <v>12331.92</v>
@@ -21919,7 +21949,7 @@
         <v>4.095592722141439E-3</v>
       </c>
       <c r="AB259" s="3">
-        <v>5.5869994129018252E-3</v>
+        <v>5.5184323637434158E-3</v>
       </c>
       <c r="AC259" s="3">
         <v>4.652234949884663E-3</v>
@@ -21928,13 +21958,13 @@
         <v>4.9616001553278713E-3</v>
       </c>
       <c r="AF259">
-        <v>19404.599999999999</v>
+        <v>23714.75</v>
       </c>
       <c r="AG259">
         <v>20933.099999999999</v>
       </c>
       <c r="AH259">
-        <v>12331.92</v>
+        <v>12565.375</v>
       </c>
     </row>
     <row r="260" spans="1:34" x14ac:dyDescent="0.3">
@@ -22014,7 +22044,7 @@
         <v>4.3444972451389674E-4</v>
       </c>
       <c r="AB260" s="3">
-        <v>5.3544329237682703E-3</v>
+        <v>5.3954821033975527E-3</v>
       </c>
       <c r="AC260" s="3">
         <v>4.5688627907099714E-3</v>
@@ -22026,7 +22056,7 @@
         <v>23714.75</v>
       </c>
       <c r="AG260">
-        <v>20933.099999999999</v>
+        <v>19063.245000000003</v>
       </c>
       <c r="AH260">
         <v>12565.375</v>
@@ -22109,7 +22139,7 @@
         <v>9.5268579402427722E-3</v>
       </c>
       <c r="AB261" s="3">
-        <v>5.5287522916828823E-3</v>
+        <v>5.536487708135359E-3</v>
       </c>
       <c r="AC261" s="3">
         <v>4.6293671291342429E-3</v>
@@ -22204,7 +22234,7 @@
         <v>1.1369145981123152E-2</v>
       </c>
       <c r="AB262" s="3">
-        <v>5.7246379750059331E-3</v>
+        <v>5.9061578626855796E-3</v>
       </c>
       <c r="AC262" s="3">
         <v>4.7630723410079755E-3</v>
@@ -22213,7 +22243,7 @@
         <v>4.8557211580727662E-3</v>
       </c>
       <c r="AF262">
-        <v>23714.75</v>
+        <v>16079.75</v>
       </c>
       <c r="AG262">
         <v>19063.245000000003</v>
@@ -22299,7 +22329,7 @@
         <v>8.6481436306125037E-3</v>
       </c>
       <c r="AB263" s="3">
-        <v>5.9946090164896739E-3</v>
+        <v>6.0854738311165541E-3</v>
       </c>
       <c r="AC263" s="3">
         <v>4.9037085308579528E-3</v>
@@ -22311,10 +22341,10 @@
         <v>16079.75</v>
       </c>
       <c r="AG263">
-        <v>19063.245000000003</v>
+        <v>20933.099999999999</v>
       </c>
       <c r="AH263">
-        <v>12565.375</v>
+        <v>12882.725</v>
       </c>
     </row>
     <row r="264" spans="1:34" x14ac:dyDescent="0.3">
@@ -22394,7 +22424,7 @@
         <v>5.6649767563026199E-3</v>
       </c>
       <c r="AB264" s="3">
-        <v>6.0719094093483628E-3</v>
+        <v>6.2215274574783227E-3</v>
       </c>
       <c r="AC264" s="3">
         <v>4.9849122070321885E-3</v>
@@ -22406,10 +22436,10 @@
         <v>16079.75</v>
       </c>
       <c r="AG264">
-        <v>20933.099999999999</v>
+        <v>21511.599999999999</v>
       </c>
       <c r="AH264">
-        <v>12882.725</v>
+        <v>13007.6</v>
       </c>
     </row>
     <row r="265" spans="1:34" x14ac:dyDescent="0.3">
@@ -22489,7 +22519,7 @@
         <v>4.83025782391866E-3</v>
       </c>
       <c r="AB265" s="3">
-        <v>6.1766477918796239E-3</v>
+        <v>6.3337676497812858E-3</v>
       </c>
       <c r="AC265" s="3">
         <v>4.9763253526819073E-3</v>
@@ -22498,13 +22528,13 @@
         <v>4.734652091505827E-3</v>
       </c>
       <c r="AF265">
-        <v>16079.75</v>
+        <v>21860.47</v>
       </c>
       <c r="AG265">
-        <v>21511.599999999999</v>
+        <v>22455.45</v>
       </c>
       <c r="AH265">
-        <v>13007.6</v>
+        <v>13345.05</v>
       </c>
     </row>
     <row r="266" spans="1:34" x14ac:dyDescent="0.3">
@@ -22584,7 +22614,7 @@
         <v>8.2465084016325463E-4</v>
       </c>
       <c r="AB266" s="3">
-        <v>6.156054204309736E-3</v>
+        <v>6.233549722622537E-3</v>
       </c>
       <c r="AC266" s="3">
         <v>4.8676221465701018E-3</v>
@@ -22593,7 +22623,7 @@
         <v>4.6993789892427629E-3</v>
       </c>
       <c r="AF266">
-        <v>21860.47</v>
+        <v>13028.4</v>
       </c>
       <c r="AG266">
         <v>22455.45</v>
@@ -22679,7 +22709,7 @@
         <v>2.3561367840541081E-4</v>
       </c>
       <c r="AB267" s="3">
-        <v>6.0400679147445653E-3</v>
+        <v>6.1289627558600941E-3</v>
       </c>
       <c r="AC267" s="3">
         <v>4.7448982706850161E-3</v>
@@ -22688,7 +22718,7 @@
         <v>4.6166342460954362E-3</v>
       </c>
       <c r="AF267">
-        <v>13028.4</v>
+        <v>9177.9</v>
       </c>
       <c r="AG267">
         <v>22455.45</v>
@@ -22774,7 +22804,7 @@
         <v>1.655123141300896E-3</v>
       </c>
       <c r="AB268" s="3">
-        <v>5.9846453489388295E-3</v>
+        <v>5.9782773655858417E-3</v>
       </c>
       <c r="AC268" s="3">
         <v>4.6761512805192085E-3</v>
@@ -22789,7 +22819,7 @@
         <v>22455.45</v>
       </c>
       <c r="AH268">
-        <v>13345.05</v>
+        <v>13340.150000000001</v>
       </c>
     </row>
     <row r="269" spans="1:34" x14ac:dyDescent="0.3">
@@ -22869,7 +22899,7 @@
         <v>1.4979138654669377E-3</v>
       </c>
       <c r="AB269" s="3">
-        <v>5.8337495107432967E-3</v>
+        <v>5.6437623539829325E-3</v>
       </c>
       <c r="AC269" s="3">
         <v>4.6677582617777377E-3</v>
@@ -22878,13 +22908,13 @@
         <v>4.5950321556245685E-3</v>
       </c>
       <c r="AF269">
-        <v>9177.9</v>
+        <v>8906.5</v>
       </c>
       <c r="AG269">
-        <v>22455.45</v>
+        <v>21430.7</v>
       </c>
       <c r="AH269">
-        <v>13340.150000000001</v>
+        <v>12882.725</v>
       </c>
     </row>
     <row r="270" spans="1:34" x14ac:dyDescent="0.3">
@@ -22964,7 +22994,7 @@
         <v>5.5018925291665521E-3</v>
       </c>
       <c r="AB270" s="3">
-        <v>5.6391859080211137E-3</v>
+        <v>5.6931112119089711E-3</v>
       </c>
       <c r="AC270" s="3">
         <v>4.6863973995666221E-3</v>
@@ -22973,10 +23003,10 @@
         <v>4.6001179748321923E-3</v>
       </c>
       <c r="AF270">
-        <v>8906.5</v>
+        <v>8688.1</v>
       </c>
       <c r="AG270">
-        <v>21430.7</v>
+        <v>19063.245000000003</v>
       </c>
       <c r="AH270">
         <v>12882.725</v>
@@ -23059,7 +23089,7 @@
         <v>2.7964784492982009E-3</v>
       </c>
       <c r="AB271" s="3">
-        <v>5.5996714453731391E-3</v>
+        <v>5.5978513674203034E-3</v>
       </c>
       <c r="AC271" s="3">
         <v>4.7198041403914781E-3</v>
@@ -23068,10 +23098,10 @@
         <v>4.6011919952771378E-3</v>
       </c>
       <c r="AF271">
-        <v>8688.1</v>
+        <v>8906.5</v>
       </c>
       <c r="AG271">
-        <v>19063.245000000003</v>
+        <v>17037.145</v>
       </c>
       <c r="AH271">
         <v>12882.725</v>
@@ -23154,7 +23184,7 @@
         <v>3.5139509121631107E-3</v>
       </c>
       <c r="AB272" s="3">
-        <v>5.5306287720894264E-3</v>
+        <v>5.6799588880809045E-3</v>
       </c>
       <c r="AC272" s="3">
         <v>4.754408212443521E-3</v>
@@ -23163,10 +23193,10 @@
         <v>4.6119765851653253E-3</v>
       </c>
       <c r="AF272">
-        <v>8906.5</v>
+        <v>8688.1</v>
       </c>
       <c r="AG272">
-        <v>17037.145</v>
+        <v>16539.5</v>
       </c>
       <c r="AH272">
         <v>12882.725</v>
@@ -23249,7 +23279,7 @@
         <v>1.6764587015513088E-3</v>
       </c>
       <c r="AB273" s="3">
-        <v>5.550813720773499E-3</v>
+        <v>5.577995240227192E-3</v>
       </c>
       <c r="AC273" s="3">
         <v>4.71529246804677E-3</v>
@@ -23264,7 +23294,7 @@
         <v>16539.5</v>
       </c>
       <c r="AH273">
-        <v>12882.725</v>
+        <v>13340.150000000001</v>
       </c>
     </row>
     <row r="274" spans="1:34" x14ac:dyDescent="0.3">
@@ -23344,7 +23374,7 @@
         <v>2.3451152542655063E-3</v>
       </c>
       <c r="AB274" s="3">
-        <v>5.4737087890671379E-3</v>
+        <v>5.5148049637667989E-3</v>
       </c>
       <c r="AC274" s="3">
         <v>4.6125026915456628E-3</v>
@@ -23353,7 +23383,7 @@
         <v>4.6015965326199849E-3</v>
       </c>
       <c r="AF274">
-        <v>8688.1</v>
+        <v>8605</v>
       </c>
       <c r="AG274">
         <v>16539.5</v>
@@ -23439,7 +23469,7 @@
         <v>4.0251223624924171E-3</v>
       </c>
       <c r="AB275" s="3">
-        <v>5.4667506863063349E-3</v>
+        <v>5.4562863532886087E-3</v>
       </c>
       <c r="AC275" s="3">
         <v>4.6790992909259898E-3</v>
@@ -23448,7 +23478,7 @@
         <v>4.6043700909960458E-3</v>
       </c>
       <c r="AF275">
-        <v>8605</v>
+        <v>8384.2999999999993</v>
       </c>
       <c r="AG275">
         <v>16539.5</v>
@@ -23534,7 +23564,7 @@
         <v>3.6292156806669862E-3</v>
       </c>
       <c r="AB276" s="3">
-        <v>5.397348589655653E-3</v>
+        <v>5.3038214350364784E-3</v>
       </c>
       <c r="AC276" s="3">
         <v>4.7294758856559404E-3</v>
@@ -23543,10 +23573,10 @@
         <v>4.5943852557129503E-3</v>
       </c>
       <c r="AF276">
-        <v>8384.2999999999993</v>
+        <v>7669.8</v>
       </c>
       <c r="AG276">
-        <v>16539.5</v>
+        <v>15819.25</v>
       </c>
       <c r="AH276">
         <v>13340.150000000001</v>
@@ -23629,7 +23659,7 @@
         <v>3.474081673219942E-3</v>
       </c>
       <c r="AB277" s="3">
-        <v>5.2447975717520743E-3</v>
+        <v>4.9875392213483433E-3</v>
       </c>
       <c r="AC277" s="3">
         <v>4.7578353371450681E-3</v>
@@ -23638,13 +23668,13 @@
         <v>4.5997249702182975E-3</v>
       </c>
       <c r="AF277">
-        <v>7669.8</v>
+        <v>8384.2999999999993</v>
       </c>
       <c r="AG277">
         <v>15819.25</v>
       </c>
       <c r="AH277">
-        <v>13340.150000000001</v>
+        <v>13701.3</v>
       </c>
     </row>
     <row r="278" spans="1:34" x14ac:dyDescent="0.3">
@@ -23724,7 +23754,7 @@
         <v>4.1054817364405416E-4</v>
       </c>
       <c r="AB278" s="3">
-        <v>4.8398943488417532E-3</v>
+        <v>4.5853260908621961E-3</v>
       </c>
       <c r="AC278" s="3">
         <v>4.6954391677741904E-3</v>
@@ -23733,7 +23763,7 @@
         <v>4.504615748813421E-3</v>
       </c>
       <c r="AF278">
-        <v>8384.2999999999993</v>
+        <v>7669.8</v>
       </c>
       <c r="AG278">
         <v>15819.25</v>
@@ -23819,7 +23849,7 @@
         <v>8.8411734993409929E-4</v>
       </c>
       <c r="AB279" s="3">
-        <v>4.4659322605096769E-3</v>
+        <v>4.3430214223399615E-3</v>
       </c>
       <c r="AC279" s="3">
         <v>4.6116853217686238E-3</v>
@@ -23834,7 +23864,7 @@
         <v>15819.25</v>
       </c>
       <c r="AH279">
-        <v>13701.3</v>
+        <v>13799.6</v>
       </c>
     </row>
     <row r="280" spans="1:34" x14ac:dyDescent="0.3">
@@ -23914,7 +23944,7 @@
         <v>2.5233465397000998E-4</v>
       </c>
       <c r="AB280" s="3">
-        <v>4.2110637846506085E-3</v>
+        <v>4.0406727299562521E-3</v>
       </c>
       <c r="AC280" s="3">
         <v>4.566126188746006E-3</v>
@@ -23923,13 +23953,13 @@
         <v>4.4677770685527581E-3</v>
       </c>
       <c r="AF280">
-        <v>7669.8</v>
+        <v>7066.5</v>
       </c>
       <c r="AG280">
         <v>15819.25</v>
       </c>
       <c r="AH280">
-        <v>13799.6</v>
+        <v>13701.3</v>
       </c>
     </row>
     <row r="281" spans="1:34" x14ac:dyDescent="0.3">
@@ -24009,7 +24039,7 @@
         <v>2.5333469675179465E-3</v>
       </c>
       <c r="AB281" s="3">
-        <v>3.9920493182646934E-3</v>
+        <v>3.8362748931941729E-3</v>
       </c>
       <c r="AC281" s="3">
         <v>4.5560014937297095E-3</v>
@@ -24024,7 +24054,7 @@
         <v>15819.25</v>
       </c>
       <c r="AH281">
-        <v>13701.3</v>
+        <v>13799.6</v>
       </c>
     </row>
     <row r="282" spans="1:34" x14ac:dyDescent="0.3">
@@ -24104,7 +24134,7 @@
         <v>7.4259150914768313E-4</v>
       </c>
       <c r="AB282" s="3">
-        <v>3.7364786549991249E-3</v>
+        <v>3.6913165567191487E-3</v>
       </c>
       <c r="AC282" s="3">
         <v>4.5450153604586581E-3</v>
@@ -24113,10 +24143,10 @@
         <v>4.4696476416920634E-3</v>
       </c>
       <c r="AF282">
-        <v>7066.5</v>
+        <v>7045.3</v>
       </c>
       <c r="AG282">
-        <v>15819.25</v>
+        <v>15205.65</v>
       </c>
       <c r="AH282">
         <v>13799.6</v>
@@ -24199,7 +24229,7 @@
         <v>9.617904086468565E-4</v>
       </c>
       <c r="AB283" s="3">
-        <v>3.6032673261361713E-3</v>
+        <v>3.3707254498453244E-3</v>
       </c>
       <c r="AC283" s="3">
         <v>4.5089047048521274E-3</v>
@@ -24211,10 +24241,10 @@
         <v>7045.3</v>
       </c>
       <c r="AG283">
-        <v>15205.65</v>
+        <v>15819.25</v>
       </c>
       <c r="AH283">
-        <v>13799.6</v>
+        <v>14013.900000000001</v>
       </c>
     </row>
     <row r="284" spans="1:34" x14ac:dyDescent="0.3">
@@ -24294,7 +24324,7 @@
         <v>3.0276505968268586E-3</v>
       </c>
       <c r="AB284" s="3">
-        <v>3.359658519102793E-3</v>
+        <v>3.3615180740847127E-3</v>
       </c>
       <c r="AC284" s="3">
         <v>4.5193170725684462E-3</v>
@@ -24306,10 +24336,10 @@
         <v>7045.3</v>
       </c>
       <c r="AG284">
-        <v>15819.25</v>
+        <v>15205.65</v>
       </c>
       <c r="AH284">
-        <v>14013.900000000001</v>
+        <v>14321.875</v>
       </c>
     </row>
     <row r="285" spans="1:34" x14ac:dyDescent="0.3">
@@ -24389,7 +24419,7 @@
         <v>4.2220195231182922E-3</v>
       </c>
       <c r="AB285" s="3">
-        <v>3.3892761853438606E-3</v>
+        <v>3.4488742837086544E-3</v>
       </c>
       <c r="AC285" s="3">
         <v>4.5420293466533869E-3</v>
@@ -24398,13 +24428,13 @@
         <v>4.3631468606001251E-3</v>
       </c>
       <c r="AF285">
-        <v>7045.3</v>
+        <v>7045.8</v>
       </c>
       <c r="AG285">
-        <v>15205.65</v>
+        <v>14831.3</v>
       </c>
       <c r="AH285">
-        <v>14321.875</v>
+        <v>14013.900000000001</v>
       </c>
     </row>
     <row r="286" spans="1:34" x14ac:dyDescent="0.3">
@@ -24484,7 +24514,7 @@
         <v>2.4318096432507375E-3</v>
       </c>
       <c r="AB286" s="3">
-        <v>3.4160657469196895E-3</v>
+        <v>3.4511647939862648E-3</v>
       </c>
       <c r="AC286" s="3">
         <v>4.5289530733850407E-3</v>
@@ -24493,10 +24523,10 @@
         <v>4.3318257296920968E-3</v>
       </c>
       <c r="AF286">
-        <v>7045.8</v>
+        <v>7445.3</v>
       </c>
       <c r="AG286">
-        <v>14831.3</v>
+        <v>13300.599999999999</v>
       </c>
       <c r="AH286">
         <v>14013.900000000001</v>
@@ -24579,7 +24609,7 @@
         <v>7.5797966629561619E-3</v>
       </c>
       <c r="AB287" s="3">
-        <v>3.584346467178842E-3</v>
+        <v>3.4233937633965763E-3</v>
       </c>
       <c r="AC287" s="3">
         <v>4.5676613932055339E-3</v>
@@ -24588,10 +24618,10 @@
         <v>4.3011381517608759E-3</v>
       </c>
       <c r="AF287">
-        <v>7445.3</v>
+        <v>6954.375</v>
       </c>
       <c r="AG287">
-        <v>13300.599999999999</v>
+        <v>11860.349999999999</v>
       </c>
       <c r="AH287">
         <v>14013.900000000001</v>
@@ -24674,7 +24704,7 @@
         <v>8.8703068617557168E-3</v>
       </c>
       <c r="AB288" s="3">
-        <v>3.5991006375371937E-3</v>
+        <v>3.5887118005927996E-3</v>
       </c>
       <c r="AC288" s="3">
         <v>4.6127123849266519E-3</v>
@@ -24683,13 +24713,13 @@
         <v>4.3177289832038177E-3</v>
       </c>
       <c r="AF288">
-        <v>6954.375</v>
+        <v>7445.3</v>
       </c>
       <c r="AG288">
         <v>11860.349999999999</v>
       </c>
       <c r="AH288">
-        <v>14013.900000000001</v>
+        <v>14321.875</v>
       </c>
     </row>
     <row r="289" spans="1:34" x14ac:dyDescent="0.3">
@@ -24769,7 +24799,7 @@
         <v>1.139453781403077E-2</v>
       </c>
       <c r="AB289" s="3">
-        <v>3.8405126397359599E-3</v>
+        <v>3.8320099703224439E-3</v>
       </c>
       <c r="AC289" s="3">
         <v>4.6752211670329303E-3</v>
@@ -24864,7 +24894,7 @@
         <v>4.6328989702377754E-3</v>
       </c>
       <c r="AB290" s="3">
-        <v>3.8578450993519706E-3</v>
+        <v>3.9719582785132396E-3</v>
       </c>
       <c r="AC290" s="3">
         <v>4.6837201909553962E-3</v>
@@ -24873,10 +24903,10 @@
         <v>4.3812275752133532E-3</v>
       </c>
       <c r="AF290">
-        <v>7445.3</v>
+        <v>8069.3</v>
       </c>
       <c r="AG290">
-        <v>11860.349999999999</v>
+        <v>11117.65</v>
       </c>
       <c r="AH290">
         <v>14321.875</v>
@@ -24959,7 +24989,7 @@
         <v>7.3983775938516461E-3</v>
       </c>
       <c r="AB291" s="3">
-        <v>4.082487933846737E-3</v>
+        <v>3.9010089336335356E-3</v>
       </c>
       <c r="AC291" s="3">
         <v>4.7187483208844475E-3</v>
@@ -24971,10 +25001,10 @@
         <v>8069.3</v>
       </c>
       <c r="AG291">
-        <v>11117.65</v>
+        <v>9750.8499999999985</v>
       </c>
       <c r="AH291">
-        <v>14321.875</v>
+        <v>14013.900000000001</v>
       </c>
     </row>
     <row r="292" spans="1:34" x14ac:dyDescent="0.3">
@@ -25054,7 +25084,7 @@
         <v>1.3140159190128342E-2</v>
       </c>
       <c r="AB292" s="3">
-        <v>4.1990460386817554E-3</v>
+        <v>3.9600427072670422E-3</v>
       </c>
       <c r="AC292" s="3">
         <v>4.9331002849763109E-3</v>
@@ -25063,7 +25093,7 @@
         <v>4.4205111759050199E-3</v>
       </c>
       <c r="AF292">
-        <v>8069.3</v>
+        <v>8524.2999999999993</v>
       </c>
       <c r="AG292">
         <v>9750.8499999999985</v>
@@ -25149,7 +25179,7 @@
         <v>5.1895707201142782E-3</v>
       </c>
       <c r="AB293" s="3">
-        <v>3.9997049012298561E-3</v>
+        <v>3.8447569435837675E-3</v>
       </c>
       <c r="AC293" s="3">
         <v>4.9651153873501606E-3</v>
@@ -25158,10 +25188,10 @@
         <v>4.4427623717123652E-3</v>
       </c>
       <c r="AF293">
-        <v>8524.2999999999993</v>
+        <v>8510.5499999999993</v>
       </c>
       <c r="AG293">
-        <v>9750.8499999999985</v>
+        <v>9177.9</v>
       </c>
       <c r="AH293">
         <v>14013.900000000001</v>
@@ -25244,7 +25274,7 @@
         <v>8.4007745265071154E-3</v>
       </c>
       <c r="AB294" s="3">
-        <v>3.9917252527103273E-3</v>
+        <v>3.9359502025905846E-3</v>
       </c>
       <c r="AC294" s="3">
         <v>5.0787388300344537E-3</v>
@@ -25339,7 +25369,7 @@
         <v>6.5738053952590914E-4</v>
       </c>
       <c r="AB295" s="3">
-        <v>3.8301898908788207E-3</v>
+        <v>3.7968542931108257E-3</v>
       </c>
       <c r="AC295" s="3">
         <v>5.0653109714460555E-3</v>
@@ -25354,7 +25384,7 @@
         <v>9177.9</v>
       </c>
       <c r="AH295">
-        <v>14013.900000000001</v>
+        <v>14321.875</v>
       </c>
     </row>
     <row r="296" spans="1:34" x14ac:dyDescent="0.3">
@@ -25434,7 +25464,7 @@
         <v>4.0177273718373652E-3</v>
       </c>
       <c r="AB296" s="3">
-        <v>3.8039792311342626E-3</v>
+        <v>3.9032901774999629E-3</v>
       </c>
       <c r="AC296" s="3">
         <v>5.0684199500612504E-3</v>
@@ -25446,7 +25476,7 @@
         <v>8510.5499999999993</v>
       </c>
       <c r="AG296">
-        <v>9177.9</v>
+        <v>8937.5</v>
       </c>
       <c r="AH296">
         <v>14321.875</v>
@@ -25529,7 +25559,7 @@
         <v>9.7086691961694171E-3</v>
       </c>
       <c r="AB297" s="3">
-        <v>4.0905604684247842E-3</v>
+        <v>4.219058694758763E-3</v>
       </c>
       <c r="AC297" s="3">
         <v>5.1740107253094286E-3</v>
@@ -25541,7 +25571,7 @@
         <v>8510.5499999999993</v>
       </c>
       <c r="AG297">
-        <v>8937.5</v>
+        <v>8762.25</v>
       </c>
       <c r="AH297">
         <v>14321.875</v>
@@ -25624,7 +25654,7 @@
         <v>1.9935717167604006E-3</v>
       </c>
       <c r="AB298" s="3">
-        <v>4.1472687922426872E-3</v>
+        <v>4.2303403139407466E-3</v>
       </c>
       <c r="AC298" s="3">
         <v>5.1043088397632937E-3</v>
@@ -25719,7 +25749,7 @@
         <v>1.566405794849457E-4</v>
       </c>
       <c r="AB299" s="3">
-        <v>4.098930645087334E-3</v>
+        <v>4.1856312044080135E-3</v>
       </c>
       <c r="AC299" s="3">
         <v>4.9146967791954725E-3</v>
@@ -25728,7 +25758,7 @@
         <v>4.407464832995589E-3</v>
       </c>
       <c r="AF299">
-        <v>8510.5499999999993</v>
+        <v>8762.25</v>
       </c>
       <c r="AG299">
         <v>8762.25</v>
@@ -25814,7 +25844,7 @@
         <v>4.6983634135880914E-3</v>
       </c>
       <c r="AB300" s="3">
-        <v>4.2021709530912421E-3</v>
+        <v>4.1588469005553984E-3</v>
       </c>
       <c r="AC300" s="3">
         <v>4.9259790562321843E-3</v>
@@ -25823,13 +25853,13 @@
         <v>4.4284303586206207E-3</v>
       </c>
       <c r="AF300">
-        <v>8762.25</v>
+        <v>9510.4500000000007</v>
       </c>
       <c r="AG300">
         <v>8762.25</v>
       </c>
       <c r="AH300">
-        <v>14321.875</v>
+        <v>14550.474999999999</v>
       </c>
     </row>
     <row r="301" spans="1:34" x14ac:dyDescent="0.3">
@@ -25909,7 +25939,7 @@
         <v>3.680200644742504E-3</v>
       </c>
       <c r="AB301" s="3">
-        <v>4.1434066987549823E-3</v>
+        <v>4.1883043070702081E-3</v>
       </c>
       <c r="AC301" s="3">
         <v>4.8930778372452558E-3</v>
@@ -25918,10 +25948,10 @@
         <v>4.4353907571351965E-3</v>
       </c>
       <c r="AF301">
-        <v>9510.4500000000007</v>
+        <v>10383.200000000001</v>
       </c>
       <c r="AG301">
-        <v>8762.25</v>
+        <v>8937.5</v>
       </c>
       <c r="AH301">
         <v>14550.474999999999</v>
@@ -26004,7 +26034,7 @@
         <v>1.4114873917071558E-3</v>
       </c>
       <c r="AB302" s="3">
-        <v>4.0987295678649484E-3</v>
+        <v>4.1182221897216762E-3</v>
       </c>
       <c r="AC302" s="3">
         <v>4.8990905389012908E-3</v>
@@ -26016,7 +26046,7 @@
         <v>10383.200000000001</v>
       </c>
       <c r="AG302">
-        <v>8937.5</v>
+        <v>8762.25</v>
       </c>
       <c r="AH302">
         <v>14550.474999999999</v>
@@ -26099,7 +26129,7 @@
         <v>8.387146519228672E-4</v>
       </c>
       <c r="AB303" s="3">
-        <v>4.0124316239862311E-3</v>
+        <v>4.0902973880673947E-3</v>
       </c>
       <c r="AC303" s="3">
         <v>4.8341463141472934E-3</v>
@@ -26114,7 +26144,7 @@
         <v>8762.25</v>
       </c>
       <c r="AH303">
-        <v>14550.474999999999</v>
+        <v>14806.474999999999</v>
       </c>
     </row>
     <row r="304" spans="1:34" x14ac:dyDescent="0.3">
@@ -26194,7 +26224,7 @@
         <v>4.9461524939854451E-3</v>
       </c>
       <c r="AB304" s="3">
-        <v>4.1179056172905579E-3</v>
+        <v>4.1769986293913926E-3</v>
       </c>
       <c r="AC304" s="3">
         <v>4.8459017965790958E-3</v>
@@ -26203,10 +26233,10 @@
         <v>4.4001923652234242E-3</v>
       </c>
       <c r="AF304">
-        <v>10383.200000000001</v>
+        <v>10530.2</v>
       </c>
       <c r="AG304">
-        <v>8762.25</v>
+        <v>8923</v>
       </c>
       <c r="AH304">
         <v>14806.474999999999</v>
@@ -26289,7 +26319,7 @@
         <v>3.2919623246226992E-3</v>
       </c>
       <c r="AB305" s="3">
-        <v>4.1484490711730477E-3</v>
+        <v>4.152559961462402E-3</v>
       </c>
       <c r="AC305" s="3">
         <v>4.8044231573755054E-3</v>
@@ -26301,10 +26331,10 @@
         <v>10530.2</v>
       </c>
       <c r="AG305">
-        <v>8923</v>
+        <v>8762.25</v>
       </c>
       <c r="AH305">
-        <v>14806.474999999999</v>
+        <v>14550.474999999999</v>
       </c>
     </row>
     <row r="306" spans="1:34" x14ac:dyDescent="0.3">
@@ -26384,7 +26414,7 @@
         <v>5.4775908509612226E-3</v>
       </c>
       <c r="AB306" s="3">
-        <v>4.195302893381719E-3</v>
+        <v>4.2141724671388766E-3</v>
       </c>
       <c r="AC306" s="3">
         <v>4.7589969510876779E-3</v>
@@ -26393,7 +26423,7 @@
         <v>4.4259185822734387E-3</v>
       </c>
       <c r="AF306">
-        <v>10530.2</v>
+        <v>10746.8</v>
       </c>
       <c r="AG306">
         <v>8762.25</v>
@@ -26479,7 +26509,7 @@
         <v>6.1824922746311906E-4</v>
       </c>
       <c r="AB307" s="3">
-        <v>4.098174943278369E-3</v>
+        <v>4.1189780522803161E-3</v>
       </c>
       <c r="AC307" s="3">
         <v>4.5532586368143297E-3</v>
@@ -26488,13 +26518,13 @@
         <v>4.4247903513708799E-3</v>
       </c>
       <c r="AF307">
-        <v>10746.8</v>
+        <v>9286.6</v>
       </c>
       <c r="AG307">
         <v>8762.25</v>
       </c>
       <c r="AH307">
-        <v>14550.474999999999</v>
+        <v>14321.875</v>
       </c>
     </row>
     <row r="308" spans="1:34" x14ac:dyDescent="0.3">
@@ -26574,7 +26604,7 @@
         <v>1.4106624693681624E-3</v>
       </c>
       <c r="AB308" s="3">
-        <v>4.0316130334766987E-3</v>
+        <v>4.1523151954711195E-3</v>
       </c>
       <c r="AC308" s="3">
         <v>4.3688206431666578E-3</v>
@@ -26586,7 +26616,7 @@
         <v>9286.6</v>
       </c>
       <c r="AG308">
-        <v>8762.25</v>
+        <v>8731.25</v>
       </c>
       <c r="AH308">
         <v>14321.875</v>
@@ -26669,7 +26699,7 @@
         <v>3.1676981353281342E-3</v>
       </c>
       <c r="AB309" s="3">
-        <v>4.1205533548213458E-3</v>
+        <v>4.2284345549842544E-3</v>
       </c>
       <c r="AC309" s="3">
         <v>4.2857279886621084E-3</v>
@@ -26678,10 +26708,10 @@
         <v>4.4198831704141588E-3</v>
       </c>
       <c r="AF309">
-        <v>9286.6</v>
+        <v>8923</v>
       </c>
       <c r="AG309">
-        <v>8731.25</v>
+        <v>8622.25</v>
       </c>
       <c r="AH309">
         <v>14321.875</v>
@@ -26764,7 +26794,7 @@
         <v>3.4267473768598844E-3</v>
       </c>
       <c r="AB310" s="3">
-        <v>4.202573678270565E-3</v>
+        <v>4.3342483124139165E-3</v>
       </c>
       <c r="AC310" s="3">
         <v>4.1874605211850843E-3</v>
@@ -26773,13 +26803,13 @@
         <v>4.4270894021327918E-3</v>
       </c>
       <c r="AF310">
-        <v>8923</v>
+        <v>9286.6</v>
       </c>
       <c r="AG310">
-        <v>8622.25</v>
+        <v>8762.25</v>
       </c>
       <c r="AH310">
-        <v>14321.875</v>
+        <v>14550.474999999999</v>
       </c>
     </row>
     <row r="311" spans="1:34" x14ac:dyDescent="0.3">
@@ -26859,7 +26889,7 @@
         <v>2.8084271828129337E-3</v>
       </c>
       <c r="AB311" s="3">
-        <v>4.2850282759751756E-3</v>
+        <v>4.3434176529237494E-3</v>
       </c>
       <c r="AC311" s="3">
         <v>4.0898462730589611E-3</v>
@@ -26954,7 +26984,7 @@
         <v>1.0441372600724641E-3</v>
       </c>
       <c r="AB312" s="3">
-        <v>4.2369892531543534E-3</v>
+        <v>4.353469177954576E-3</v>
       </c>
       <c r="AC312" s="3">
         <v>4.0223928673368626E-3</v>
@@ -26963,13 +26993,13 @@
         <v>4.414078096307731E-3</v>
       </c>
       <c r="AF312">
-        <v>9286.6</v>
+        <v>9858.9750000000004</v>
       </c>
       <c r="AG312">
         <v>8762.25</v>
       </c>
       <c r="AH312">
-        <v>14550.474999999999</v>
+        <v>14806.474999999999</v>
       </c>
     </row>
     <row r="313" spans="1:34" x14ac:dyDescent="0.3">
@@ -27049,7 +27079,7 @@
         <v>8.3084034424407704E-4</v>
       </c>
       <c r="AB313" s="3">
-        <v>4.2398359897703663E-3</v>
+        <v>4.3491041758078166E-3</v>
       </c>
       <c r="AC313" s="3">
         <v>3.8599148128265703E-3</v>
@@ -27144,7 +27174,7 @@
         <v>4.2435124902775456E-3</v>
       </c>
       <c r="AB314" s="3">
-        <v>4.3456979924036141E-3</v>
+        <v>4.3896329055895062E-3</v>
       </c>
       <c r="AC314" s="3">
         <v>3.8755754898371093E-3</v>
@@ -27153,7 +27183,7 @@
         <v>4.4356846285938719E-3</v>
       </c>
       <c r="AF314">
-        <v>9858.9750000000004</v>
+        <v>9562.39</v>
       </c>
       <c r="AG314">
         <v>8762.25</v>
@@ -27239,7 +27269,7 @@
         <v>3.1146542503721619E-3</v>
       </c>
       <c r="AB315" s="3">
-        <v>4.3485045618728178E-3</v>
+        <v>4.3527207298313013E-3</v>
       </c>
       <c r="AC315" s="3">
         <v>3.9007975067699781E-3</v>
@@ -27251,7 +27281,7 @@
         <v>9562.39</v>
       </c>
       <c r="AG315">
-        <v>8762.25</v>
+        <v>8923</v>
       </c>
       <c r="AH315">
         <v>14806.474999999999</v>
@@ -27334,7 +27364,7 @@
         <v>2.8201740118767304E-3</v>
       </c>
       <c r="AB316" s="3">
-        <v>4.3032837389295414E-3</v>
+        <v>4.3656662087855017E-3</v>
       </c>
       <c r="AC316" s="3">
         <v>3.9084155013858835E-3</v>
@@ -27343,10 +27373,10 @@
         <v>4.4066205415318567E-3</v>
       </c>
       <c r="AF316">
-        <v>9562.39</v>
+        <v>9918.1650000000009</v>
       </c>
       <c r="AG316">
-        <v>8923</v>
+        <v>9286.6</v>
       </c>
       <c r="AH316">
         <v>14806.474999999999</v>
@@ -27429,7 +27459,7 @@
         <v>4.6943790144706732E-3</v>
       </c>
       <c r="AB317" s="3">
-        <v>4.3762698476785718E-3</v>
+        <v>4.2694856205026518E-3</v>
       </c>
       <c r="AC317" s="3">
         <v>3.846439691949614E-3</v>
@@ -27438,13 +27468,13 @@
         <v>4.3914584660437921E-3</v>
       </c>
       <c r="AF317">
-        <v>9918.1650000000009</v>
+        <v>10369.674999999999</v>
       </c>
       <c r="AG317">
         <v>9286.6</v>
       </c>
       <c r="AH317">
-        <v>14806.474999999999</v>
+        <v>15026.974999999999</v>
       </c>
     </row>
     <row r="318" spans="1:34" x14ac:dyDescent="0.3">
@@ -27524,7 +27554,7 @@
         <v>6.6287667387006088E-3</v>
       </c>
       <c r="AB318" s="3">
-        <v>4.3455914630251662E-3</v>
+        <v>4.1947676164008152E-3</v>
       </c>
       <c r="AC318" s="3">
         <v>3.8917397084968072E-3</v>
@@ -27536,7 +27566,7 @@
         <v>10369.674999999999</v>
       </c>
       <c r="AG318">
-        <v>9286.6</v>
+        <v>9562.39</v>
       </c>
       <c r="AH318">
         <v>15026.974999999999</v>
@@ -27619,7 +27649,7 @@
         <v>2.4713730979883941E-3</v>
       </c>
       <c r="AB319" s="3">
-        <v>4.1391742448391236E-3</v>
+        <v>3.8973287925327354E-3</v>
       </c>
       <c r="AC319" s="3">
         <v>3.8646693814275899E-3</v>
@@ -27634,7 +27664,7 @@
         <v>9562.39</v>
       </c>
       <c r="AH319">
-        <v>15026.974999999999</v>
+        <v>15205.65</v>
       </c>
     </row>
     <row r="320" spans="1:34" x14ac:dyDescent="0.3">
@@ -27714,7 +27744,7 @@
         <v>1.8202540775391629E-3</v>
       </c>
       <c r="AB320" s="3">
-        <v>3.8303263823716528E-3</v>
+        <v>3.8035739627761151E-3</v>
       </c>
       <c r="AC320" s="3">
         <v>3.8877661206446774E-3</v>
@@ -27723,13 +27753,13 @@
         <v>4.4355424585292985E-3</v>
       </c>
       <c r="AF320">
-        <v>10369.674999999999</v>
+        <v>10581.865</v>
       </c>
       <c r="AG320">
-        <v>9562.39</v>
+        <v>9918.1650000000009</v>
       </c>
       <c r="AH320">
-        <v>15205.65</v>
+        <v>15370.55</v>
       </c>
     </row>
     <row r="321" spans="1:34" x14ac:dyDescent="0.3">
@@ -27809,7 +27839,7 @@
         <v>1.2377342386469259E-3</v>
       </c>
       <c r="AB321" s="3">
-        <v>3.7208049394171091E-3</v>
+        <v>3.5982191842692914E-3</v>
       </c>
       <c r="AC321" s="3">
         <v>3.7496140589514133E-3</v>
@@ -27818,13 +27848,13 @@
         <v>4.4182750371925383E-3</v>
       </c>
       <c r="AF321">
-        <v>10581.865</v>
+        <v>11224.14</v>
       </c>
       <c r="AG321">
-        <v>9918.1650000000009</v>
+        <v>10229.825000000001</v>
       </c>
       <c r="AH321">
-        <v>15370.55</v>
+        <v>15799.95</v>
       </c>
     </row>
     <row r="322" spans="1:34" x14ac:dyDescent="0.3">
@@ -27904,7 +27934,7 @@
         <v>3.5317360401873055E-3</v>
       </c>
       <c r="AB322" s="3">
-        <v>3.5960745667182594E-3</v>
+        <v>3.27793841260459E-3</v>
       </c>
       <c r="AC322" s="3">
         <v>3.6189905599358159E-3</v>
@@ -27913,7 +27943,7 @@
         <v>4.4347975202651772E-3</v>
       </c>
       <c r="AF322">
-        <v>11224.14</v>
+        <v>10581.865</v>
       </c>
       <c r="AG322">
         <v>10229.825000000001</v>
@@ -27999,7 +28029,7 @@
         <v>4.7380893348192288E-4</v>
       </c>
       <c r="AB323" s="3">
-        <v>3.1874826229554717E-3</v>
+        <v>3.1207463530501783E-3</v>
       </c>
       <c r="AC323" s="3">
         <v>3.4827516483169731E-3</v>
@@ -28008,13 +28038,13 @@
         <v>4.3850466102320724E-3</v>
       </c>
       <c r="AF323">
-        <v>10581.865</v>
+        <v>11224.14</v>
       </c>
       <c r="AG323">
         <v>10229.825000000001</v>
       </c>
       <c r="AH323">
-        <v>15799.95</v>
+        <v>16223.75</v>
       </c>
     </row>
     <row r="324" spans="1:34" x14ac:dyDescent="0.3">
@@ -28094,7 +28124,7 @@
         <v>4.9000998711237198E-3</v>
       </c>
       <c r="AB324" s="3">
-        <v>3.1781448536331957E-3</v>
+        <v>3.0040571978707316E-3</v>
       </c>
       <c r="AC324" s="3">
         <v>3.4700037002306579E-3</v>
@@ -28109,7 +28139,7 @@
         <v>10229.825000000001</v>
       </c>
       <c r="AH324">
-        <v>16223.75</v>
+        <v>15805.400000000001</v>
       </c>
     </row>
     <row r="325" spans="1:34" x14ac:dyDescent="0.3">
@@ -28189,7 +28219,7 @@
         <v>9.9755083701369429E-4</v>
       </c>
       <c r="AB325" s="3">
-        <v>2.9393311862301822E-3</v>
+        <v>3.0153962077869912E-3</v>
       </c>
       <c r="AC325" s="3">
         <v>3.4061252504489084E-3</v>
@@ -28284,7 +28314,7 @@
         <v>2.0541590677249921E-3</v>
       </c>
       <c r="AB326" s="3">
-        <v>2.984388558107572E-3</v>
+        <v>2.9499439309832454E-3</v>
       </c>
       <c r="AC326" s="3">
         <v>3.4266170542416041E-3</v>
@@ -28379,7 +28409,7 @@
         <v>1.7280304132198943E-3</v>
       </c>
       <c r="AB327" s="3">
-        <v>2.9105273658941049E-3</v>
+        <v>2.6839226382182613E-3</v>
       </c>
       <c r="AC327" s="3">
         <v>3.4514906664885121E-3</v>
@@ -28394,7 +28424,7 @@
         <v>10229.825000000001</v>
       </c>
       <c r="AH327">
-        <v>15805.400000000001</v>
+        <v>15370.55</v>
       </c>
     </row>
     <row r="328" spans="1:34" x14ac:dyDescent="0.3">
@@ -28474,7 +28504,7 @@
         <v>3.5908568136545638E-3</v>
       </c>
       <c r="AB328" s="3">
-        <v>2.7131785793613676E-3</v>
+        <v>2.7371654747814001E-3</v>
       </c>
       <c r="AC328" s="3">
         <v>3.4837528943610732E-3</v>
@@ -28489,7 +28519,7 @@
         <v>10229.825000000001</v>
       </c>
       <c r="AH328">
-        <v>15370.55</v>
+        <v>15205.65</v>
       </c>
     </row>
     <row r="329" spans="1:34" x14ac:dyDescent="0.3">
@@ -28569,7 +28599,7 @@
         <v>1.5149948220313236E-3</v>
       </c>
       <c r="AB329" s="3">
-        <v>2.6977406150152684E-3</v>
+        <v>2.7824439495329461E-3</v>
       </c>
       <c r="AC329" s="3">
         <v>3.4840375769704798E-3</v>
@@ -28581,10 +28611,10 @@
         <v>11224.14</v>
       </c>
       <c r="AG329">
-        <v>10229.825000000001</v>
+        <v>10384.75</v>
       </c>
       <c r="AH329">
-        <v>15205.65</v>
+        <v>15370.55</v>
       </c>
     </row>
     <row r="330" spans="1:34" x14ac:dyDescent="0.3">
@@ -28664,7 +28694,7 @@
         <v>5.0966229835798238E-3</v>
       </c>
       <c r="AB330" s="3">
-        <v>2.8570948861151033E-3</v>
+        <v>2.7957192685326704E-3</v>
       </c>
       <c r="AC330" s="3">
         <v>3.4772830845440344E-3</v>
@@ -28673,7 +28703,7 @@
         <v>4.2825410541806191E-3</v>
       </c>
       <c r="AF330">
-        <v>11224.14</v>
+        <v>10581.865</v>
       </c>
       <c r="AG330">
         <v>10384.75</v>
@@ -28759,7 +28789,7 @@
         <v>9.0111177487361971E-4</v>
       </c>
       <c r="AB331" s="3">
-        <v>2.7346028977694751E-3</v>
+        <v>2.7030829728703744E-3</v>
       </c>
       <c r="AC331" s="3">
         <v>3.4456936399702913E-3</v>
@@ -28771,10 +28801,10 @@
         <v>10581.865</v>
       </c>
       <c r="AG331">
-        <v>10384.75</v>
+        <v>10581.865</v>
       </c>
       <c r="AH331">
-        <v>15370.55</v>
+        <v>15805.400000000001</v>
       </c>
     </row>
     <row r="332" spans="1:34" x14ac:dyDescent="0.3">
@@ -28854,7 +28884,7 @@
         <v>1.8541733072005018E-3</v>
       </c>
       <c r="AB332" s="3">
-        <v>2.67569879010683E-3</v>
+        <v>2.7178391700534857E-3</v>
       </c>
       <c r="AC332" s="3">
         <v>3.418030679887581E-3</v>
@@ -28863,13 +28893,13 @@
         <v>4.2418866666079072E-3</v>
       </c>
       <c r="AF332">
-        <v>10581.865</v>
+        <v>11224.14</v>
       </c>
       <c r="AG332">
-        <v>10581.865</v>
+        <v>11224.14</v>
       </c>
       <c r="AH332">
-        <v>15805.400000000001</v>
+        <v>16021.7</v>
       </c>
     </row>
     <row r="333" spans="1:34" x14ac:dyDescent="0.3">
@@ -28949,7 +28979,7 @@
         <v>3.1408968883694932E-4</v>
       </c>
       <c r="AB333" s="3">
-        <v>2.640298864207791E-3</v>
+        <v>2.7003516712839552E-3</v>
       </c>
       <c r="AC333" s="3">
         <v>3.3953245296756752E-3</v>
@@ -28958,13 +28988,13 @@
         <v>4.226411865269065E-3</v>
       </c>
       <c r="AF333">
-        <v>11224.14</v>
+        <v>10634.04</v>
       </c>
       <c r="AG333">
-        <v>11224.14</v>
+        <v>10634.04</v>
       </c>
       <c r="AH333">
-        <v>16021.7</v>
+        <v>15597.900000000001</v>
       </c>
     </row>
     <row r="334" spans="1:34" x14ac:dyDescent="0.3">
@@ -29044,7 +29074,7 @@
         <v>1.0220871839667245E-2</v>
       </c>
       <c r="AB334" s="3">
-        <v>2.9429490960705129E-3</v>
+        <v>2.8761756494733487E-3</v>
       </c>
       <c r="AC334" s="3">
         <v>3.5265871394323709E-3</v>
@@ -29053,13 +29083,13 @@
         <v>4.252177166176617E-3</v>
       </c>
       <c r="AF334">
-        <v>10634.04</v>
+        <v>11224.14</v>
       </c>
       <c r="AG334">
-        <v>10634.04</v>
+        <v>11224.14</v>
       </c>
       <c r="AH334">
-        <v>15597.900000000001</v>
+        <v>15370.55</v>
       </c>
     </row>
     <row r="335" spans="1:34" x14ac:dyDescent="0.3">
@@ -29139,7 +29169,7 @@
         <v>1.0310931219941644E-2</v>
       </c>
       <c r="AB335" s="3">
-        <v>3.1160064743271645E-3</v>
+        <v>3.1101412793173135E-3</v>
       </c>
       <c r="AC335" s="3">
         <v>3.6313506203898577E-3</v>
@@ -29148,10 +29178,10 @@
         <v>4.3021570951269324E-3</v>
       </c>
       <c r="AF335">
-        <v>11224.14</v>
+        <v>12257.775</v>
       </c>
       <c r="AG335">
-        <v>11224.14</v>
+        <v>11899.775</v>
       </c>
       <c r="AH335">
         <v>15370.55</v>
@@ -29234,7 +29264,7 @@
         <v>4.1017435590255946E-3</v>
       </c>
       <c r="AB336" s="3">
-        <v>3.1421284496304836E-3</v>
+        <v>3.0642797029194592E-3</v>
       </c>
       <c r="AC336" s="3">
         <v>3.6392260850291679E-3</v>
@@ -29249,7 +29279,7 @@
         <v>11899.775</v>
       </c>
       <c r="AH336">
-        <v>15370.55</v>
+        <v>15319.65</v>
       </c>
     </row>
     <row r="337" spans="1:34" x14ac:dyDescent="0.3">
@@ -29329,7 +29359,7 @@
         <v>3.657767022388736E-3</v>
       </c>
       <c r="AB337" s="3">
-        <v>3.0834244551604033E-3</v>
+        <v>3.1655969627503128E-3</v>
       </c>
       <c r="AC337" s="3">
         <v>3.6422875075153146E-3</v>
@@ -29341,10 +29371,10 @@
         <v>12257.775</v>
       </c>
       <c r="AG337">
-        <v>11899.775</v>
+        <v>11224.14</v>
       </c>
       <c r="AH337">
-        <v>15319.65</v>
+        <v>15213.34</v>
       </c>
     </row>
     <row r="338" spans="1:34" x14ac:dyDescent="0.3">
@@ -29424,7 +29454,7 @@
         <v>5.0065651655057941E-3</v>
       </c>
       <c r="AB338" s="3">
-        <v>3.2249830338069415E-3</v>
+        <v>3.2854603859549009E-3</v>
       </c>
       <c r="AC338" s="3">
         <v>3.7188877907130104E-3</v>
@@ -29433,10 +29463,10 @@
         <v>4.2973127044256664E-3</v>
       </c>
       <c r="AF338">
-        <v>12257.775</v>
+        <v>13631.424999999999</v>
       </c>
       <c r="AG338">
-        <v>11224.14</v>
+        <v>11899.775</v>
       </c>
       <c r="AH338">
         <v>15213.34</v>
@@ -29519,7 +29549,7 @@
         <v>4.3295634293354368E-3</v>
       </c>
       <c r="AB339" s="3">
-        <v>3.3191411292897567E-3</v>
+        <v>3.3241892290884773E-3</v>
       </c>
       <c r="AC339" s="3">
         <v>3.7763118920363659E-3</v>
@@ -29528,7 +29558,7 @@
         <v>4.3006795222758683E-3</v>
       </c>
       <c r="AF339">
-        <v>13631.424999999999</v>
+        <v>13742.025000000001</v>
       </c>
       <c r="AG339">
         <v>11899.775</v>
@@ -29614,7 +29644,7 @@
         <v>4.5905314869609803E-3</v>
       </c>
       <c r="AB340" s="3">
-        <v>3.3650389793424291E-3</v>
+        <v>3.3629820327585138E-3</v>
       </c>
       <c r="AC340" s="3">
         <v>3.8486151725862154E-3</v>
@@ -29623,7 +29653,7 @@
         <v>4.3184225006470097E-3</v>
       </c>
       <c r="AF340">
-        <v>13742.025000000001</v>
+        <v>12817</v>
       </c>
       <c r="AG340">
         <v>11899.775</v>
@@ -29709,7 +29739,7 @@
         <v>4.2568502043989209E-3</v>
       </c>
       <c r="AB341" s="3">
-        <v>3.3918164899082045E-3</v>
+        <v>3.4112628001447135E-3</v>
       </c>
       <c r="AC341" s="3">
         <v>3.8773402265342314E-3</v>
@@ -29721,7 +29751,7 @@
         <v>12817</v>
       </c>
       <c r="AG341">
-        <v>11899.775</v>
+        <v>11860.42</v>
       </c>
       <c r="AH341">
         <v>15213.34</v>
@@ -29804,7 +29834,7 @@
         <v>6.2656000986163196E-3</v>
       </c>
       <c r="AB342" s="3">
-        <v>3.5033381968696039E-3</v>
+        <v>3.5853115614295087E-3</v>
       </c>
       <c r="AC342" s="3">
         <v>3.9693903696920423E-3</v>
@@ -29816,10 +29846,10 @@
         <v>12817</v>
       </c>
       <c r="AG342">
-        <v>11860.42</v>
+        <v>11951.045</v>
       </c>
       <c r="AH342">
-        <v>15213.34</v>
+        <v>15319.65</v>
       </c>
     </row>
     <row r="343" spans="1:34" x14ac:dyDescent="0.3">
@@ -29899,7 +29929,7 @@
         <v>1.474214129352891E-3</v>
       </c>
       <c r="AB343" s="3">
-        <v>3.5172116442657468E-3</v>
+        <v>3.6067573542664694E-3</v>
       </c>
       <c r="AC343" s="3">
         <v>3.9779307650371432E-3</v>
@@ -29994,7 +30024,7 @@
         <v>6.2724310431530039E-3</v>
       </c>
       <c r="AB344" s="3">
-        <v>3.6927468281015186E-3</v>
+        <v>3.6743879726956513E-3</v>
       </c>
       <c r="AC344" s="3">
         <v>4.0320104391425781E-3</v>
@@ -30006,7 +30036,7 @@
         <v>12817</v>
       </c>
       <c r="AG344">
-        <v>11951.045</v>
+        <v>11860.42</v>
       </c>
       <c r="AH344">
         <v>15319.65</v>
@@ -30089,7 +30119,7 @@
         <v>8.8778920020351482E-3</v>
       </c>
       <c r="AB345" s="3">
-        <v>3.842242941384022E-3</v>
+        <v>3.8664958977510842E-3</v>
       </c>
       <c r="AC345" s="3">
         <v>4.1096083137911925E-3</v>
@@ -30098,7 +30128,7 @@
         <v>4.3451409109198291E-3</v>
       </c>
       <c r="AF345">
-        <v>12817</v>
+        <v>13742.025000000001</v>
       </c>
       <c r="AG345">
         <v>11860.42</v>
@@ -30184,7 +30214,7 @@
         <v>7.2703037038053253E-3</v>
       </c>
       <c r="AB346" s="3">
-        <v>3.9762961495592849E-3</v>
+        <v>4.0148335541487041E-3</v>
       </c>
       <c r="AC346" s="3">
         <v>4.1902498814671025E-3</v>
@@ -30199,7 +30229,7 @@
         <v>11860.42</v>
       </c>
       <c r="AH346">
-        <v>15319.65</v>
+        <v>15213.34</v>
       </c>
     </row>
     <row r="347" spans="1:34" x14ac:dyDescent="0.3">
@@ -30279,7 +30309,7 @@
         <v>3.2856824967752996E-3</v>
       </c>
       <c r="AB347" s="3">
-        <v>3.991312552297949E-3</v>
+        <v>3.9678770035588579E-3</v>
       </c>
       <c r="AC347" s="3">
         <v>4.1186813120307553E-3</v>
@@ -30288,13 +30318,13 @@
         <v>4.3819000534491082E-3</v>
       </c>
       <c r="AF347">
-        <v>13742.025000000001</v>
+        <v>12817</v>
       </c>
       <c r="AG347">
         <v>11860.42</v>
       </c>
       <c r="AH347">
-        <v>15213.34</v>
+        <v>15099.34</v>
       </c>
     </row>
     <row r="348" spans="1:34" x14ac:dyDescent="0.3">
@@ -30374,7 +30404,7 @@
         <v>5.1786353305154353E-3</v>
       </c>
       <c r="AB348" s="3">
-        <v>4.0069337237832641E-3</v>
+        <v>3.9195392899526857E-3</v>
       </c>
       <c r="AC348" s="3">
         <v>4.0571534531767504E-3</v>
@@ -30386,7 +30416,7 @@
         <v>12817</v>
       </c>
       <c r="AG348">
-        <v>11860.42</v>
+        <v>11224.14</v>
       </c>
       <c r="AH348">
         <v>15099.34</v>
@@ -30469,7 +30499,7 @@
         <v>5.5171346258195975E-3</v>
       </c>
       <c r="AB349" s="3">
-        <v>3.971074623367747E-3</v>
+        <v>4.0210646742137261E-3</v>
       </c>
       <c r="AC349" s="3">
         <v>3.959196733373231E-3</v>
@@ -30484,7 +30514,7 @@
         <v>11224.14</v>
       </c>
       <c r="AH349">
-        <v>15099.34</v>
+        <v>15213.34</v>
       </c>
     </row>
     <row r="350" spans="1:34" x14ac:dyDescent="0.3">
@@ -30564,7 +30594,7 @@
         <v>5.8290884519247577E-3</v>
       </c>
       <c r="AB350" s="3">
-        <v>4.0793880218818234E-3</v>
+        <v>4.1546924866932454E-3</v>
       </c>
       <c r="AC350" s="3">
         <v>3.9791332247346807E-3</v>
@@ -30573,13 +30603,13 @@
         <v>4.4639649849087448E-3</v>
       </c>
       <c r="AF350">
-        <v>12817</v>
+        <v>12309.045</v>
       </c>
       <c r="AG350">
-        <v>11224.14</v>
+        <v>11281.305</v>
       </c>
       <c r="AH350">
-        <v>15213.34</v>
+        <v>15099.34</v>
       </c>
     </row>
     <row r="351" spans="1:34" x14ac:dyDescent="0.3">
@@ -30659,7 +30689,7 @@
         <v>3.0447911969222474E-4</v>
       </c>
       <c r="AB351" s="3">
-        <v>4.030492055499664E-3</v>
+        <v>4.1235839827280891E-3</v>
       </c>
       <c r="AC351" s="3">
         <v>3.8609015834986898E-3</v>
@@ -30671,7 +30701,7 @@
         <v>12309.045</v>
       </c>
       <c r="AG351">
-        <v>11281.305</v>
+        <v>11860.42</v>
       </c>
       <c r="AH351">
         <v>15099.34</v>
@@ -30754,7 +30784,7 @@
         <v>2.2149680778775771E-3</v>
       </c>
       <c r="AB352" s="3">
-        <v>4.0620157277329108E-3</v>
+        <v>4.079691717317765E-3</v>
       </c>
       <c r="AC352" s="3">
         <v>3.6788150649611773E-3</v>
@@ -30766,13 +30796,13 @@
         <v>12309.045</v>
       </c>
       <c r="AG352">
-        <v>11860.42</v>
+        <v>11281.305</v>
       </c>
       <c r="AH352">
-        <v>15099.34</v>
-      </c>
-    </row>
-    <row r="353" spans="1:34" x14ac:dyDescent="0.3">
+        <v>15026.974999999999</v>
+      </c>
+    </row>
+    <row r="353" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A353" s="1">
         <v>46267</v>
       </c>
@@ -30849,7 +30879,7 @@
         <v>1.9606634496809328E-3</v>
       </c>
       <c r="AB353" s="3">
-        <v>4.0113359667488342E-3</v>
+        <v>4.1292535345243981E-3</v>
       </c>
       <c r="AC353" s="3">
         <v>3.6249999437872882E-3</v>
@@ -30858,7 +30888,7 @@
         <v>4.4279744643727359E-3</v>
       </c>
       <c r="AF353">
-        <v>12309.045</v>
+        <v>11332.575000000001</v>
       </c>
       <c r="AG353">
         <v>11281.305</v>
@@ -30867,7 +30897,7 @@
         <v>15026.974999999999</v>
       </c>
     </row>
-    <row r="354" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A354" s="1">
         <v>46268</v>
       </c>
@@ -30944,7 +30974,7 @@
         <v>9.6047903954477043E-4</v>
       </c>
       <c r="AB354" s="3">
-        <v>4.0270350024282815E-3</v>
+        <v>3.9979328401384328E-3</v>
       </c>
       <c r="AC354" s="3">
         <v>3.5009950190045824E-3</v>
@@ -30959,10 +30989,10 @@
         <v>11281.305</v>
       </c>
       <c r="AH354">
-        <v>15026.974999999999</v>
-      </c>
-    </row>
-    <row r="355" spans="1:34" x14ac:dyDescent="0.3">
+        <v>15099.34</v>
+      </c>
+    </row>
+    <row r="355" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A355" s="1">
         <v>46269</v>
       </c>
@@ -31039,7 +31069,7 @@
         <v>2.5287834154252842E-3</v>
       </c>
       <c r="AB355" s="3">
-        <v>3.9505409232122026E-3</v>
+        <v>4.0489739260854861E-3</v>
       </c>
       <c r="AC355" s="3">
         <v>3.5321850669362389E-3</v>
@@ -31048,16 +31078,16 @@
         <v>4.3174597247044588E-3</v>
       </c>
       <c r="AF355">
-        <v>11332.575000000001</v>
+        <v>10691.205</v>
       </c>
       <c r="AG355">
-        <v>11281.305</v>
+        <v>10696.294999999998</v>
       </c>
       <c r="AH355">
-        <v>15099.34</v>
-      </c>
-    </row>
-    <row r="356" spans="1:34" x14ac:dyDescent="0.3">
+        <v>15026.974999999999</v>
+      </c>
+    </row>
+    <row r="356" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A356" s="1">
         <v>46272</v>
       </c>
@@ -31134,7 +31164,7 @@
         <v>1.6753113438161549E-4</v>
       </c>
       <c r="AB356" s="3">
-        <v>3.9237660940950386E-3</v>
+        <v>3.9860863283073733E-3</v>
       </c>
       <c r="AC356" s="3">
         <v>3.4680151296453093E-3</v>
@@ -31152,7 +31182,7 @@
         <v>15026.974999999999</v>
       </c>
     </row>
-    <row r="357" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A357" s="1">
         <v>46273</v>
       </c>
@@ -31229,7 +31259,7 @@
         <v>2.5165264244890739E-3</v>
       </c>
       <c r="AB357" s="3">
-        <v>3.9386811701196869E-3</v>
+        <v>4.0123695286830132E-3</v>
       </c>
       <c r="AC357" s="3">
         <v>3.3481460834506372E-3</v>
@@ -31244,10 +31274,10 @@
         <v>10696.294999999998</v>
       </c>
       <c r="AH357">
-        <v>15026.974999999999</v>
-      </c>
-    </row>
-    <row r="358" spans="1:34" x14ac:dyDescent="0.3">
+        <v>14806.474999999999</v>
+      </c>
+    </row>
+    <row r="358" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A358" s="1">
         <v>46274</v>
       </c>
@@ -31324,7 +31354,7 @@
         <v>1.8525486756668652E-3</v>
       </c>
       <c r="AB358" s="3">
-        <v>3.9426978882631369E-3</v>
+        <v>3.9544259240834228E-3</v>
       </c>
       <c r="AC358" s="3">
         <v>3.3457956994324117E-3</v>
@@ -31342,7 +31372,7 @@
         <v>14806.474999999999</v>
       </c>
     </row>
-    <row r="359" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A359" s="1">
         <v>46275</v>
       </c>
@@ -31419,7 +31449,7 @@
         <v>9.5370559753069628E-3</v>
       </c>
       <c r="AB359" s="3">
-        <v>4.1345107644454723E-3</v>
+        <v>4.2218279625259444E-3</v>
       </c>
       <c r="AC359" s="3">
         <v>3.5021359560294452E-3</v>
@@ -31428,16 +31458,16 @@
         <v>4.3600937548831107E-3</v>
       </c>
       <c r="AF359">
-        <v>10691.205</v>
+        <v>10365.225</v>
       </c>
       <c r="AG359">
-        <v>10696.294999999998</v>
+        <v>10634.04</v>
       </c>
       <c r="AH359">
-        <v>14806.474999999999</v>
-      </c>
-    </row>
-    <row r="360" spans="1:34" x14ac:dyDescent="0.3">
+        <v>14583.625</v>
+      </c>
+    </row>
+    <row r="360" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A360" s="1">
         <v>46276</v>
       </c>
@@ -31520,7 +31550,7 @@
         <v>7.0544302483779298E-3</v>
       </c>
       <c r="AB360" s="3">
-        <v>4.3132022298114922E-3</v>
+        <v>4.2870882046858816E-3</v>
       </c>
       <c r="AC360" s="3">
         <v>3.541403736609276E-3</v>
@@ -31532,13 +31562,16 @@
         <v>10365.225</v>
       </c>
       <c r="AG360">
-        <v>10634.04</v>
+        <v>10576.775000000001</v>
       </c>
       <c r="AH360">
         <v>14583.625</v>
       </c>
-    </row>
-    <row r="361" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AI360">
+        <v>10262.950000000001</v>
+      </c>
+    </row>
+    <row r="361" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A361" s="1">
         <v>46279</v>
       </c>
@@ -31621,7 +31654,7 @@
         <v>7.406412654292982E-3</v>
       </c>
       <c r="AB361" s="3">
-        <v>4.3877115740280455E-3</v>
+        <v>4.5039315673331935E-3</v>
       </c>
       <c r="AC361" s="3">
         <v>3.603507270101784E-3</v>
@@ -31629,6 +31662,9 @@
       <c r="AD361" s="3">
         <v>4.4234507089234813E-3</v>
       </c>
+      <c r="AE361" s="3">
+        <v>5.0403580844362549E-3</v>
+      </c>
       <c r="AF361">
         <v>10365.225</v>
       </c>
@@ -31636,10 +31672,13 @@
         <v>10576.775000000001</v>
       </c>
       <c r="AH361">
-        <v>14583.625</v>
-      </c>
-    </row>
-    <row r="362" spans="1:34" x14ac:dyDescent="0.3">
+        <v>14523.3</v>
+      </c>
+      <c r="AI361">
+        <v>10402.799999999999</v>
+      </c>
+    </row>
+    <row r="362" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A362" s="1">
         <v>46280</v>
       </c>
@@ -31722,7 +31761,7 @@
         <v>1.0741939687670898E-2</v>
       </c>
       <c r="AB362" s="3">
-        <v>4.7051576357311836E-3</v>
+        <v>4.8001904466822062E-3</v>
       </c>
       <c r="AC362" s="3">
         <v>3.7590148083678459E-3</v>
@@ -31737,13 +31776,16 @@
         <v>10365.225</v>
       </c>
       <c r="AG362">
-        <v>10576.775000000001</v>
+        <v>10634.04</v>
       </c>
       <c r="AH362">
-        <v>14523.3</v>
-      </c>
-    </row>
-    <row r="363" spans="1:34" x14ac:dyDescent="0.3">
+        <v>14583.625</v>
+      </c>
+      <c r="AI362">
+        <v>10402.799999999999</v>
+      </c>
+    </row>
+    <row r="363" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A363" s="1">
         <v>46281</v>
       </c>
@@ -31826,7 +31868,7 @@
         <v>1.5921143293013085E-2</v>
       </c>
       <c r="AB363" s="3">
-        <v>5.1589308610799764E-3</v>
+        <v>5.3204255668214111E-3</v>
       </c>
       <c r="AC363" s="3">
         <v>4.0103886190526834E-3</v>
@@ -31838,16 +31880,19 @@
         <v>5.0780246920304247E-3</v>
       </c>
       <c r="AF363">
-        <v>10365.225</v>
+        <v>10047.755000000001</v>
       </c>
       <c r="AG363">
-        <v>10634.04</v>
+        <v>10576.775000000001</v>
       </c>
       <c r="AH363">
-        <v>14583.625</v>
-      </c>
-    </row>
-    <row r="364" spans="1:34" x14ac:dyDescent="0.3">
+        <v>14523.3</v>
+      </c>
+      <c r="AI363">
+        <v>10262.950000000001</v>
+      </c>
+    </row>
+    <row r="364" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A364" s="1">
         <v>46282</v>
       </c>
@@ -31930,7 +31975,7 @@
         <v>1.0969133742124049E-2</v>
       </c>
       <c r="AB364" s="3">
-        <v>5.5026419595731093E-3</v>
+        <v>5.3453676302366382E-3</v>
       </c>
       <c r="AC364" s="3">
         <v>4.1107716398549928E-3</v>
@@ -31942,16 +31987,19 @@
         <v>5.0831681096143106E-3</v>
       </c>
       <c r="AF364">
-        <v>10047.755000000001</v>
+        <v>9703.1049999999996</v>
       </c>
       <c r="AG364">
         <v>10576.775000000001</v>
       </c>
       <c r="AH364">
-        <v>14523.3</v>
-      </c>
-    </row>
-    <row r="365" spans="1:34" x14ac:dyDescent="0.3">
+        <v>14321.875</v>
+      </c>
+      <c r="AI364">
+        <v>10229.825000000001</v>
+      </c>
+    </row>
+    <row r="365" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A365" s="1">
         <v>46283</v>
       </c>
@@ -32034,7 +32082,7 @@
         <v>1.5962208833382174E-2</v>
       </c>
       <c r="AB365" s="3">
-        <v>5.6878463787252038E-3</v>
+        <v>5.5337435506846557E-3</v>
       </c>
       <c r="AC365" s="3">
         <v>4.3219424150009846E-3</v>
@@ -32049,13 +32097,16 @@
         <v>9703.1049999999996</v>
       </c>
       <c r="AG365">
-        <v>10576.775000000001</v>
+        <v>10634.04</v>
       </c>
       <c r="AH365">
-        <v>14321.875</v>
-      </c>
-    </row>
-    <row r="366" spans="1:34" x14ac:dyDescent="0.3">
+        <v>14523.3</v>
+      </c>
+      <c r="AI365">
+        <v>10229.825000000001</v>
+      </c>
+    </row>
+    <row r="366" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A366" s="1">
         <v>46286</v>
       </c>
@@ -32138,7 +32189,7 @@
         <v>1.6435146354335739E-2</v>
       </c>
       <c r="AB366" s="3">
-        <v>5.885401705641142E-3</v>
+        <v>5.9448569771949934E-3</v>
       </c>
       <c r="AC366" s="3">
         <v>4.5045683400572268E-3</v>
@@ -32150,16 +32201,19 @@
         <v>5.1051661980878755E-3</v>
       </c>
       <c r="AF366">
-        <v>9703.1049999999996</v>
+        <v>10047.755000000001</v>
       </c>
       <c r="AG366">
-        <v>10634.04</v>
+        <v>10696.294999999998</v>
       </c>
       <c r="AH366">
-        <v>14523.3</v>
-      </c>
-    </row>
-    <row r="367" spans="1:34" x14ac:dyDescent="0.3">
+        <v>14321.875</v>
+      </c>
+      <c r="AI366">
+        <v>10229.825000000001</v>
+      </c>
+    </row>
+    <row r="367" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A367" s="1">
         <v>46287</v>
       </c>
@@ -32242,7 +32296,7 @@
         <v>1.6773399619015583E-2</v>
       </c>
       <c r="AB367" s="3">
-        <v>6.2941648043504965E-3</v>
+        <v>6.3820447304158883E-3</v>
       </c>
       <c r="AC367" s="3">
         <v>4.7738208465831012E-3</v>
@@ -32254,13 +32308,16 @@
         <v>5.1114920139901671E-3</v>
       </c>
       <c r="AF367">
-        <v>10047.755000000001</v>
+        <v>10101.5</v>
       </c>
       <c r="AG367">
-        <v>10696.294999999998</v>
+        <v>10753.46</v>
       </c>
       <c r="AH367">
-        <v>14321.875</v>
+        <v>14153.6</v>
+      </c>
+      <c r="AI367">
+        <v>10214.75</v>
       </c>
     </row>
   </sheetData>

--- a/Data/Data-ETFPESOV.xlsx
+++ b/Data/Data-ETFPESOV.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Desktop\Dashboards\ETFPESOV\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6ADAB20C-CF59-4CDA-90D1-19D939734D26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6741337C-1431-4C9A-A2DF-08FED9D24CA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{F6F75CCC-009E-413C-B55D-A670828334F1}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="36">
   <si>
     <t>Fecha</t>
   </si>
@@ -530,7 +530,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E89EACC1-FF2B-4ECD-9B28-49A6BC374F12}">
-  <dimension ref="A1:AI367"/>
+  <dimension ref="A1:AI368"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="27" max="31" width="11.5546875" style="3"/>
@@ -32226,8 +32226,8 @@
       <c r="D367" t="s">
         <v>23</v>
       </c>
-      <c r="E367" t="s">
-        <v>23</v>
+      <c r="E367">
+        <v>8185.43</v>
       </c>
       <c r="F367">
         <v>2</v>
@@ -32284,7 +32284,7 @@
         <v>0.98475968050917295</v>
       </c>
       <c r="X367">
-        <v>112.64</v>
+        <v>112.13</v>
       </c>
       <c r="Y367">
         <v>-2.3400283702201263</v>
@@ -32293,31 +32293,138 @@
         <v>-3.9109511967821864</v>
       </c>
       <c r="AA367" s="3">
-        <v>1.6773399619015583E-2</v>
+        <v>1.2169755852984965E-2</v>
       </c>
       <c r="AB367" s="3">
-        <v>6.3820447304158883E-3</v>
+        <v>6.2285899382148683E-3</v>
       </c>
       <c r="AC367" s="3">
-        <v>4.7738208465831012E-3</v>
+        <v>4.6970934504825907E-3</v>
       </c>
       <c r="AD367" s="3">
-        <v>4.7392286830733087E-3</v>
+        <v>4.7136528843731386E-3</v>
       </c>
       <c r="AE367" s="3">
-        <v>5.1114920139901671E-3</v>
+        <v>5.0987041146400821E-3</v>
       </c>
       <c r="AF367">
-        <v>10101.5</v>
+        <v>10047.755000000001</v>
       </c>
       <c r="AG367">
+        <v>10696.294999999998</v>
+      </c>
+      <c r="AH367">
+        <v>14013.900000000001</v>
+      </c>
+      <c r="AI367">
+        <v>10191.35</v>
+      </c>
+    </row>
+    <row r="368" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A368" s="1">
+        <v>46288</v>
+      </c>
+      <c r="B368">
+        <v>110.77187807763744</v>
+      </c>
+      <c r="C368">
+        <v>149818965.10000464</v>
+      </c>
+      <c r="D368" t="s">
+        <v>23</v>
+      </c>
+      <c r="E368" t="s">
+        <v>23</v>
+      </c>
+      <c r="F368">
+        <v>5</v>
+      </c>
+      <c r="G368">
+        <v>6.3550661114652192</v>
+      </c>
+      <c r="H368">
+        <v>6.0694748748429186</v>
+      </c>
+      <c r="I368">
+        <v>182.02</v>
+      </c>
+      <c r="J368">
+        <v>6.4</v>
+      </c>
+      <c r="K368">
+        <v>6.1</v>
+      </c>
+      <c r="L368">
+        <v>10.771878077637442</v>
+      </c>
+      <c r="M368">
+        <v>11.262570742885902</v>
+      </c>
+      <c r="N368">
+        <v>6.5793825768943535</v>
+      </c>
+      <c r="O368">
+        <v>6.5699999999999994</v>
+      </c>
+      <c r="P368">
+        <v>4.3863515183109108E-3</v>
+      </c>
+      <c r="Q368">
+        <v>4.026915827890918E-3</v>
+      </c>
+      <c r="R368">
+        <v>0.10887086985837749</v>
+      </c>
+      <c r="S368">
+        <v>0.17143019702372669</v>
+      </c>
+      <c r="T368">
+        <v>4.5090410616155374E-2</v>
+      </c>
+      <c r="U368">
+        <v>9.0695918317706958E-2</v>
+      </c>
+      <c r="V368">
+        <v>0.26455507137004286</v>
+      </c>
+      <c r="W368">
+        <v>0.29329973143967791</v>
+      </c>
+      <c r="X368">
+        <v>112.13</v>
+      </c>
+      <c r="Y368">
+        <v>-2.3487859872683092</v>
+      </c>
+      <c r="Z368">
+        <v>-3.9109511967821864</v>
+      </c>
+      <c r="AA368" s="3">
+        <v>1.2260529891988226E-2</v>
+      </c>
+      <c r="AB368" s="3">
+        <v>6.4703887624309488E-3</v>
+      </c>
+      <c r="AC368" s="3">
+        <v>4.8779245741929246E-3</v>
+      </c>
+      <c r="AD368" s="3">
+        <v>4.7611961608826038E-3</v>
+      </c>
+      <c r="AE368" s="3">
+        <v>5.1033297175852432E-3</v>
+      </c>
+      <c r="AF368">
+        <v>9994.01</v>
+      </c>
+      <c r="AG368">
         <v>10753.46</v>
       </c>
-      <c r="AH367">
-        <v>14153.6</v>
-      </c>
-      <c r="AI367">
-        <v>10214.75</v>
+      <c r="AH368">
+        <v>13874.2</v>
+      </c>
+      <c r="AI368">
+        <v>10167.950000000001</v>
       </c>
     </row>
   </sheetData>

--- a/Data/Data-ETFPESOV.xlsx
+++ b/Data/Data-ETFPESOV.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Desktop\Dashboards\ETFPESOV\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6741337C-1431-4C9A-A2DF-08FED9D24CA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C3AC6D7-BA80-4320-A74B-C52DD65F0128}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{F6F75CCC-009E-413C-B55D-A670828334F1}"/>
   </bookViews>
@@ -32391,7 +32391,7 @@
         <v>0.29329973143967791</v>
       </c>
       <c r="X368">
-        <v>112.13</v>
+        <v>111</v>
       </c>
       <c r="Y368">
         <v>-2.3487859872683092</v>
@@ -32400,19 +32400,19 @@
         <v>-3.9109511967821864</v>
       </c>
       <c r="AA368" s="3">
-        <v>1.2260529891988226E-2</v>
+        <v>2.0593848034486939E-3</v>
       </c>
       <c r="AB368" s="3">
-        <v>6.4703887624309488E-3</v>
+        <v>6.1303505928129642E-3</v>
       </c>
       <c r="AC368" s="3">
-        <v>4.8779245741929246E-3</v>
+        <v>4.7079054893839328E-3</v>
       </c>
       <c r="AD368" s="3">
-        <v>4.7611961608826038E-3</v>
+        <v>4.7045231326129401E-3</v>
       </c>
       <c r="AE368" s="3">
-        <v>5.1033297175852432E-3</v>
+        <v>5.0749932034504109E-3</v>
       </c>
       <c r="AF368">
         <v>9994.01</v>
